--- a/argus/kship/models/108380_model.xlsx
+++ b/argus/kship/models/108380_model.xlsx
@@ -21,7 +21,7 @@
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
     <definedName name="환율">변수!$C$6:$AO$13</definedName>
     <definedName name="BS연결H">BS연결!$C$1:$AO$1</definedName>
-    <definedName name="BS연결">BS연결!$C$5:$AO$83</definedName>
+    <definedName name="BS연결">BS연결!$C$5:$AO$84</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AO$1</definedName>
     <definedName name="BS별도">BS별도!$C$5:$AO$82</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AO$1</definedName>
@@ -4354,7 +4354,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 17.9, "op_wape_pct": 43.3, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 543.67, "rev_act": 615.33, "op_pred": 34.39, "op_act": 77.43}, {"q": "2025Q4", "rev_pred": 732.64, "rev_act": 565.96, "op_pred": 46.35, "op_act": 78.24}, {"q": "2026Q1", "rev_pred": 676.16, "rev_act": 508.96, "op_pred": 42.77, "op_act": 62.74}, {"q": "2026Q2", "rev_pred": 684.5, "rev_act": 708.34, "op_pred": 43.3, "op_act": 75.59}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 17.9, "op_wape_pct": 43.3, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 543.67, "rev_act": 615.33, "op_pred": 34.39, "op_act": 77.43}, {"q": "2025Q4", "rev_pred": 732.64, "rev_act": 565.96, "op_pred": 46.35, "op_act": 78.24}, {"q": "2026Q1", "rev_pred": 676.16, "rev_act": 508.96, "op_pred": 42.77, "op_act": 62.74}, {"q": "2026Q2", "rev_pred": 684.5, "rev_act": 708.34, "op_pred": 43.3, "op_act": 75.59}]}</t>
         </is>
       </c>
     </row>
@@ -9921,7 +9921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO83"/>
+  <dimension ref="A1:AO84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10169,7 +10169,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -15553,78 +15553,16 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E67" s="18" t="n">
-        <v>-2021.08</v>
+          <t>이자수익</t>
+        </is>
       </c>
       <c r="F67" s="9" t="n"/>
-      <c r="G67" s="18" t="n">
-        <v>-2106.41</v>
-      </c>
-      <c r="H67" s="18" t="n">
-        <v>-1064.97</v>
-      </c>
-      <c r="I67" s="18" t="n">
-        <v>3475.43</v>
-      </c>
-      <c r="J67" s="18" t="n">
-        <v>1252.2</v>
-      </c>
-      <c r="K67" s="34" t="n">
-        <v>1556.25</v>
-      </c>
-      <c r="L67" s="18" t="n">
-        <v>-1921.42</v>
-      </c>
-      <c r="M67" s="18" t="n">
-        <v>10344.92</v>
-      </c>
-      <c r="N67" s="18" t="n">
-        <v>-5291.58</v>
-      </c>
-      <c r="O67" s="18" t="n">
-        <v>20819.54</v>
-      </c>
-      <c r="P67" s="34" t="n">
-        <v>23951.46</v>
-      </c>
-      <c r="Q67" s="18" t="n">
-        <v>-5922.09</v>
-      </c>
-      <c r="R67" s="18" t="n">
-        <v>852.4299999999999</v>
-      </c>
-      <c r="S67" s="18" t="n">
-        <v>2627.91</v>
-      </c>
-      <c r="T67" s="18" t="n">
-        <v>-1822.15</v>
-      </c>
-      <c r="U67" s="34" t="n">
-        <v>-4263.9</v>
-      </c>
-      <c r="V67" s="18" t="n">
-        <v>-684.3200000000001</v>
-      </c>
-      <c r="W67" s="18" t="n">
-        <v>5477.81</v>
-      </c>
-      <c r="X67" s="18" t="n">
-        <v>-1425.65</v>
-      </c>
-      <c r="Y67" s="18" t="n">
-        <v>12197.11</v>
-      </c>
-      <c r="Z67" s="34" t="n">
-        <v>15564.95</v>
-      </c>
-      <c r="AA67" s="18" t="n">
-        <v>-1071.33</v>
-      </c>
+      <c r="K67" s="9" t="n"/>
+      <c r="P67" s="9" t="n"/>
+      <c r="U67" s="9" t="n"/>
+      <c r="Z67" s="9" t="n"/>
       <c r="AB67" s="19" t="n">
-        <v>13163.98</v>
+        <v>801.8200000000001</v>
       </c>
       <c r="AC67" s="10" t="n"/>
       <c r="AD67" s="10" t="n"/>
@@ -15646,41 +15584,79 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>감가상각비</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E68" s="18" t="n">
-        <v>873.66</v>
+        <v>-2021.08</v>
       </c>
       <c r="F68" s="9" t="n"/>
       <c r="G68" s="18" t="n">
-        <v>890.37</v>
+        <v>-2106.41</v>
       </c>
       <c r="H68" s="18" t="n">
-        <v>935.65</v>
+        <v>-1064.97</v>
       </c>
       <c r="I68" s="18" t="n">
-        <v>909.11</v>
+        <v>3475.43</v>
       </c>
       <c r="J68" s="18" t="n">
-        <v>903.46</v>
+        <v>1252.2</v>
       </c>
       <c r="K68" s="34" t="n">
-        <v>3638.59</v>
+        <v>1556.25</v>
       </c>
       <c r="L68" s="18" t="n">
-        <v>1018.41</v>
+        <v>-1921.42</v>
       </c>
       <c r="M68" s="18" t="n">
-        <v>1026</v>
-      </c>
-      <c r="P68" s="9" t="n"/>
+        <v>10344.92</v>
+      </c>
+      <c r="N68" s="18" t="n">
+        <v>-5291.58</v>
+      </c>
+      <c r="O68" s="18" t="n">
+        <v>20819.54</v>
+      </c>
+      <c r="P68" s="34" t="n">
+        <v>23951.46</v>
+      </c>
+      <c r="Q68" s="18" t="n">
+        <v>-5922.09</v>
+      </c>
+      <c r="R68" s="18" t="n">
+        <v>852.4299999999999</v>
+      </c>
       <c r="S68" s="18" t="n">
-        <v>1274.43</v>
-      </c>
-      <c r="U68" s="9" t="n"/>
-      <c r="Z68" s="9" t="n"/>
-      <c r="AB68" s="5" t="n"/>
+        <v>2627.91</v>
+      </c>
+      <c r="T68" s="18" t="n">
+        <v>-1822.15</v>
+      </c>
+      <c r="U68" s="34" t="n">
+        <v>-4263.9</v>
+      </c>
+      <c r="V68" s="18" t="n">
+        <v>-684.3200000000001</v>
+      </c>
+      <c r="W68" s="18" t="n">
+        <v>5477.81</v>
+      </c>
+      <c r="X68" s="18" t="n">
+        <v>-1425.65</v>
+      </c>
+      <c r="Y68" s="18" t="n">
+        <v>12197.11</v>
+      </c>
+      <c r="Z68" s="34" t="n">
+        <v>15564.95</v>
+      </c>
+      <c r="AA68" s="18" t="n">
+        <v>-1071.33</v>
+      </c>
+      <c r="AB68" s="19" t="n">
+        <v>13163.98</v>
+      </c>
       <c r="AC68" s="10" t="n"/>
       <c r="AD68" s="10" t="n"/>
       <c r="AE68" s="11" t="n"/>
@@ -15701,37 +15677,37 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>무형자산상각비</t>
+          <t>감가상각비</t>
         </is>
       </c>
       <c r="E69" s="18" t="n">
-        <v>286.54</v>
+        <v>873.66</v>
       </c>
       <c r="F69" s="9" t="n"/>
       <c r="G69" s="18" t="n">
-        <v>64.31</v>
+        <v>890.37</v>
       </c>
       <c r="H69" s="18" t="n">
-        <v>64.67</v>
+        <v>935.65</v>
       </c>
       <c r="I69" s="18" t="n">
-        <v>70.65000000000001</v>
+        <v>909.11</v>
       </c>
       <c r="J69" s="18" t="n">
-        <v>71.55</v>
+        <v>903.46</v>
       </c>
       <c r="K69" s="34" t="n">
-        <v>271.18</v>
+        <v>3638.59</v>
       </c>
       <c r="L69" s="18" t="n">
-        <v>66.23999999999999</v>
+        <v>1018.41</v>
       </c>
       <c r="M69" s="18" t="n">
-        <v>69.7</v>
+        <v>1026</v>
       </c>
       <c r="P69" s="9" t="n"/>
       <c r="S69" s="18" t="n">
-        <v>24.42</v>
+        <v>1274.43</v>
       </c>
       <c r="U69" s="9" t="n"/>
       <c r="Z69" s="9" t="n"/>
@@ -15756,39 +15732,39 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>배당금수취(CF)</t>
+          <t>무형자산상각비</t>
         </is>
       </c>
       <c r="E70" s="18" t="n">
-        <v>24.13</v>
+        <v>286.54</v>
       </c>
       <c r="F70" s="9" t="n"/>
       <c r="G70" s="18" t="n">
-        <v>0</v>
+        <v>64.31</v>
       </c>
       <c r="H70" s="18" t="n">
-        <v>0.16</v>
+        <v>64.67</v>
       </c>
       <c r="I70" s="18" t="n">
-        <v>0</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="J70" s="18" t="n">
-        <v>0</v>
+        <v>71.55</v>
       </c>
       <c r="K70" s="34" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="N70" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" s="18" t="n">
-        <v>0</v>
+        <v>271.18</v>
+      </c>
+      <c r="L70" s="18" t="n">
+        <v>66.23999999999999</v>
+      </c>
+      <c r="M70" s="18" t="n">
+        <v>69.7</v>
       </c>
       <c r="P70" s="9" t="n"/>
+      <c r="S70" s="18" t="n">
+        <v>24.42</v>
+      </c>
       <c r="U70" s="9" t="n"/>
-      <c r="V70" s="18" t="n">
-        <v>0</v>
-      </c>
       <c r="Z70" s="9" t="n"/>
       <c r="AB70" s="5" t="n"/>
       <c r="AC70" s="10" t="n"/>
@@ -15811,79 +15787,41 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
+          <t>배당금수취(CF)</t>
         </is>
       </c>
       <c r="E71" s="18" t="n">
-        <v>380.97</v>
+        <v>24.13</v>
       </c>
       <c r="F71" s="9" t="n"/>
       <c r="G71" s="18" t="n">
-        <v>-51.17</v>
+        <v>0</v>
       </c>
       <c r="H71" s="18" t="n">
-        <v>1078.28</v>
+        <v>0.16</v>
       </c>
       <c r="I71" s="18" t="n">
-        <v>-4.15</v>
+        <v>0</v>
       </c>
       <c r="J71" s="18" t="n">
-        <v>178.33</v>
+        <v>0</v>
       </c>
       <c r="K71" s="34" t="n">
-        <v>1201.29</v>
-      </c>
-      <c r="L71" s="18" t="n">
-        <v>-162.56</v>
-      </c>
-      <c r="M71" s="18" t="n">
-        <v>161.75</v>
+        <v>0.16</v>
       </c>
       <c r="N71" s="18" t="n">
-        <v>-122.81</v>
+        <v>0</v>
       </c>
       <c r="O71" s="18" t="n">
-        <v>-130.4</v>
-      </c>
-      <c r="P71" s="34" t="n">
-        <v>-254.02</v>
-      </c>
-      <c r="Q71" s="18" t="n">
-        <v>-143.69</v>
-      </c>
-      <c r="R71" s="18" t="n">
-        <v>-139.11</v>
-      </c>
-      <c r="S71" s="18" t="n">
-        <v>-130.96</v>
-      </c>
-      <c r="T71" s="18" t="n">
-        <v>-134.36</v>
-      </c>
-      <c r="U71" s="34" t="n">
-        <v>-548.12</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P71" s="9" t="n"/>
+      <c r="U71" s="9" t="n"/>
       <c r="V71" s="18" t="n">
-        <v>-1463.8</v>
-      </c>
-      <c r="W71" s="18" t="n">
-        <v>-1662.06</v>
-      </c>
-      <c r="X71" s="18" t="n">
-        <v>-910.35</v>
-      </c>
-      <c r="Y71" s="18" t="n">
-        <v>-692.9299999999999</v>
-      </c>
-      <c r="Z71" s="34" t="n">
-        <v>-4729.14</v>
-      </c>
-      <c r="AA71" s="18" t="n">
-        <v>-2628.39</v>
-      </c>
-      <c r="AB71" s="19" t="n">
-        <v>-3268.93</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z71" s="9" t="n"/>
+      <c r="AB71" s="5" t="n"/>
       <c r="AC71" s="10" t="n"/>
       <c r="AD71" s="10" t="n"/>
       <c r="AE71" s="11" t="n"/>
@@ -15904,78 +15842,78 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E72" s="18" t="n">
-        <v>-9118.129999999999</v>
+        <v>380.97</v>
       </c>
       <c r="F72" s="9" t="n"/>
       <c r="G72" s="18" t="n">
-        <v>-8931.379999999999</v>
+        <v>-51.17</v>
       </c>
       <c r="H72" s="18" t="n">
-        <v>-1454.67</v>
+        <v>1078.28</v>
       </c>
       <c r="I72" s="18" t="n">
-        <v>-1729.73</v>
+        <v>-4.15</v>
       </c>
       <c r="J72" s="18" t="n">
-        <v>-1660.56</v>
+        <v>178.33</v>
       </c>
       <c r="K72" s="34" t="n">
-        <v>-13776.34</v>
+        <v>1201.29</v>
       </c>
       <c r="L72" s="18" t="n">
-        <v>-1998.76</v>
+        <v>-162.56</v>
       </c>
       <c r="M72" s="18" t="n">
-        <v>-4132.58</v>
+        <v>161.75</v>
       </c>
       <c r="N72" s="18" t="n">
-        <v>-6298.03</v>
+        <v>-122.81</v>
       </c>
       <c r="O72" s="18" t="n">
-        <v>-3875.81</v>
+        <v>-130.4</v>
       </c>
       <c r="P72" s="34" t="n">
-        <v>-16305.18</v>
+        <v>-254.02</v>
       </c>
       <c r="Q72" s="18" t="n">
-        <v>-2651.72</v>
+        <v>-143.69</v>
       </c>
       <c r="R72" s="18" t="n">
-        <v>-2828.43</v>
+        <v>-139.11</v>
       </c>
       <c r="S72" s="18" t="n">
-        <v>-790.13</v>
+        <v>-130.96</v>
       </c>
       <c r="T72" s="18" t="n">
-        <v>-2556.5</v>
+        <v>-134.36</v>
       </c>
       <c r="U72" s="34" t="n">
-        <v>-8826.780000000001</v>
+        <v>-548.12</v>
       </c>
       <c r="V72" s="18" t="n">
-        <v>1089.33</v>
+        <v>-1463.8</v>
       </c>
       <c r="W72" s="18" t="n">
-        <v>-3797.75</v>
+        <v>-1662.06</v>
       </c>
       <c r="X72" s="18" t="n">
-        <v>-1999.43</v>
+        <v>-910.35</v>
       </c>
       <c r="Y72" s="18" t="n">
-        <v>-1251.82</v>
+        <v>-692.9299999999999</v>
       </c>
       <c r="Z72" s="34" t="n">
-        <v>-5959.67</v>
+        <v>-4729.14</v>
       </c>
       <c r="AA72" s="18" t="n">
-        <v>-1962.85</v>
+        <v>-2628.39</v>
       </c>
       <c r="AB72" s="19" t="n">
-        <v>-8154.67</v>
+        <v>-3268.93</v>
       </c>
       <c r="AC72" s="10" t="n"/>
       <c r="AD72" s="10" t="n"/>
@@ -15997,73 +15935,78 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E73" s="18" t="n">
-        <v>31.27</v>
+        <v>-9118.129999999999</v>
       </c>
       <c r="F73" s="9" t="n"/>
       <c r="G73" s="18" t="n">
-        <v>493.39</v>
+        <v>-8931.379999999999</v>
       </c>
       <c r="H73" s="18" t="n">
-        <v>52.65</v>
+        <v>-1454.67</v>
+      </c>
+      <c r="I73" s="18" t="n">
+        <v>-1729.73</v>
       </c>
       <c r="J73" s="18" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="K73" s="9" t="n"/>
+        <v>-1660.56</v>
+      </c>
+      <c r="K73" s="34" t="n">
+        <v>-13776.34</v>
+      </c>
       <c r="L73" s="18" t="n">
-        <v>0</v>
+        <v>-1998.76</v>
       </c>
       <c r="M73" s="18" t="n">
-        <v>15.23</v>
+        <v>-4132.58</v>
       </c>
       <c r="N73" s="18" t="n">
-        <v>100.2</v>
+        <v>-6298.03</v>
       </c>
       <c r="O73" s="18" t="n">
-        <v>7.69</v>
+        <v>-3875.81</v>
       </c>
       <c r="P73" s="34" t="n">
-        <v>123.12</v>
+        <v>-16305.18</v>
       </c>
       <c r="Q73" s="18" t="n">
-        <v>1</v>
+        <v>-2651.72</v>
       </c>
       <c r="R73" s="18" t="n">
-        <v>15.37</v>
+        <v>-2828.43</v>
       </c>
       <c r="S73" s="18" t="n">
-        <v>3.15</v>
+        <v>-790.13</v>
       </c>
       <c r="T73" s="18" t="n">
-        <v>0</v>
+        <v>-2556.5</v>
       </c>
       <c r="U73" s="34" t="n">
-        <v>19.52</v>
+        <v>-8826.780000000001</v>
       </c>
       <c r="V73" s="18" t="n">
-        <v>2.73</v>
+        <v>1089.33</v>
       </c>
       <c r="W73" s="18" t="n">
-        <v>5.28</v>
+        <v>-3797.75</v>
       </c>
       <c r="X73" s="18" t="n">
-        <v>0.34</v>
+        <v>-1999.43</v>
       </c>
       <c r="Y73" s="18" t="n">
-        <v>6.48</v>
+        <v>-1251.82</v>
       </c>
       <c r="Z73" s="34" t="n">
-        <v>14.83</v>
+        <v>-5959.67</v>
       </c>
       <c r="AA73" s="18" t="n">
-        <v>3.7</v>
+        <v>-1962.85</v>
       </c>
       <c r="AB73" s="19" t="n">
-        <v>1.46</v>
+        <v>-8154.67</v>
       </c>
       <c r="AC73" s="10" t="n"/>
       <c r="AD73" s="10" t="n"/>
@@ -16085,78 +16028,73 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
+          <t>유형자산의감소</t>
         </is>
       </c>
       <c r="E74" s="18" t="n">
-        <v>4117.28</v>
+        <v>31.27</v>
       </c>
       <c r="F74" s="9" t="n"/>
       <c r="G74" s="18" t="n">
-        <v>4224.3</v>
+        <v>493.39</v>
       </c>
       <c r="H74" s="18" t="n">
-        <v>1707.59</v>
-      </c>
-      <c r="I74" s="18" t="n">
-        <v>1377.17</v>
+        <v>52.65</v>
       </c>
       <c r="J74" s="18" t="n">
-        <v>593.84</v>
-      </c>
-      <c r="K74" s="34" t="n">
-        <v>7902.9</v>
-      </c>
+        <v>3.63</v>
+      </c>
+      <c r="K74" s="9" t="n"/>
       <c r="L74" s="18" t="n">
-        <v>478.92</v>
+        <v>0</v>
       </c>
       <c r="M74" s="18" t="n">
-        <v>4775.9</v>
+        <v>15.23</v>
       </c>
       <c r="N74" s="18" t="n">
-        <v>3064.44</v>
+        <v>100.2</v>
       </c>
       <c r="O74" s="18" t="n">
-        <v>2557.4</v>
+        <v>7.69</v>
       </c>
       <c r="P74" s="34" t="n">
-        <v>10876.66</v>
+        <v>123.12</v>
       </c>
       <c r="Q74" s="18" t="n">
-        <v>360.45</v>
+        <v>1</v>
       </c>
       <c r="R74" s="18" t="n">
-        <v>2282.96</v>
+        <v>15.37</v>
       </c>
       <c r="S74" s="18" t="n">
-        <v>592.9400000000001</v>
+        <v>3.15</v>
       </c>
       <c r="T74" s="18" t="n">
-        <v>1931.61</v>
+        <v>0</v>
       </c>
       <c r="U74" s="34" t="n">
-        <v>5167.96</v>
+        <v>19.52</v>
       </c>
       <c r="V74" s="18" t="n">
-        <v>1884.92</v>
+        <v>2.73</v>
       </c>
       <c r="W74" s="18" t="n">
-        <v>3191.58</v>
+        <v>5.28</v>
       </c>
       <c r="X74" s="18" t="n">
-        <v>1062.93</v>
+        <v>0.34</v>
       </c>
       <c r="Y74" s="18" t="n">
-        <v>1099.92</v>
+        <v>6.48</v>
       </c>
       <c r="Z74" s="34" t="n">
-        <v>7239.35</v>
+        <v>14.83</v>
       </c>
       <c r="AA74" s="18" t="n">
-        <v>1585.4</v>
+        <v>3.7</v>
       </c>
       <c r="AB74" s="19" t="n">
-        <v>7225.51</v>
+        <v>1.46</v>
       </c>
       <c r="AC74" s="10" t="n"/>
       <c r="AD74" s="10" t="n"/>
@@ -16178,7 +16116,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>유형자산의증가</t>
         </is>
       </c>
       <c r="E75" s="18" t="n">
@@ -16234,13 +16172,13 @@
         <v>1884.92</v>
       </c>
       <c r="W75" s="18" t="n">
-        <v>3665.39</v>
+        <v>3191.58</v>
       </c>
       <c r="X75" s="18" t="n">
-        <v>650.64</v>
+        <v>1062.93</v>
       </c>
       <c r="Y75" s="18" t="n">
-        <v>1038.4</v>
+        <v>1099.92</v>
       </c>
       <c r="Z75" s="34" t="n">
         <v>7239.35</v>
@@ -16271,78 +16209,78 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="E76" s="18" t="n">
-        <v>293.26</v>
+        <v>4117.28</v>
       </c>
       <c r="F76" s="9" t="n"/>
       <c r="G76" s="18" t="n">
-        <v>-53.22</v>
+        <v>4224.3</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>1885.67</v>
+        <v>1707.59</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>54.81</v>
+        <v>1377.17</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>37.69</v>
+        <v>593.84</v>
       </c>
       <c r="K76" s="34" t="n">
-        <v>1924.95</v>
+        <v>7902.9</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>-52.06</v>
+        <v>478.92</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>1631.23</v>
+        <v>4775.9</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>1437.69</v>
+        <v>3064.44</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>709.11</v>
+        <v>2557.4</v>
       </c>
       <c r="P76" s="34" t="n">
-        <v>3725.97</v>
+        <v>10876.66</v>
       </c>
       <c r="Q76" s="18" t="n">
-        <v>-34.18</v>
+        <v>360.45</v>
       </c>
       <c r="R76" s="18" t="n">
-        <v>4797.94</v>
+        <v>2282.96</v>
       </c>
       <c r="S76" s="18" t="n">
-        <v>538.13</v>
+        <v>592.9400000000001</v>
       </c>
       <c r="T76" s="18" t="n">
-        <v>2028.97</v>
+        <v>1931.61</v>
       </c>
       <c r="U76" s="34" t="n">
-        <v>7330.86</v>
+        <v>5167.96</v>
       </c>
       <c r="V76" s="18" t="n">
-        <v>2595.38</v>
+        <v>1884.92</v>
       </c>
       <c r="W76" s="18" t="n">
-        <v>-3627.7</v>
+        <v>3665.39</v>
       </c>
       <c r="X76" s="18" t="n">
-        <v>6048.52</v>
+        <v>650.64</v>
       </c>
       <c r="Y76" s="18" t="n">
-        <v>-5809.48</v>
+        <v>1038.4</v>
       </c>
       <c r="Z76" s="34" t="n">
-        <v>-793.28</v>
+        <v>7239.35</v>
       </c>
       <c r="AA76" s="18" t="n">
-        <v>1716.66</v>
+        <v>1585.4</v>
       </c>
       <c r="AB76" s="19" t="n">
-        <v>-3594</v>
+        <v>7225.51</v>
       </c>
       <c r="AC76" s="10" t="n"/>
       <c r="AD76" s="10" t="n"/>
@@ -16364,77 +16302,79 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>이자지급(CF)</t>
+          <t>재무활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E77" s="18" t="n">
-        <v>-5.23</v>
+        <v>293.26</v>
       </c>
       <c r="F77" s="9" t="n"/>
       <c r="G77" s="18" t="n">
-        <v>-4.49</v>
+        <v>-53.22</v>
       </c>
       <c r="H77" s="18" t="n">
-        <v>4.49</v>
+        <v>1885.67</v>
       </c>
       <c r="I77" s="18" t="n">
-        <v>-12.57</v>
+        <v>54.81</v>
       </c>
       <c r="J77" s="18" t="n">
-        <v>-3.59</v>
+        <v>37.69</v>
       </c>
       <c r="K77" s="34" t="n">
-        <v>-16.16</v>
+        <v>1924.95</v>
       </c>
       <c r="L77" s="18" t="n">
-        <v>-3.28</v>
+        <v>-52.06</v>
       </c>
       <c r="M77" s="18" t="n">
-        <v>-2.99</v>
+        <v>1631.23</v>
       </c>
       <c r="N77" s="18" t="n">
-        <v>-2.7</v>
+        <v>1437.69</v>
       </c>
       <c r="O77" s="18" t="n">
-        <v>-2.41</v>
+        <v>709.11</v>
       </c>
       <c r="P77" s="34" t="n">
-        <v>-11.38</v>
+        <v>3725.97</v>
       </c>
       <c r="Q77" s="18" t="n">
-        <v>-2.11</v>
+        <v>-34.18</v>
       </c>
       <c r="R77" s="18" t="n">
-        <v>-1.82</v>
+        <v>4797.94</v>
       </c>
       <c r="S77" s="18" t="n">
-        <v>-1.52</v>
+        <v>538.13</v>
       </c>
       <c r="T77" s="18" t="n">
-        <v>-3.41</v>
+        <v>2028.97</v>
       </c>
       <c r="U77" s="34" t="n">
-        <v>-8.859999999999999</v>
+        <v>7330.86</v>
       </c>
       <c r="V77" s="18" t="n">
-        <v>-1.44</v>
+        <v>2595.38</v>
       </c>
       <c r="W77" s="18" t="n">
-        <v>1.44</v>
+        <v>-3627.7</v>
       </c>
       <c r="X77" s="18" t="n">
-        <v>0</v>
+        <v>6048.52</v>
       </c>
       <c r="Y77" s="18" t="n">
-        <v>0</v>
+        <v>-5809.48</v>
       </c>
       <c r="Z77" s="34" t="n">
-        <v>0</v>
+        <v>-793.28</v>
       </c>
       <c r="AA77" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB77" s="5" t="n"/>
+        <v>1716.66</v>
+      </c>
+      <c r="AB77" s="19" t="n">
+        <v>-3594</v>
+      </c>
       <c r="AC77" s="10" t="n"/>
       <c r="AD77" s="10" t="n"/>
       <c r="AE77" s="11" t="n"/>
@@ -16455,79 +16395,77 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
+          <t>이자지급(CF)</t>
         </is>
       </c>
       <c r="E78" s="18" t="n">
-        <v>53.91</v>
+        <v>-5.23</v>
       </c>
       <c r="F78" s="9" t="n"/>
       <c r="G78" s="18" t="n">
-        <v>48.72</v>
+        <v>-4.49</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>49</v>
+        <v>4.49</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>49.3</v>
+        <v>-12.57</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>50.22</v>
+        <v>-3.59</v>
       </c>
       <c r="K78" s="34" t="n">
-        <v>197.24</v>
+        <v>-16.16</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>48.78</v>
+        <v>-3.28</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>49.1</v>
+        <v>-2.99</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>49.42</v>
+        <v>-2.7</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>49.74</v>
+        <v>-2.41</v>
       </c>
       <c r="P78" s="34" t="n">
-        <v>197.04</v>
+        <v>-11.38</v>
       </c>
       <c r="Q78" s="18" t="n">
-        <v>50.07</v>
+        <v>-2.11</v>
       </c>
       <c r="R78" s="18" t="n">
-        <v>50.39</v>
+        <v>-1.82</v>
       </c>
       <c r="S78" s="18" t="n">
-        <v>50.73</v>
+        <v>-1.52</v>
       </c>
       <c r="T78" s="18" t="n">
-        <v>75.12</v>
+        <v>-3.41</v>
       </c>
       <c r="U78" s="34" t="n">
-        <v>226.31</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="V78" s="18" t="n">
-        <v>46.17</v>
+        <v>-1.44</v>
       </c>
       <c r="W78" s="18" t="n">
-        <v>68.73999999999999</v>
+        <v>1.44</v>
       </c>
       <c r="X78" s="18" t="n">
-        <v>37.09</v>
+        <v>0</v>
       </c>
       <c r="Y78" s="18" t="n">
-        <v>108.83</v>
+        <v>0</v>
       </c>
       <c r="Z78" s="34" t="n">
-        <v>260.83</v>
+        <v>0</v>
       </c>
       <c r="AA78" s="18" t="n">
-        <v>53.34</v>
-      </c>
-      <c r="AB78" s="19" t="n">
-        <v>84.68000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB78" s="5" t="n"/>
       <c r="AC78" s="10" t="n"/>
       <c r="AD78" s="10" t="n"/>
       <c r="AE78" s="11" t="n"/>
@@ -16548,36 +16486,79 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>배당금지급</t>
+          <t>리스부채의상환</t>
         </is>
       </c>
       <c r="E79" s="18" t="n">
-        <v>0</v>
+        <v>53.91</v>
       </c>
       <c r="F79" s="9" t="n"/>
+      <c r="G79" s="18" t="n">
+        <v>48.72</v>
+      </c>
+      <c r="H79" s="18" t="n">
+        <v>49</v>
+      </c>
       <c r="I79" s="18" t="n">
-        <v>0</v>
+        <v>49.3</v>
       </c>
       <c r="J79" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" s="9" t="n"/>
+        <v>50.22</v>
+      </c>
+      <c r="K79" s="34" t="n">
+        <v>197.24</v>
+      </c>
+      <c r="L79" s="18" t="n">
+        <v>48.78</v>
+      </c>
+      <c r="M79" s="18" t="n">
+        <v>49.1</v>
+      </c>
       <c r="N79" s="18" t="n">
-        <v>0</v>
+        <v>49.42</v>
       </c>
       <c r="O79" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" s="9" t="n"/>
-      <c r="U79" s="9" t="n"/>
+        <v>49.74</v>
+      </c>
+      <c r="P79" s="34" t="n">
+        <v>197.04</v>
+      </c>
+      <c r="Q79" s="18" t="n">
+        <v>50.07</v>
+      </c>
+      <c r="R79" s="18" t="n">
+        <v>50.39</v>
+      </c>
+      <c r="S79" s="18" t="n">
+        <v>50.73</v>
+      </c>
+      <c r="T79" s="18" t="n">
+        <v>75.12</v>
+      </c>
+      <c r="U79" s="34" t="n">
+        <v>226.31</v>
+      </c>
+      <c r="V79" s="18" t="n">
+        <v>46.17</v>
+      </c>
+      <c r="W79" s="18" t="n">
+        <v>68.73999999999999</v>
+      </c>
       <c r="X79" s="18" t="n">
-        <v>0</v>
+        <v>37.09</v>
       </c>
       <c r="Y79" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z79" s="9" t="n"/>
-      <c r="AB79" s="5" t="n"/>
+        <v>108.83</v>
+      </c>
+      <c r="Z79" s="34" t="n">
+        <v>260.83</v>
+      </c>
+      <c r="AA79" s="18" t="n">
+        <v>53.34</v>
+      </c>
+      <c r="AB79" s="19" t="n">
+        <v>84.68000000000001</v>
+      </c>
       <c r="AC79" s="10" t="n"/>
       <c r="AD79" s="10" t="n"/>
       <c r="AE79" s="11" t="n"/>
@@ -16598,16 +16579,34 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>자기주식의취득</t>
+          <t>배당금지급</t>
         </is>
       </c>
       <c r="E80" s="18" t="n">
         <v>0</v>
       </c>
       <c r="F80" s="9" t="n"/>
+      <c r="I80" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="K80" s="9" t="n"/>
+      <c r="N80" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="P80" s="9" t="n"/>
       <c r="U80" s="9" t="n"/>
+      <c r="X80" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y80" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="Z80" s="9" t="n"/>
       <c r="AB80" s="5" t="n"/>
       <c r="AC80" s="10" t="n"/>
@@ -16630,79 +16629,18 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>자기주식의취득</t>
         </is>
       </c>
       <c r="E81" s="18" t="n">
-        <v>-10920.66</v>
+        <v>0</v>
       </c>
       <c r="F81" s="9" t="n"/>
-      <c r="G81" s="18" t="n">
-        <v>-11121.84</v>
-      </c>
-      <c r="H81" s="18" t="n">
-        <v>-649.49</v>
-      </c>
-      <c r="I81" s="18" t="n">
-        <v>2507.94</v>
-      </c>
-      <c r="J81" s="18" t="n">
-        <v>-1292.4</v>
-      </c>
-      <c r="K81" s="34" t="n">
-        <v>-10555.79</v>
-      </c>
-      <c r="L81" s="18" t="n">
-        <v>-3661.85</v>
-      </c>
-      <c r="M81" s="18" t="n">
-        <v>7746.88</v>
-      </c>
-      <c r="N81" s="18" t="n">
-        <v>-10010.3</v>
-      </c>
-      <c r="O81" s="18" t="n">
-        <v>17335.9</v>
-      </c>
-      <c r="P81" s="34" t="n">
-        <v>11410.63</v>
-      </c>
-      <c r="Q81" s="18" t="n">
-        <v>-8299.34</v>
-      </c>
-      <c r="R81" s="18" t="n">
-        <v>3072.16</v>
-      </c>
-      <c r="S81" s="18" t="n">
-        <v>1812.24</v>
-      </c>
-      <c r="T81" s="18" t="n">
-        <v>-929.74</v>
-      </c>
-      <c r="U81" s="34" t="n">
-        <v>-4344.68</v>
-      </c>
-      <c r="V81" s="18" t="n">
-        <v>3064.69</v>
-      </c>
-      <c r="W81" s="18" t="n">
-        <v>-2901.93</v>
-      </c>
-      <c r="X81" s="18" t="n">
-        <v>3024.57</v>
-      </c>
-      <c r="Y81" s="18" t="n">
-        <v>5309.75</v>
-      </c>
-      <c r="Z81" s="34" t="n">
-        <v>8497.08</v>
-      </c>
-      <c r="AA81" s="18" t="n">
-        <v>-258.74</v>
-      </c>
-      <c r="AB81" s="19" t="n">
-        <v>1065.06</v>
-      </c>
+      <c r="K81" s="9" t="n"/>
+      <c r="P81" s="9" t="n"/>
+      <c r="U81" s="9" t="n"/>
+      <c r="Z81" s="9" t="n"/>
+      <c r="AB81" s="5" t="n"/>
       <c r="AC81" s="10" t="n"/>
       <c r="AD81" s="10" t="n"/>
       <c r="AE81" s="11" t="n"/>
@@ -16723,33 +16661,33 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>현금및현금성자산의증감</t>
         </is>
       </c>
       <c r="E82" s="18" t="n">
-        <v>-10920.67</v>
+        <v>-10920.66</v>
       </c>
       <c r="F82" s="9" t="n"/>
       <c r="G82" s="18" t="n">
-        <v>27317.76</v>
+        <v>-11121.84</v>
       </c>
       <c r="H82" s="18" t="n">
         <v>-649.49</v>
       </c>
       <c r="I82" s="18" t="n">
-        <v>2507.95</v>
+        <v>2507.94</v>
       </c>
       <c r="J82" s="18" t="n">
         <v>-1292.4</v>
       </c>
       <c r="K82" s="34" t="n">
-        <v>27883.82</v>
+        <v>-10555.79</v>
       </c>
       <c r="L82" s="18" t="n">
-        <v>24221.97</v>
+        <v>-3661.85</v>
       </c>
       <c r="M82" s="18" t="n">
-        <v>7746.87</v>
+        <v>7746.88</v>
       </c>
       <c r="N82" s="18" t="n">
         <v>-10010.3</v>
@@ -16758,40 +16696,40 @@
         <v>17335.9</v>
       </c>
       <c r="P82" s="34" t="n">
-        <v>39294.44</v>
+        <v>11410.63</v>
       </c>
       <c r="Q82" s="18" t="n">
-        <v>30995.1</v>
+        <v>-8299.34</v>
       </c>
       <c r="R82" s="18" t="n">
-        <v>3072.17</v>
+        <v>3072.16</v>
       </c>
       <c r="S82" s="18" t="n">
-        <v>1812.23</v>
+        <v>1812.24</v>
       </c>
       <c r="T82" s="18" t="n">
         <v>-929.74</v>
       </c>
       <c r="U82" s="34" t="n">
-        <v>34949.76</v>
+        <v>-4344.68</v>
       </c>
       <c r="V82" s="18" t="n">
-        <v>38014.46</v>
+        <v>3064.69</v>
       </c>
       <c r="W82" s="18" t="n">
-        <v>-2901.94</v>
+        <v>-2901.93</v>
       </c>
       <c r="X82" s="18" t="n">
-        <v>3024.58</v>
+        <v>3024.57</v>
       </c>
       <c r="Y82" s="18" t="n">
-        <v>5309.74</v>
+        <v>5309.75</v>
       </c>
       <c r="Z82" s="34" t="n">
-        <v>43446.84</v>
+        <v>8497.08</v>
       </c>
       <c r="AA82" s="18" t="n">
-        <v>43188.11</v>
+        <v>-258.74</v>
       </c>
       <c r="AB82" s="19" t="n">
         <v>1065.06</v>
@@ -16816,50 +16754,78 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
-        </is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="E83" s="18" t="n">
+        <v>-10920.67</v>
       </c>
       <c r="F83" s="9" t="n"/>
-      <c r="K83" s="9" t="n"/>
+      <c r="G83" s="18" t="n">
+        <v>27317.76</v>
+      </c>
+      <c r="H83" s="18" t="n">
+        <v>-649.49</v>
+      </c>
+      <c r="I83" s="18" t="n">
+        <v>2507.95</v>
+      </c>
+      <c r="J83" s="18" t="n">
+        <v>-1292.4</v>
+      </c>
+      <c r="K83" s="34" t="n">
+        <v>27883.82</v>
+      </c>
+      <c r="L83" s="18" t="n">
+        <v>24221.97</v>
+      </c>
+      <c r="M83" s="18" t="n">
+        <v>7746.87</v>
+      </c>
+      <c r="N83" s="18" t="n">
+        <v>-10010.3</v>
+      </c>
       <c r="O83" s="18" t="n">
-        <v>819.29</v>
-      </c>
-      <c r="P83" s="9" t="n"/>
+        <v>17335.9</v>
+      </c>
+      <c r="P83" s="34" t="n">
+        <v>39294.44</v>
+      </c>
       <c r="Q83" s="18" t="n">
-        <v>1038.7</v>
+        <v>30995.1</v>
       </c>
       <c r="R83" s="18" t="n">
-        <v>795</v>
+        <v>3072.17</v>
       </c>
       <c r="S83" s="18" t="n">
-        <v>846.61</v>
+        <v>1812.23</v>
       </c>
       <c r="T83" s="18" t="n">
-        <v>881.49</v>
+        <v>-929.74</v>
       </c>
       <c r="U83" s="34" t="n">
-        <v>3561.8</v>
+        <v>34949.76</v>
       </c>
       <c r="V83" s="18" t="n">
-        <v>549.9</v>
+        <v>38014.46</v>
       </c>
       <c r="W83" s="18" t="n">
-        <v>892.4400000000001</v>
+        <v>-2901.94</v>
       </c>
       <c r="X83" s="18" t="n">
-        <v>822.8</v>
+        <v>3024.58</v>
       </c>
       <c r="Y83" s="18" t="n">
-        <v>612.28</v>
+        <v>5309.74</v>
       </c>
       <c r="Z83" s="34" t="n">
-        <v>2877.42</v>
+        <v>43446.84</v>
       </c>
       <c r="AA83" s="18" t="n">
-        <v>642.38</v>
+        <v>43188.11</v>
       </c>
       <c r="AB83" s="19" t="n">
-        <v>849.4400000000001</v>
+        <v>1065.06</v>
       </c>
       <c r="AC83" s="10" t="n"/>
       <c r="AD83" s="10" t="n"/>
@@ -16874,6 +16840,71 @@
       <c r="AM83" s="10" t="n"/>
       <c r="AN83" s="10" t="n"/>
       <c r="AO83" s="11" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>이자수취(CF)</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="n"/>
+      <c r="K84" s="9" t="n"/>
+      <c r="O84" s="18" t="n">
+        <v>819.29</v>
+      </c>
+      <c r="P84" s="9" t="n"/>
+      <c r="Q84" s="18" t="n">
+        <v>1038.7</v>
+      </c>
+      <c r="R84" s="18" t="n">
+        <v>795</v>
+      </c>
+      <c r="S84" s="18" t="n">
+        <v>846.61</v>
+      </c>
+      <c r="T84" s="18" t="n">
+        <v>881.49</v>
+      </c>
+      <c r="U84" s="34" t="n">
+        <v>3561.8</v>
+      </c>
+      <c r="V84" s="18" t="n">
+        <v>549.9</v>
+      </c>
+      <c r="W84" s="18" t="n">
+        <v>892.4400000000001</v>
+      </c>
+      <c r="X84" s="18" t="n">
+        <v>822.8</v>
+      </c>
+      <c r="Y84" s="18" t="n">
+        <v>612.28</v>
+      </c>
+      <c r="Z84" s="34" t="n">
+        <v>2877.42</v>
+      </c>
+      <c r="AA84" s="18" t="n">
+        <v>642.38</v>
+      </c>
+      <c r="AB84" s="19" t="n">
+        <v>849.4400000000001</v>
+      </c>
+      <c r="AC84" s="10" t="n"/>
+      <c r="AD84" s="10" t="n"/>
+      <c r="AE84" s="11" t="n"/>
+      <c r="AF84" s="10" t="n"/>
+      <c r="AG84" s="10" t="n"/>
+      <c r="AH84" s="10" t="n"/>
+      <c r="AI84" s="10" t="n"/>
+      <c r="AJ84" s="11" t="n"/>
+      <c r="AK84" s="10" t="n"/>
+      <c r="AL84" s="10" t="n"/>
+      <c r="AM84" s="10" t="n"/>
+      <c r="AN84" s="10" t="n"/>
+      <c r="AO84" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17134,7 +17165,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/108380_model.xlsx
+++ b/argus/kship/models/108380_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -3829,7 +3829,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -4700,35 +4700,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4819,35 +4819,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4938,35 +4938,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5057,35 +5057,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5176,35 +5176,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5295,35 +5295,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5414,35 +5414,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5533,35 +5533,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5668,7 +5668,7 @@
         <v>18520</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>18770</v>
+        <v>18760</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5759,7 +5759,7 @@
         <v>19600</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>18830</v>
+        <v>18970</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -5941,7 +5941,7 @@
         <v>17674.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>18640</v>
+        <v>18680</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8257,7 +8257,7 @@
         </is>
       </c>
       <c r="D39" s="34" t="n">
-        <v>18770</v>
+        <v>18760</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
       </c>
       <c r="D40" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -8571,7 +8571,7 @@
         </is>
       </c>
       <c r="D47" s="36" t="n">
-        <v>0.06922589795370447</v>
+        <v>0.06922589795370446</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.08495179126460657</v>
+        <v>0.08495179126460656</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29141,7 +29141,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33890,7 +33890,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/108380_model.xlsx
+++ b/argus/kship/models/108380_model.xlsx
@@ -3829,7 +3829,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -4700,35 +4700,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4819,35 +4819,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4938,35 +4938,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5057,35 +5057,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5176,35 +5176,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5295,35 +5295,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5414,35 +5414,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5533,35 +5533,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5668,7 +5668,7 @@
         <v>18520</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>18760</v>
+        <v>18180</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5850,7 +5850,7 @@
         <v>14000</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>18300</v>
+        <v>18080</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5941,7 +5941,7 @@
         <v>17674.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>18680</v>
+        <v>18590</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8257,11 +8257,11 @@
         </is>
       </c>
       <c r="D39" s="34" t="n">
-        <v>18760</v>
+        <v>18180</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 18,640원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 18,750원)</t>
         </is>
       </c>
       <c r="F39" s="9" t="n"/>
@@ -8297,7 +8297,7 @@
       </c>
       <c r="D40" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29141,7 +29141,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33890,7 +33890,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35898,7 +35898,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.99</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="32">
@@ -35908,7 +35908,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/108380_model.xlsx
+++ b/argus/kship/models/108380_model.xlsx
@@ -3829,7 +3829,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -9123,7 +9123,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/108380_model.xlsx
+++ b/argus/kship/models/108380_model.xlsx
@@ -4700,35 +4700,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4819,35 +4819,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4938,35 +4938,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5057,35 +5057,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5176,35 +5176,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5295,35 +5295,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5414,35 +5414,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5533,35 +5533,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5668,7 +5668,7 @@
         <v>18520</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>18180</v>
+        <v>17780</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5850,7 +5850,7 @@
         <v>14000</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>18080</v>
+        <v>17630</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5941,7 +5941,7 @@
         <v>17674.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>18590</v>
+        <v>18418</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8257,11 +8257,11 @@
         </is>
       </c>
       <c r="D39" s="34" t="n">
-        <v>18180</v>
+        <v>17780</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 18,750원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 18,790원)</t>
         </is>
       </c>
       <c r="F39" s="9" t="n"/>
@@ -8297,7 +8297,7 @@
       </c>
       <c r="D40" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -29141,7 +29141,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33890,7 +33890,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35898,7 +35898,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.8</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="32">
@@ -35908,7 +35908,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/108380_model.xlsx
+++ b/argus/kship/models/108380_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -1824,121 +1824,121 @@
     </comment>
     <comment ref="AC11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 565억 × 8.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 565억 × 5.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AD11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 635억 × 8.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 631억 × 5.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 701억 × 8.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 693억 × 5.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 762억 × 8.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 750억 × 5.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 826억 × 8.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 810억 × 5.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 904억 × 8.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 882억 × 5.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 977억 × 8.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 950억 × 5.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 1046억 × 8.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 1012억 × 5.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 1119억 × 8.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 1078억 × 5.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 1203억 × 8.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 1155억 × 5.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AC12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 565억 × 8.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 565억 × 5.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AD12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 635억 × 8.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 631억 × 5.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 701억 × 8.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 693억 × 5.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 762억 × 8.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 750억 × 5.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 826억 × 8.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 810억 × 5.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 904억 × 8.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 882억 × 5.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 977억 × 8.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 950억 × 5.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1046억 × 8.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 1012억 × 5.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1119억 × 8.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 1078억 × 5.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1203억 × 8.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 1155억 × 5.50%(주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3829,7 +3829,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>· 이자율 자산 8.50% / 부채 — — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.085, None] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)", "debt": null}</t>
+          <t>· 이자율 자산 5.50% / 부채 — — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.055, None] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2024Q1~2026Q2)", "debt": null}</t>
         </is>
       </c>
     </row>
@@ -4030,7 +4030,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 지배주주순이익 face 누락 분기는 당기순이익 − 비지배 로 파생: 2026Q2 / 매출 드라이버 폴백(고객 조선사 연결 없음(suppliers.json)): 전년동기 × (1+g) 추세</t>
+          <t>한계: 모델 quality.warnings — 지배주주순이익 face 누락 분기는 당기순이익 − 비지배 로 파생: 2026Q2 / 매출 드라이버 폴백(고객 조선사 연결 없음(suppliers.json)): 전년동기 × (1+g) 추세 / 금융손익 실적→추정 단절: 최근 4분기 실적 +19/-0/+27/+18(중위 +19억) → 추정 2026Q3 +8억(차 -11억, -58%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -7309,36 +7309,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>0.004656524</v>
+        <v>-0.004736154</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>-0.005766602</v>
+        <v>0.003494381</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>0.001829938</v>
+        <v>0.007968543999999999</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>18.585084442</v>
+        <v>18.581169199</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>-0.001773629</v>
+        <v>0.00266492</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>-0.0029393</v>
+        <v>-0.006976671</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>-0.001285148</v>
+        <v>0.004632015</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>18.579062775</v>
+        <v>18.578053481</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>0.005414327</v>
+        <v>0.008174249</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>0.003173004</v>
+        <v>0.003590014</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7437,36 +7437,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.004656524</v>
+        <v>-0.004736154</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.005766602</v>
+        <v>0.003494381</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.001829938</v>
+        <v>0.007968543999999999</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>18.585084442</v>
+        <v>18.581169199</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.001773629</v>
+        <v>0.00266492</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.0029393</v>
+        <v>-0.006976671</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-0.001285148</v>
+        <v>0.004632015</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>18.579062775</v>
+        <v>18.578053481</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.005414327</v>
+        <v>0.008174249</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>0.003173004</v>
+        <v>0.003590014</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7565,36 +7565,36 @@
         <v/>
       </c>
       <c r="AC31" s="24" t="n">
-        <v>0.123458689</v>
+        <v>0.117388044</v>
       </c>
       <c r="AD31" s="24" t="n">
-        <v>0.103832884</v>
+        <v>0.098235499</v>
       </c>
       <c r="AE31" s="25" t="n"/>
       <c r="AF31" s="24" t="n">
-        <v>0.08735799499999999</v>
+        <v>0.082035306</v>
       </c>
       <c r="AG31" s="24" t="n">
-        <v>0.084093504</v>
+        <v>0.079054702</v>
       </c>
       <c r="AH31" s="24" t="n">
-        <v>0.09391496000000001</v>
+        <v>0.089395343</v>
       </c>
       <c r="AI31" s="24" t="n">
-        <v>0.081436145</v>
+        <v>0.076945755</v>
       </c>
       <c r="AJ31" s="25" t="n"/>
       <c r="AK31" s="24" t="n">
-        <v>0.07032985</v>
+        <v>0.065783655</v>
       </c>
       <c r="AL31" s="24" t="n">
-        <v>0.06958109799999999</v>
+        <v>0.065250035</v>
       </c>
       <c r="AM31" s="24" t="n">
-        <v>0.075406758</v>
+        <v>0.07151004800000001</v>
       </c>
       <c r="AN31" s="24" t="n">
-        <v>0.066785818</v>
+        <v>0.0627564</v>
       </c>
       <c r="AO31" s="25" t="n"/>
     </row>
@@ -8532,7 +8532,7 @@
         </is>
       </c>
       <c r="D46" s="36" t="n">
-        <v>0.1895965700707681</v>
+        <v>0.1896133923212023</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -8571,7 +8571,7 @@
         </is>
       </c>
       <c r="D47" s="36" t="n">
-        <v>0.06922589795370446</v>
+        <v>0.06922589795370447</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -8649,11 +8649,11 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.08495179126460656</v>
+        <v>0.05500607956717433</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>연결 — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.085)</t>
+          <t>연결 — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.055)</t>
         </is>
       </c>
       <c r="F49" s="9" t="n"/>
@@ -9123,7 +9123,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -9726,80 +9726,80 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>기타유동금융자산</t>
+          <t>단기투자자산(공정가치)</t>
         </is>
       </c>
       <c r="E8" s="18" t="n">
-        <v>9935.309999999999</v>
+        <v>4185.91</v>
       </c>
       <c r="F8" s="37" t="n">
-        <v>9935.309999999999</v>
+        <v>4185.91</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>27061.86</v>
+        <v>4275.47</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>27150.2</v>
+        <v>6559.14</v>
       </c>
       <c r="I8" s="18" t="n">
-        <v>27220.74</v>
+        <v>7250.59</v>
       </c>
       <c r="J8" s="18" t="n">
-        <v>29539.42</v>
+        <v>10352.3</v>
       </c>
       <c r="K8" s="37" t="n">
-        <v>29539.42</v>
+        <v>10352.3</v>
       </c>
       <c r="L8" s="18" t="n">
-        <v>29532.67</v>
+        <v>10706.2</v>
       </c>
       <c r="M8" s="18" t="n">
-        <v>29207.07</v>
+        <v>10835</v>
       </c>
       <c r="N8" s="18" t="n">
-        <v>30376.83</v>
+        <v>8371.18</v>
       </c>
       <c r="O8" s="18" t="n">
-        <v>30183</v>
+        <v>4097.66</v>
       </c>
       <c r="P8" s="37" t="n">
-        <v>30183</v>
+        <v>4097.66</v>
       </c>
       <c r="Q8" s="18" t="n">
-        <v>32340.55</v>
+        <v>4281.83</v>
       </c>
       <c r="R8" s="18" t="n">
-        <v>32591.88</v>
+        <v>4466.09</v>
       </c>
       <c r="S8" s="18" t="n">
-        <v>32770.64</v>
+        <v>4288.21</v>
       </c>
       <c r="T8" s="18" t="n">
-        <v>31990.05</v>
+        <v>12155.52</v>
       </c>
       <c r="U8" s="37" t="n">
-        <v>31990.05</v>
+        <v>12155.52</v>
       </c>
       <c r="V8" s="18" t="n">
-        <v>31173.51</v>
+        <v>24521.68</v>
       </c>
       <c r="W8" s="18" t="n">
-        <v>31662.29</v>
+        <v>38933.25</v>
       </c>
       <c r="X8" s="18" t="n">
-        <v>36655.54</v>
+        <v>34460.12</v>
       </c>
       <c r="Y8" s="18" t="n">
-        <v>36809.09</v>
+        <v>34769.73</v>
       </c>
       <c r="Z8" s="37" t="n">
-        <v>36809.09</v>
+        <v>34769.73</v>
       </c>
       <c r="AA8" s="18" t="n">
-        <v>36933.97</v>
+        <v>40501.05</v>
       </c>
       <c r="AB8" s="19" t="n">
-        <v>38343</v>
+        <v>30461.19</v>
       </c>
       <c r="AC8" s="10" t="n"/>
       <c r="AD8" s="10" t="n"/>
@@ -9821,79 +9821,81 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>당기법인세자산(선급법인세)</t>
+          <t>기타유동금융자산</t>
         </is>
       </c>
       <c r="E9" s="18" t="n">
-        <v>567.6</v>
+        <v>9935.309999999999</v>
       </c>
       <c r="F9" s="37" t="n">
-        <v>567.6</v>
+        <v>9935.309999999999</v>
       </c>
       <c r="G9" s="18" t="n">
-        <v>568.04</v>
+        <v>27061.86</v>
       </c>
       <c r="H9" s="18" t="n">
-        <v>98.47</v>
+        <v>27150.2</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>157.51</v>
+        <v>27220.74</v>
       </c>
       <c r="J9" s="18" t="n">
-        <v>250.06</v>
+        <v>29539.42</v>
       </c>
       <c r="K9" s="37" t="n">
-        <v>250.06</v>
+        <v>29539.42</v>
       </c>
       <c r="L9" s="18" t="n">
-        <v>412.2</v>
+        <v>29532.67</v>
       </c>
       <c r="M9" s="18" t="n">
-        <v>283.51</v>
+        <v>29207.07</v>
       </c>
       <c r="N9" s="18" t="n">
-        <v>369.61</v>
+        <v>30376.83</v>
       </c>
       <c r="O9" s="18" t="n">
-        <v>24.3</v>
+        <v>30183</v>
       </c>
       <c r="P9" s="37" t="n">
-        <v>24.3</v>
+        <v>30183</v>
       </c>
       <c r="Q9" s="18" t="n">
-        <v>30.46</v>
+        <v>32340.55</v>
       </c>
       <c r="R9" s="18" t="n">
-        <v>0</v>
+        <v>32591.88</v>
       </c>
       <c r="S9" s="18" t="n">
-        <v>26.92</v>
+        <v>32770.64</v>
       </c>
       <c r="T9" s="18" t="n">
-        <v>41.98</v>
+        <v>31990.05</v>
       </c>
       <c r="U9" s="37" t="n">
-        <v>41.98</v>
+        <v>31990.05</v>
       </c>
       <c r="V9" s="18" t="n">
-        <v>56.11</v>
+        <v>31173.51</v>
       </c>
       <c r="W9" s="18" t="n">
-        <v>17.9</v>
+        <v>31662.29</v>
       </c>
       <c r="X9" s="18" t="n">
-        <v>0</v>
+        <v>36655.54</v>
       </c>
       <c r="Y9" s="18" t="n">
-        <v>0</v>
+        <v>36809.09</v>
       </c>
       <c r="Z9" s="37" t="n">
-        <v>0</v>
+        <v>36809.09</v>
       </c>
       <c r="AA9" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="5" t="n"/>
+        <v>36933.97</v>
+      </c>
+      <c r="AB9" s="19" t="n">
+        <v>38343</v>
+      </c>
       <c r="AC9" s="10" t="n"/>
       <c r="AD9" s="10" t="n"/>
       <c r="AE9" s="11" t="n"/>
@@ -9914,81 +9916,79 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>재고자산</t>
+          <t>당기법인세자산(선급법인세)</t>
         </is>
       </c>
       <c r="E10" s="18" t="n">
-        <v>29020.6</v>
+        <v>567.6</v>
       </c>
       <c r="F10" s="37" t="n">
-        <v>29020.6</v>
+        <v>567.6</v>
       </c>
       <c r="G10" s="18" t="n">
-        <v>27948.39</v>
+        <v>568.04</v>
       </c>
       <c r="H10" s="18" t="n">
-        <v>28352.22</v>
+        <v>98.47</v>
       </c>
       <c r="I10" s="18" t="n">
-        <v>31545.25</v>
+        <v>157.51</v>
       </c>
       <c r="J10" s="18" t="n">
-        <v>25689.56</v>
+        <v>250.06</v>
       </c>
       <c r="K10" s="37" t="n">
-        <v>25689.56</v>
+        <v>250.06</v>
       </c>
       <c r="L10" s="18" t="n">
-        <v>29376.08</v>
+        <v>412.2</v>
       </c>
       <c r="M10" s="18" t="n">
-        <v>34923.37</v>
+        <v>283.51</v>
       </c>
       <c r="N10" s="18" t="n">
-        <v>38119.12</v>
+        <v>369.61</v>
       </c>
       <c r="O10" s="18" t="n">
-        <v>38466.57</v>
+        <v>24.3</v>
       </c>
       <c r="P10" s="37" t="n">
-        <v>38466.57</v>
+        <v>24.3</v>
       </c>
       <c r="Q10" s="18" t="n">
-        <v>44248.95</v>
+        <v>30.46</v>
       </c>
       <c r="R10" s="18" t="n">
-        <v>42418.41</v>
+        <v>0</v>
       </c>
       <c r="S10" s="18" t="n">
-        <v>42899.8</v>
+        <v>26.92</v>
       </c>
       <c r="T10" s="18" t="n">
-        <v>38204.64</v>
+        <v>41.98</v>
       </c>
       <c r="U10" s="37" t="n">
-        <v>38204.64</v>
+        <v>41.98</v>
       </c>
       <c r="V10" s="18" t="n">
-        <v>41740.88</v>
+        <v>56.11</v>
       </c>
       <c r="W10" s="18" t="n">
-        <v>42997.2</v>
+        <v>17.9</v>
       </c>
       <c r="X10" s="18" t="n">
-        <v>39982.46</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="18" t="n">
-        <v>35932.39</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="37" t="n">
-        <v>35932.39</v>
+        <v>0</v>
       </c>
       <c r="AA10" s="18" t="n">
-        <v>48678.08</v>
-      </c>
-      <c r="AB10" s="19" t="n">
-        <v>46027.62</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB10" s="5" t="n"/>
       <c r="AC10" s="10" t="n"/>
       <c r="AD10" s="10" t="n"/>
       <c r="AE10" s="11" t="n"/>
@@ -10009,28 +10009,81 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>매각예정비유동자산및처분자산</t>
+          <t>재고자산</t>
         </is>
       </c>
       <c r="E11" s="18" t="n">
-        <v>0</v>
+        <v>29020.6</v>
       </c>
       <c r="F11" s="37" t="n">
-        <v>0</v>
+        <v>29020.6</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>27948.39</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>28352.22</v>
+      </c>
+      <c r="I11" s="18" t="n">
+        <v>31545.25</v>
       </c>
       <c r="J11" s="18" t="n">
-        <v>0</v>
+        <v>25689.56</v>
       </c>
       <c r="K11" s="37" t="n">
-        <v>0</v>
+        <v>25689.56</v>
       </c>
       <c r="L11" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="9" t="n"/>
-      <c r="U11" s="9" t="n"/>
-      <c r="Z11" s="9" t="n"/>
-      <c r="AB11" s="5" t="n"/>
+        <v>29376.08</v>
+      </c>
+      <c r="M11" s="18" t="n">
+        <v>34923.37</v>
+      </c>
+      <c r="N11" s="18" t="n">
+        <v>38119.12</v>
+      </c>
+      <c r="O11" s="18" t="n">
+        <v>38466.57</v>
+      </c>
+      <c r="P11" s="37" t="n">
+        <v>38466.57</v>
+      </c>
+      <c r="Q11" s="18" t="n">
+        <v>44248.95</v>
+      </c>
+      <c r="R11" s="18" t="n">
+        <v>42418.41</v>
+      </c>
+      <c r="S11" s="18" t="n">
+        <v>42899.8</v>
+      </c>
+      <c r="T11" s="18" t="n">
+        <v>38204.64</v>
+      </c>
+      <c r="U11" s="37" t="n">
+        <v>38204.64</v>
+      </c>
+      <c r="V11" s="18" t="n">
+        <v>41740.88</v>
+      </c>
+      <c r="W11" s="18" t="n">
+        <v>42997.2</v>
+      </c>
+      <c r="X11" s="18" t="n">
+        <v>39982.46</v>
+      </c>
+      <c r="Y11" s="18" t="n">
+        <v>35932.39</v>
+      </c>
+      <c r="Z11" s="37" t="n">
+        <v>35932.39</v>
+      </c>
+      <c r="AA11" s="18" t="n">
+        <v>48678.08</v>
+      </c>
+      <c r="AB11" s="19" t="n">
+        <v>46027.62</v>
+      </c>
       <c r="AC11" s="10" t="n"/>
       <c r="AD11" s="10" t="n"/>
       <c r="AE11" s="11" t="n"/>
@@ -10051,81 +10104,28 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>비유동자산</t>
+          <t>매각예정비유동자산및처분자산</t>
         </is>
       </c>
       <c r="E12" s="18" t="n">
-        <v>145340.64</v>
+        <v>0</v>
       </c>
       <c r="F12" s="37" t="n">
-        <v>145340.64</v>
-      </c>
-      <c r="G12" s="18" t="n">
-        <v>135820.12</v>
-      </c>
-      <c r="H12" s="18" t="n">
-        <v>135195.14</v>
-      </c>
-      <c r="I12" s="18" t="n">
-        <v>134729.92</v>
+        <v>0</v>
       </c>
       <c r="J12" s="18" t="n">
-        <v>133915.81</v>
+        <v>0</v>
       </c>
       <c r="K12" s="37" t="n">
-        <v>133915.81</v>
+        <v>0</v>
       </c>
       <c r="L12" s="18" t="n">
-        <v>134063.15</v>
-      </c>
-      <c r="M12" s="18" t="n">
-        <v>138247.38</v>
-      </c>
-      <c r="N12" s="18" t="n">
-        <v>141884.87</v>
-      </c>
-      <c r="O12" s="18" t="n">
-        <v>145756.43</v>
-      </c>
-      <c r="P12" s="37" t="n">
-        <v>145756.43</v>
-      </c>
-      <c r="Q12" s="18" t="n">
-        <v>144952.59</v>
-      </c>
-      <c r="R12" s="18" t="n">
-        <v>147464.64</v>
-      </c>
-      <c r="S12" s="18" t="n">
-        <v>145947.16</v>
-      </c>
-      <c r="T12" s="18" t="n">
-        <v>140866.02</v>
-      </c>
-      <c r="U12" s="37" t="n">
-        <v>140866.02</v>
-      </c>
-      <c r="V12" s="18" t="n">
-        <v>126986.11</v>
-      </c>
-      <c r="W12" s="18" t="n">
-        <v>115327.82</v>
-      </c>
-      <c r="X12" s="18" t="n">
-        <v>115610.24</v>
-      </c>
-      <c r="Y12" s="18" t="n">
-        <v>114680.87</v>
-      </c>
-      <c r="Z12" s="37" t="n">
-        <v>114680.87</v>
-      </c>
-      <c r="AA12" s="18" t="n">
-        <v>109014.32</v>
-      </c>
-      <c r="AB12" s="19" t="n">
-        <v>121134.94</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P12" s="9" t="n"/>
+      <c r="U12" s="9" t="n"/>
+      <c r="Z12" s="9" t="n"/>
+      <c r="AB12" s="5" t="n"/>
       <c r="AC12" s="10" t="n"/>
       <c r="AD12" s="10" t="n"/>
       <c r="AE12" s="11" t="n"/>
@@ -10146,80 +10146,80 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>유형자산</t>
+          <t>비유동자산</t>
         </is>
       </c>
       <c r="E13" s="18" t="n">
-        <v>72261.42</v>
+        <v>145340.64</v>
       </c>
       <c r="F13" s="37" t="n">
-        <v>72261.42</v>
+        <v>145340.64</v>
       </c>
       <c r="G13" s="18" t="n">
-        <v>76101.88</v>
+        <v>135820.12</v>
       </c>
       <c r="H13" s="18" t="n">
-        <v>76939.60000000001</v>
+        <v>135195.14</v>
       </c>
       <c r="I13" s="18" t="n">
-        <v>76874.77</v>
+        <v>134729.92</v>
       </c>
       <c r="J13" s="18" t="n">
-        <v>76491.86</v>
+        <v>133915.81</v>
       </c>
       <c r="K13" s="37" t="n">
-        <v>76491.86</v>
+        <v>133915.81</v>
       </c>
       <c r="L13" s="18" t="n">
-        <v>75953.3</v>
+        <v>134063.15</v>
       </c>
       <c r="M13" s="18" t="n">
-        <v>79693.95</v>
+        <v>138247.38</v>
       </c>
       <c r="N13" s="18" t="n">
-        <v>81650.53999999999</v>
+        <v>141884.87</v>
       </c>
       <c r="O13" s="18" t="n">
-        <v>83082.81</v>
+        <v>145756.43</v>
       </c>
       <c r="P13" s="37" t="n">
-        <v>83082.81</v>
+        <v>145756.43</v>
       </c>
       <c r="Q13" s="18" t="n">
-        <v>82231.88</v>
+        <v>144952.59</v>
       </c>
       <c r="R13" s="18" t="n">
-        <v>83275.2</v>
+        <v>147464.64</v>
       </c>
       <c r="S13" s="18" t="n">
-        <v>82602.88</v>
+        <v>145947.16</v>
       </c>
       <c r="T13" s="18" t="n">
-        <v>79646.8</v>
+        <v>140866.02</v>
       </c>
       <c r="U13" s="37" t="n">
-        <v>79646.8</v>
+        <v>140866.02</v>
       </c>
       <c r="V13" s="18" t="n">
-        <v>80262.64999999999</v>
+        <v>126986.11</v>
       </c>
       <c r="W13" s="18" t="n">
-        <v>82623.92999999999</v>
+        <v>115327.82</v>
       </c>
       <c r="X13" s="18" t="n">
-        <v>72019.5</v>
+        <v>115610.24</v>
       </c>
       <c r="Y13" s="18" t="n">
-        <v>79391.81</v>
+        <v>114680.87</v>
       </c>
       <c r="Z13" s="37" t="n">
-        <v>79391.81</v>
+        <v>114680.87</v>
       </c>
       <c r="AA13" s="18" t="n">
-        <v>79496.72</v>
+        <v>109014.32</v>
       </c>
       <c r="AB13" s="19" t="n">
-        <v>90293.77</v>
+        <v>121134.94</v>
       </c>
       <c r="AC13" s="10" t="n"/>
       <c r="AD13" s="10" t="n"/>
@@ -10241,80 +10241,80 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>투자부동산</t>
+          <t>장기매출채권및기타채권</t>
         </is>
       </c>
       <c r="E14" s="18" t="n">
-        <v>1876.49</v>
+        <v>813.6900000000001</v>
       </c>
       <c r="F14" s="37" t="n">
-        <v>1876.49</v>
+        <v>813.6900000000001</v>
       </c>
       <c r="G14" s="18" t="n">
-        <v>1863.36</v>
+        <v>924.67</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>1850.22</v>
+        <v>1230.12</v>
       </c>
       <c r="I14" s="18" t="n">
-        <v>1837.08</v>
+        <v>1484.21</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>1906.88</v>
+        <v>81.14</v>
       </c>
       <c r="K14" s="37" t="n">
-        <v>1906.88</v>
+        <v>81.14</v>
       </c>
       <c r="L14" s="18" t="n">
-        <v>1897.7</v>
+        <v>37.83</v>
       </c>
       <c r="M14" s="18" t="n">
-        <v>1888.53</v>
+        <v>104.49</v>
       </c>
       <c r="N14" s="18" t="n">
-        <v>1879.36</v>
+        <v>177.2</v>
       </c>
       <c r="O14" s="18" t="n">
-        <v>1870.19</v>
+        <v>726.05</v>
       </c>
       <c r="P14" s="37" t="n">
-        <v>1870.19</v>
+        <v>726.05</v>
       </c>
       <c r="Q14" s="18" t="n">
-        <v>1861.01</v>
+        <v>1009.24</v>
       </c>
       <c r="R14" s="18" t="n">
-        <v>1851.84</v>
+        <v>1930.09</v>
       </c>
       <c r="S14" s="18" t="n">
-        <v>1842.67</v>
+        <v>611.4299999999999</v>
       </c>
       <c r="T14" s="18" t="n">
-        <v>5487.18</v>
+        <v>1662.41</v>
       </c>
       <c r="U14" s="37" t="n">
-        <v>5487.18</v>
+        <v>1662.41</v>
       </c>
       <c r="V14" s="18" t="n">
-        <v>5470.99</v>
+        <v>606.5700000000001</v>
       </c>
       <c r="W14" s="18" t="n">
-        <v>5454.81</v>
+        <v>1060.04</v>
       </c>
       <c r="X14" s="18" t="n">
-        <v>15623.2</v>
+        <v>1083.31</v>
       </c>
       <c r="Y14" s="18" t="n">
-        <v>8063.26</v>
+        <v>809.54</v>
       </c>
       <c r="Z14" s="37" t="n">
-        <v>8063.26</v>
+        <v>809.54</v>
       </c>
       <c r="AA14" s="18" t="n">
-        <v>8033.02</v>
+        <v>922.35</v>
       </c>
       <c r="AB14" s="19" t="n">
-        <v>5403.94</v>
+        <v>1030.21</v>
       </c>
       <c r="AC14" s="10" t="n"/>
       <c r="AD14" s="10" t="n"/>
@@ -10336,80 +10336,80 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>무형자산</t>
+          <t>장기금융자산</t>
         </is>
       </c>
       <c r="E15" s="18" t="n">
-        <v>8010.42</v>
+        <v>39885.42</v>
       </c>
       <c r="F15" s="37" t="n">
-        <v>8010.42</v>
+        <v>39885.42</v>
       </c>
       <c r="G15" s="18" t="n">
-        <v>7954.13</v>
+        <v>43835.27</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>7893.01</v>
+        <v>41818.64</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>7863.45</v>
+        <v>41735.44</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>7812.28</v>
+        <v>41153.41</v>
       </c>
       <c r="K15" s="37" t="n">
-        <v>7812.28</v>
+        <v>41153.41</v>
       </c>
       <c r="L15" s="18" t="n">
-        <v>7750.25</v>
+        <v>42357.96</v>
       </c>
       <c r="M15" s="18" t="n">
-        <v>7701.07</v>
+        <v>42790.39</v>
       </c>
       <c r="N15" s="18" t="n">
-        <v>1195.09</v>
+        <v>45250.98</v>
       </c>
       <c r="O15" s="18" t="n">
-        <v>1148.8</v>
+        <v>46702.02</v>
       </c>
       <c r="P15" s="37" t="n">
-        <v>1148.8</v>
+        <v>46702.02</v>
       </c>
       <c r="Q15" s="18" t="n">
-        <v>1136.21</v>
+        <v>47140.66</v>
       </c>
       <c r="R15" s="18" t="n">
-        <v>7405.21</v>
+        <v>47547.47</v>
       </c>
       <c r="S15" s="18" t="n">
-        <v>7396.57</v>
+        <v>47672.28</v>
       </c>
       <c r="T15" s="18" t="n">
-        <v>943.05</v>
+        <v>41548.17</v>
       </c>
       <c r="U15" s="37" t="n">
-        <v>943.05</v>
+        <v>41548.17</v>
       </c>
       <c r="V15" s="18" t="n">
-        <v>947.13</v>
+        <v>27616.13</v>
       </c>
       <c r="W15" s="18" t="n">
-        <v>1250.01</v>
+        <v>12751.34</v>
       </c>
       <c r="X15" s="18" t="n">
-        <v>1241.37</v>
+        <v>13445.04</v>
       </c>
       <c r="Y15" s="18" t="n">
-        <v>7688.87</v>
+        <v>14471.83</v>
       </c>
       <c r="Z15" s="37" t="n">
-        <v>7688.87</v>
+        <v>14471.83</v>
       </c>
       <c r="AA15" s="18" t="n">
-        <v>7695.78</v>
+        <v>9497.84</v>
       </c>
       <c r="AB15" s="19" t="n">
-        <v>7850.17</v>
+        <v>12248.24</v>
       </c>
       <c r="AC15" s="10" t="n"/>
       <c r="AD15" s="10" t="n"/>
@@ -10431,80 +10431,80 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>이연법인세자산</t>
+          <t>투자자산</t>
         </is>
       </c>
       <c r="E16" s="18" t="n">
-        <v>1233.72</v>
+        <v>39885.42</v>
       </c>
       <c r="F16" s="37" t="n">
-        <v>1233.72</v>
+        <v>39885.42</v>
       </c>
       <c r="G16" s="18" t="n">
-        <v>1733.62</v>
+        <v>43835.27</v>
       </c>
       <c r="H16" s="18" t="n">
-        <v>2052.15</v>
+        <v>41818.64</v>
       </c>
       <c r="I16" s="18" t="n">
-        <v>1516.31</v>
+        <v>41735.44</v>
       </c>
       <c r="J16" s="18" t="n">
-        <v>4131.95</v>
+        <v>41153.41</v>
       </c>
       <c r="K16" s="37" t="n">
-        <v>4131.95</v>
+        <v>41153.41</v>
       </c>
       <c r="L16" s="18" t="n">
-        <v>3746.08</v>
+        <v>42357.96</v>
       </c>
       <c r="M16" s="18" t="n">
-        <v>3685.98</v>
+        <v>42790.39</v>
       </c>
       <c r="N16" s="18" t="n">
-        <v>2940.21</v>
+        <v>45250.98</v>
       </c>
       <c r="O16" s="18" t="n">
-        <v>3249.19</v>
+        <v>46702.02</v>
       </c>
       <c r="P16" s="37" t="n">
-        <v>3249.19</v>
+        <v>46702.02</v>
       </c>
       <c r="Q16" s="18" t="n">
-        <v>2680.62</v>
+        <v>47140.66</v>
       </c>
       <c r="R16" s="18" t="n">
-        <v>2746.1</v>
+        <v>47547.47</v>
       </c>
       <c r="S16" s="18" t="n">
-        <v>2965.36</v>
+        <v>47672.28</v>
       </c>
       <c r="T16" s="18" t="n">
-        <v>2400.37</v>
+        <v>41548.17</v>
       </c>
       <c r="U16" s="37" t="n">
-        <v>2400.37</v>
+        <v>41548.17</v>
       </c>
       <c r="V16" s="18" t="n">
-        <v>3086.21</v>
+        <v>27616.13</v>
       </c>
       <c r="W16" s="18" t="n">
-        <v>3390.1</v>
+        <v>12751.34</v>
       </c>
       <c r="X16" s="18" t="n">
-        <v>3365.58</v>
+        <v>13445.04</v>
       </c>
       <c r="Y16" s="18" t="n">
-        <v>3853.02</v>
+        <v>14471.83</v>
       </c>
       <c r="Z16" s="37" t="n">
-        <v>3853.02</v>
+        <v>14471.83</v>
       </c>
       <c r="AA16" s="18" t="n">
-        <v>3030.66</v>
+        <v>9497.84</v>
       </c>
       <c r="AB16" s="19" t="n">
-        <v>3940.26</v>
+        <v>12248.24</v>
       </c>
       <c r="AC16" s="10" t="n"/>
       <c r="AD16" s="10" t="n"/>
@@ -10526,80 +10526,80 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>자산총계</t>
+          <t>유형자산</t>
         </is>
       </c>
       <c r="E17" s="18" t="n">
-        <v>260003.39</v>
+        <v>72261.42</v>
       </c>
       <c r="F17" s="37" t="n">
-        <v>260003.39</v>
+        <v>72261.42</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>258060.48</v>
+        <v>76101.88</v>
       </c>
       <c r="H17" s="18" t="n">
-        <v>258810.24</v>
+        <v>76939.60000000001</v>
       </c>
       <c r="I17" s="18" t="n">
-        <v>262614.16</v>
+        <v>76874.77</v>
       </c>
       <c r="J17" s="18" t="n">
-        <v>261112.52</v>
+        <v>76491.86</v>
       </c>
       <c r="K17" s="37" t="n">
-        <v>261112.52</v>
+        <v>76491.86</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>266270.17</v>
+        <v>75953.3</v>
       </c>
       <c r="M17" s="18" t="n">
-        <v>279254.82</v>
+        <v>79693.95</v>
       </c>
       <c r="N17" s="18" t="n">
-        <v>280285.66</v>
+        <v>81650.53999999999</v>
       </c>
       <c r="O17" s="18" t="n">
-        <v>297950.27</v>
+        <v>83082.81</v>
       </c>
       <c r="P17" s="37" t="n">
-        <v>297950.27</v>
+        <v>83082.81</v>
       </c>
       <c r="Q17" s="18" t="n">
-        <v>295957.58</v>
+        <v>82231.88</v>
       </c>
       <c r="R17" s="18" t="n">
-        <v>302849.65</v>
+        <v>83275.2</v>
       </c>
       <c r="S17" s="18" t="n">
-        <v>303664.4</v>
+        <v>82602.88</v>
       </c>
       <c r="T17" s="18" t="n">
-        <v>308605.89</v>
+        <v>79646.8</v>
       </c>
       <c r="U17" s="37" t="n">
-        <v>308605.89</v>
+        <v>79646.8</v>
       </c>
       <c r="V17" s="18" t="n">
-        <v>310593.54</v>
+        <v>80262.64999999999</v>
       </c>
       <c r="W17" s="18" t="n">
-        <v>318841.75</v>
+        <v>82623.92999999999</v>
       </c>
       <c r="X17" s="18" t="n">
-        <v>319950.18</v>
+        <v>72019.5</v>
       </c>
       <c r="Y17" s="18" t="n">
-        <v>321983.56</v>
+        <v>79391.81</v>
       </c>
       <c r="Z17" s="37" t="n">
-        <v>321983.56</v>
+        <v>79391.81</v>
       </c>
       <c r="AA17" s="18" t="n">
-        <v>332881.78</v>
+        <v>79496.72</v>
       </c>
       <c r="AB17" s="19" t="n">
-        <v>346315.62</v>
+        <v>90293.77</v>
       </c>
       <c r="AC17" s="10" t="n"/>
       <c r="AD17" s="10" t="n"/>
@@ -10621,80 +10621,80 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>유동부채</t>
+          <t>투자부동산</t>
         </is>
       </c>
       <c r="E18" s="18" t="n">
-        <v>32079.87</v>
+        <v>1876.49</v>
       </c>
       <c r="F18" s="37" t="n">
-        <v>32079.87</v>
+        <v>1876.49</v>
       </c>
       <c r="G18" s="18" t="n">
-        <v>32653.45</v>
+        <v>1863.36</v>
       </c>
       <c r="H18" s="18" t="n">
-        <v>34194.32</v>
+        <v>1850.22</v>
       </c>
       <c r="I18" s="18" t="n">
-        <v>36116.54</v>
+        <v>1837.08</v>
       </c>
       <c r="J18" s="18" t="n">
-        <v>41386.24</v>
+        <v>1906.88</v>
       </c>
       <c r="K18" s="37" t="n">
-        <v>41386.24</v>
+        <v>1906.88</v>
       </c>
       <c r="L18" s="18" t="n">
-        <v>44968</v>
+        <v>1897.7</v>
       </c>
       <c r="M18" s="18" t="n">
-        <v>57779.65</v>
+        <v>1888.53</v>
       </c>
       <c r="N18" s="18" t="n">
-        <v>55734.54</v>
+        <v>1879.36</v>
       </c>
       <c r="O18" s="18" t="n">
-        <v>70905.91</v>
+        <v>1870.19</v>
       </c>
       <c r="P18" s="37" t="n">
-        <v>70905.91</v>
+        <v>1870.19</v>
       </c>
       <c r="Q18" s="18" t="n">
-        <v>65168.3</v>
+        <v>1861.01</v>
       </c>
       <c r="R18" s="18" t="n">
-        <v>67858.48</v>
+        <v>1851.84</v>
       </c>
       <c r="S18" s="18" t="n">
-        <v>66041.77</v>
+        <v>1842.67</v>
       </c>
       <c r="T18" s="18" t="n">
-        <v>61797.78</v>
+        <v>5487.18</v>
       </c>
       <c r="U18" s="37" t="n">
-        <v>61797.78</v>
+        <v>5487.18</v>
       </c>
       <c r="V18" s="18" t="n">
-        <v>58716.67</v>
+        <v>5470.99</v>
       </c>
       <c r="W18" s="18" t="n">
-        <v>62691.42</v>
+        <v>5454.81</v>
       </c>
       <c r="X18" s="18" t="n">
-        <v>55559.82</v>
+        <v>15623.2</v>
       </c>
       <c r="Y18" s="18" t="n">
-        <v>50824.59</v>
+        <v>8063.26</v>
       </c>
       <c r="Z18" s="37" t="n">
-        <v>50824.59</v>
+        <v>8063.26</v>
       </c>
       <c r="AA18" s="18" t="n">
-        <v>56460.74</v>
+        <v>8033.02</v>
       </c>
       <c r="AB18" s="19" t="n">
-        <v>66524.95</v>
+        <v>5403.94</v>
       </c>
       <c r="AC18" s="10" t="n"/>
       <c r="AD18" s="10" t="n"/>
@@ -10716,80 +10716,80 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>매입채무및기타채무</t>
+          <t>무형자산</t>
         </is>
       </c>
       <c r="E19" s="18" t="n">
-        <v>13670.01</v>
+        <v>8010.42</v>
       </c>
       <c r="F19" s="37" t="n">
-        <v>13670.01</v>
+        <v>8010.42</v>
       </c>
       <c r="G19" s="18" t="n">
-        <v>13892.8</v>
+        <v>7954.13</v>
       </c>
       <c r="H19" s="18" t="n">
-        <v>13093.45</v>
+        <v>7893.01</v>
       </c>
       <c r="I19" s="18" t="n">
-        <v>13550.6</v>
+        <v>7863.45</v>
       </c>
       <c r="J19" s="18" t="n">
-        <v>11171.8</v>
+        <v>7812.28</v>
       </c>
       <c r="K19" s="37" t="n">
-        <v>11171.8</v>
+        <v>7812.28</v>
       </c>
       <c r="L19" s="18" t="n">
-        <v>13443.66</v>
+        <v>7750.25</v>
       </c>
       <c r="M19" s="18" t="n">
-        <v>14536.27</v>
+        <v>7701.07</v>
       </c>
       <c r="N19" s="18" t="n">
-        <v>15167.55</v>
+        <v>1195.09</v>
       </c>
       <c r="O19" s="18" t="n">
-        <v>18152.99</v>
+        <v>1148.8</v>
       </c>
       <c r="P19" s="37" t="n">
-        <v>18152.99</v>
+        <v>1148.8</v>
       </c>
       <c r="Q19" s="18" t="n">
-        <v>15945.6</v>
+        <v>1136.21</v>
       </c>
       <c r="R19" s="18" t="n">
-        <v>16866.88</v>
+        <v>7405.21</v>
       </c>
       <c r="S19" s="18" t="n">
-        <v>16529.28</v>
+        <v>7396.57</v>
       </c>
       <c r="T19" s="18" t="n">
-        <v>20068.52</v>
+        <v>943.05</v>
       </c>
       <c r="U19" s="37" t="n">
-        <v>20068.52</v>
+        <v>943.05</v>
       </c>
       <c r="V19" s="18" t="n">
-        <v>20742.33</v>
+        <v>947.13</v>
       </c>
       <c r="W19" s="18" t="n">
-        <v>23899.03</v>
+        <v>1250.01</v>
       </c>
       <c r="X19" s="18" t="n">
-        <v>21092.94</v>
+        <v>1241.37</v>
       </c>
       <c r="Y19" s="18" t="n">
-        <v>19052.81</v>
+        <v>7688.87</v>
       </c>
       <c r="Z19" s="37" t="n">
-        <v>19052.81</v>
+        <v>7688.87</v>
       </c>
       <c r="AA19" s="18" t="n">
-        <v>28895.42</v>
+        <v>7695.78</v>
       </c>
       <c r="AB19" s="19" t="n">
-        <v>27651.01</v>
+        <v>7850.17</v>
       </c>
       <c r="AC19" s="10" t="n"/>
       <c r="AD19" s="10" t="n"/>
@@ -10811,80 +10811,80 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>유동리스부채</t>
+          <t>이연법인세자산</t>
         </is>
       </c>
       <c r="E20" s="18" t="n">
-        <v>197.24</v>
+        <v>1233.72</v>
       </c>
       <c r="F20" s="37" t="n">
-        <v>197.24</v>
+        <v>1233.72</v>
       </c>
       <c r="G20" s="18" t="n">
-        <v>193.24</v>
+        <v>1733.62</v>
       </c>
       <c r="H20" s="18" t="n">
-        <v>189.25</v>
+        <v>2052.15</v>
       </c>
       <c r="I20" s="18" t="n">
-        <v>185.25</v>
+        <v>1516.31</v>
       </c>
       <c r="J20" s="18" t="n">
-        <v>197.04</v>
+        <v>4131.95</v>
       </c>
       <c r="K20" s="37" t="n">
-        <v>197.04</v>
+        <v>4131.95</v>
       </c>
       <c r="L20" s="18" t="n">
-        <v>248.44</v>
+        <v>3746.08</v>
       </c>
       <c r="M20" s="18" t="n">
-        <v>199.63</v>
+        <v>3685.98</v>
       </c>
       <c r="N20" s="18" t="n">
-        <v>203.96</v>
+        <v>2940.21</v>
       </c>
       <c r="O20" s="18" t="n">
-        <v>201</v>
+        <v>3249.19</v>
       </c>
       <c r="P20" s="37" t="n">
-        <v>201</v>
+        <v>3249.19</v>
       </c>
       <c r="Q20" s="18" t="n">
-        <v>198.01</v>
+        <v>2680.62</v>
       </c>
       <c r="R20" s="18" t="n">
-        <v>195.01</v>
+        <v>2746.1</v>
       </c>
       <c r="S20" s="18" t="n">
-        <v>191.97</v>
+        <v>2965.36</v>
       </c>
       <c r="T20" s="18" t="n">
-        <v>194.52</v>
+        <v>2400.37</v>
       </c>
       <c r="U20" s="37" t="n">
-        <v>194.52</v>
+        <v>2400.37</v>
       </c>
       <c r="V20" s="18" t="n">
-        <v>144.01</v>
+        <v>3086.21</v>
       </c>
       <c r="W20" s="18" t="n">
-        <v>90.75</v>
+        <v>3390.1</v>
       </c>
       <c r="X20" s="18" t="n">
-        <v>35.06</v>
+        <v>3365.58</v>
       </c>
       <c r="Y20" s="18" t="n">
-        <v>228.13</v>
+        <v>3853.02</v>
       </c>
       <c r="Z20" s="37" t="n">
-        <v>228.13</v>
+        <v>3853.02</v>
       </c>
       <c r="AA20" s="18" t="n">
-        <v>221.64</v>
+        <v>3030.66</v>
       </c>
       <c r="AB20" s="19" t="n">
-        <v>247.57</v>
+        <v>3940.26</v>
       </c>
       <c r="AC20" s="10" t="n"/>
       <c r="AD20" s="10" t="n"/>
@@ -10906,80 +10906,80 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>리스부채</t>
+          <t>자산총계</t>
         </is>
       </c>
       <c r="E21" s="18" t="n">
-        <v>197.24</v>
+        <v>260003.39</v>
       </c>
       <c r="F21" s="37" t="n">
-        <v>197.24</v>
+        <v>260003.39</v>
       </c>
       <c r="G21" s="18" t="n">
-        <v>193.24</v>
+        <v>258060.48</v>
       </c>
       <c r="H21" s="18" t="n">
-        <v>189.25</v>
+        <v>258810.24</v>
       </c>
       <c r="I21" s="18" t="n">
-        <v>185.25</v>
+        <v>262614.16</v>
       </c>
       <c r="J21" s="18" t="n">
-        <v>197.04</v>
+        <v>261112.52</v>
       </c>
       <c r="K21" s="37" t="n">
-        <v>197.04</v>
+        <v>261112.52</v>
       </c>
       <c r="L21" s="18" t="n">
-        <v>248.44</v>
+        <v>266270.17</v>
       </c>
       <c r="M21" s="18" t="n">
-        <v>199.63</v>
+        <v>279254.82</v>
       </c>
       <c r="N21" s="18" t="n">
-        <v>203.96</v>
+        <v>280285.66</v>
       </c>
       <c r="O21" s="18" t="n">
-        <v>201</v>
+        <v>297950.27</v>
       </c>
       <c r="P21" s="37" t="n">
-        <v>201</v>
+        <v>297950.27</v>
       </c>
       <c r="Q21" s="18" t="n">
-        <v>198.01</v>
+        <v>295957.58</v>
       </c>
       <c r="R21" s="18" t="n">
-        <v>195.01</v>
+        <v>302849.65</v>
       </c>
       <c r="S21" s="18" t="n">
-        <v>191.97</v>
+        <v>303664.4</v>
       </c>
       <c r="T21" s="18" t="n">
-        <v>194.52</v>
+        <v>308605.89</v>
       </c>
       <c r="U21" s="37" t="n">
-        <v>194.52</v>
+        <v>308605.89</v>
       </c>
       <c r="V21" s="18" t="n">
-        <v>144.01</v>
+        <v>310593.54</v>
       </c>
       <c r="W21" s="18" t="n">
-        <v>90.75</v>
+        <v>318841.75</v>
       </c>
       <c r="X21" s="18" t="n">
-        <v>35.06</v>
+        <v>319950.18</v>
       </c>
       <c r="Y21" s="18" t="n">
-        <v>391.5</v>
+        <v>321983.56</v>
       </c>
       <c r="Z21" s="37" t="n">
-        <v>391.5</v>
+        <v>321983.56</v>
       </c>
       <c r="AA21" s="18" t="n">
-        <v>332.21</v>
+        <v>332881.78</v>
       </c>
       <c r="AB21" s="19" t="n">
-        <v>341</v>
+        <v>346315.62</v>
       </c>
       <c r="AC21" s="10" t="n"/>
       <c r="AD21" s="10" t="n"/>
@@ -11001,80 +11001,80 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>단기금융부채</t>
+          <t>유동부채</t>
         </is>
       </c>
       <c r="E22" s="18" t="n">
-        <v>197.24</v>
+        <v>32079.87</v>
       </c>
       <c r="F22" s="37" t="n">
-        <v>197.24</v>
+        <v>32079.87</v>
       </c>
       <c r="G22" s="18" t="n">
-        <v>193.24</v>
+        <v>32653.45</v>
       </c>
       <c r="H22" s="18" t="n">
-        <v>189.25</v>
+        <v>34194.32</v>
       </c>
       <c r="I22" s="18" t="n">
-        <v>185.25</v>
+        <v>36116.54</v>
       </c>
       <c r="J22" s="18" t="n">
-        <v>197.04</v>
+        <v>41386.24</v>
       </c>
       <c r="K22" s="37" t="n">
-        <v>197.04</v>
+        <v>41386.24</v>
       </c>
       <c r="L22" s="18" t="n">
-        <v>248.44</v>
+        <v>44968</v>
       </c>
       <c r="M22" s="18" t="n">
-        <v>199.63</v>
+        <v>57779.65</v>
       </c>
       <c r="N22" s="18" t="n">
-        <v>203.96</v>
+        <v>55734.54</v>
       </c>
       <c r="O22" s="18" t="n">
-        <v>201</v>
+        <v>70905.91</v>
       </c>
       <c r="P22" s="37" t="n">
-        <v>201</v>
+        <v>70905.91</v>
       </c>
       <c r="Q22" s="18" t="n">
-        <v>198.01</v>
+        <v>65168.3</v>
       </c>
       <c r="R22" s="18" t="n">
-        <v>195.01</v>
+        <v>67858.48</v>
       </c>
       <c r="S22" s="18" t="n">
-        <v>191.97</v>
+        <v>66041.77</v>
       </c>
       <c r="T22" s="18" t="n">
-        <v>194.52</v>
+        <v>61797.78</v>
       </c>
       <c r="U22" s="37" t="n">
-        <v>194.52</v>
+        <v>61797.78</v>
       </c>
       <c r="V22" s="18" t="n">
-        <v>144.01</v>
+        <v>58716.67</v>
       </c>
       <c r="W22" s="18" t="n">
-        <v>90.75</v>
+        <v>62691.42</v>
       </c>
       <c r="X22" s="18" t="n">
-        <v>35.06</v>
+        <v>55559.82</v>
       </c>
       <c r="Y22" s="18" t="n">
-        <v>228.13</v>
+        <v>50824.59</v>
       </c>
       <c r="Z22" s="37" t="n">
-        <v>228.13</v>
+        <v>50824.59</v>
       </c>
       <c r="AA22" s="18" t="n">
-        <v>221.64</v>
+        <v>56460.74</v>
       </c>
       <c r="AB22" s="19" t="n">
-        <v>247.57</v>
+        <v>66524.95</v>
       </c>
       <c r="AC22" s="10" t="n"/>
       <c r="AD22" s="10" t="n"/>
@@ -11096,60 +11096,80 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>당기법인세부채(미지급법인세)</t>
+          <t>매입채무및기타채무</t>
         </is>
       </c>
       <c r="E23" s="18" t="n">
-        <v>0</v>
+        <v>13670.01</v>
       </c>
       <c r="F23" s="37" t="n">
-        <v>0</v>
+        <v>13670.01</v>
+      </c>
+      <c r="G23" s="18" t="n">
+        <v>13892.8</v>
+      </c>
+      <c r="H23" s="18" t="n">
+        <v>13093.45</v>
+      </c>
+      <c r="I23" s="18" t="n">
+        <v>13550.6</v>
       </c>
       <c r="J23" s="18" t="n">
-        <v>0</v>
+        <v>11171.8</v>
       </c>
       <c r="K23" s="37" t="n">
-        <v>0</v>
+        <v>11171.8</v>
       </c>
       <c r="L23" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="9" t="n"/>
+        <v>13443.66</v>
+      </c>
+      <c r="M23" s="18" t="n">
+        <v>14536.27</v>
+      </c>
+      <c r="N23" s="18" t="n">
+        <v>15167.55</v>
+      </c>
+      <c r="O23" s="18" t="n">
+        <v>18152.99</v>
+      </c>
+      <c r="P23" s="37" t="n">
+        <v>18152.99</v>
+      </c>
       <c r="Q23" s="18" t="n">
-        <v>178.14</v>
+        <v>15945.6</v>
       </c>
       <c r="R23" s="18" t="n">
-        <v>1097.22</v>
+        <v>16866.88</v>
       </c>
       <c r="S23" s="18" t="n">
-        <v>1640.07</v>
+        <v>16529.28</v>
       </c>
       <c r="T23" s="18" t="n">
-        <v>3186.94</v>
+        <v>20068.52</v>
       </c>
       <c r="U23" s="37" t="n">
-        <v>3186.94</v>
+        <v>20068.52</v>
       </c>
       <c r="V23" s="18" t="n">
-        <v>3854.63</v>
+        <v>20742.33</v>
       </c>
       <c r="W23" s="18" t="n">
-        <v>2956.4</v>
+        <v>23899.03</v>
       </c>
       <c r="X23" s="18" t="n">
-        <v>4268.49</v>
+        <v>21092.94</v>
       </c>
       <c r="Y23" s="18" t="n">
-        <v>5633.29</v>
+        <v>19052.81</v>
       </c>
       <c r="Z23" s="37" t="n">
-        <v>5633.29</v>
+        <v>19052.81</v>
       </c>
       <c r="AA23" s="18" t="n">
-        <v>4113.22</v>
+        <v>28895.42</v>
       </c>
       <c r="AB23" s="19" t="n">
-        <v>4279.1</v>
+        <v>27651.01</v>
       </c>
       <c r="AC23" s="10" t="n"/>
       <c r="AD23" s="10" t="n"/>
@@ -11171,80 +11191,80 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>비유동부채</t>
+          <t>유동리스부채</t>
         </is>
       </c>
       <c r="E24" s="18" t="n">
-        <v>1233.46</v>
+        <v>197.24</v>
       </c>
       <c r="F24" s="37" t="n">
-        <v>1233.46</v>
+        <v>197.24</v>
       </c>
       <c r="G24" s="18" t="n">
-        <v>1333.26</v>
+        <v>193.24</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>1317.18</v>
+        <v>189.25</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>1168.27</v>
+        <v>185.25</v>
       </c>
       <c r="J24" s="18" t="n">
-        <v>1257.11</v>
+        <v>197.04</v>
       </c>
       <c r="K24" s="37" t="n">
-        <v>1257.11</v>
+        <v>197.04</v>
       </c>
       <c r="L24" s="18" t="n">
-        <v>1210.79</v>
+        <v>248.44</v>
       </c>
       <c r="M24" s="18" t="n">
-        <v>1332.36</v>
+        <v>199.63</v>
       </c>
       <c r="N24" s="18" t="n">
-        <v>1448.72</v>
+        <v>203.96</v>
       </c>
       <c r="O24" s="18" t="n">
-        <v>1366.55</v>
+        <v>201</v>
       </c>
       <c r="P24" s="37" t="n">
-        <v>1366.55</v>
+        <v>201</v>
       </c>
       <c r="Q24" s="18" t="n">
-        <v>1406.38</v>
+        <v>198.01</v>
       </c>
       <c r="R24" s="18" t="n">
-        <v>1312.81</v>
+        <v>195.01</v>
       </c>
       <c r="S24" s="18" t="n">
-        <v>1400.34</v>
+        <v>191.97</v>
       </c>
       <c r="T24" s="18" t="n">
-        <v>1539.37</v>
+        <v>194.52</v>
       </c>
       <c r="U24" s="37" t="n">
-        <v>1539.37</v>
+        <v>194.52</v>
       </c>
       <c r="V24" s="18" t="n">
-        <v>1772.99</v>
+        <v>144.01</v>
       </c>
       <c r="W24" s="18" t="n">
-        <v>1688.73</v>
+        <v>90.75</v>
       </c>
       <c r="X24" s="18" t="n">
-        <v>1818.63</v>
+        <v>35.06</v>
       </c>
       <c r="Y24" s="18" t="n">
-        <v>1959.13</v>
+        <v>228.13</v>
       </c>
       <c r="Z24" s="37" t="n">
-        <v>1959.13</v>
+        <v>228.13</v>
       </c>
       <c r="AA24" s="18" t="n">
-        <v>1806.73</v>
+        <v>221.64</v>
       </c>
       <c r="AB24" s="19" t="n">
-        <v>1949.45</v>
+        <v>247.57</v>
       </c>
       <c r="AC24" s="10" t="n"/>
       <c r="AD24" s="10" t="n"/>
@@ -11266,49 +11286,80 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>기타비유동금융부채</t>
+          <t>리스부채</t>
         </is>
       </c>
       <c r="E25" s="18" t="n">
-        <v>622.1799999999999</v>
+        <v>721.3099999999999</v>
       </c>
       <c r="F25" s="37" t="n">
-        <v>622.1799999999999</v>
+        <v>721.3099999999999</v>
       </c>
       <c r="G25" s="18" t="n">
-        <v>616.25</v>
+        <v>672.59</v>
       </c>
       <c r="H25" s="18" t="n">
-        <v>706.27</v>
+        <v>623.59</v>
       </c>
       <c r="I25" s="18" t="n">
-        <v>694.15</v>
+        <v>574.3</v>
       </c>
       <c r="J25" s="18" t="n">
-        <v>718.39</v>
+        <v>556.17</v>
       </c>
       <c r="K25" s="37" t="n">
-        <v>718.39</v>
+        <v>556.17</v>
       </c>
       <c r="L25" s="18" t="n">
-        <v>703.98</v>
+        <v>507.39</v>
       </c>
       <c r="M25" s="18" t="n">
-        <v>745.63</v>
-      </c>
-      <c r="P25" s="9" t="n"/>
-      <c r="U25" s="9" t="n"/>
+        <v>458.29</v>
+      </c>
+      <c r="N25" s="18" t="n">
+        <v>408.87</v>
+      </c>
+      <c r="O25" s="18" t="n">
+        <v>359.13</v>
+      </c>
+      <c r="P25" s="37" t="n">
+        <v>359.13</v>
+      </c>
+      <c r="Q25" s="18" t="n">
+        <v>309.05</v>
+      </c>
+      <c r="R25" s="18" t="n">
+        <v>258.67</v>
+      </c>
+      <c r="S25" s="18" t="n">
+        <v>207.94</v>
+      </c>
+      <c r="T25" s="18" t="n">
+        <v>204.35</v>
+      </c>
+      <c r="U25" s="37" t="n">
+        <v>204.35</v>
+      </c>
+      <c r="V25" s="18" t="n">
+        <v>148.34</v>
+      </c>
+      <c r="W25" s="18" t="n">
+        <v>91.91</v>
+      </c>
+      <c r="X25" s="18" t="n">
+        <v>35.06</v>
+      </c>
       <c r="Y25" s="18" t="n">
-        <v>290</v>
+        <v>391.5</v>
       </c>
       <c r="Z25" s="37" t="n">
-        <v>290</v>
+        <v>391.5</v>
       </c>
       <c r="AA25" s="18" t="n">
-        <v>964.35</v>
+        <v>332.21</v>
       </c>
       <c r="AB25" s="19" t="n">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="AC25" s="10" t="n"/>
       <c r="AD25" s="10" t="n"/>
@@ -11330,49 +11381,80 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>장기금융부채</t>
+          <t>단기금융부채</t>
         </is>
       </c>
       <c r="E26" s="18" t="n">
-        <v>622.1799999999999</v>
+        <v>197.24</v>
       </c>
       <c r="F26" s="37" t="n">
-        <v>622.1799999999999</v>
+        <v>197.24</v>
       </c>
       <c r="G26" s="18" t="n">
-        <v>616.25</v>
+        <v>193.24</v>
       </c>
       <c r="H26" s="18" t="n">
-        <v>706.27</v>
+        <v>189.25</v>
       </c>
       <c r="I26" s="18" t="n">
-        <v>694.15</v>
+        <v>185.25</v>
       </c>
       <c r="J26" s="18" t="n">
-        <v>718.39</v>
+        <v>197.04</v>
       </c>
       <c r="K26" s="37" t="n">
-        <v>718.39</v>
+        <v>197.04</v>
       </c>
       <c r="L26" s="18" t="n">
-        <v>703.98</v>
+        <v>248.44</v>
       </c>
       <c r="M26" s="18" t="n">
-        <v>745.63</v>
-      </c>
-      <c r="P26" s="9" t="n"/>
-      <c r="U26" s="9" t="n"/>
+        <v>199.63</v>
+      </c>
+      <c r="N26" s="18" t="n">
+        <v>203.96</v>
+      </c>
+      <c r="O26" s="18" t="n">
+        <v>201</v>
+      </c>
+      <c r="P26" s="37" t="n">
+        <v>201</v>
+      </c>
+      <c r="Q26" s="18" t="n">
+        <v>198.01</v>
+      </c>
+      <c r="R26" s="18" t="n">
+        <v>195.01</v>
+      </c>
+      <c r="S26" s="18" t="n">
+        <v>191.97</v>
+      </c>
+      <c r="T26" s="18" t="n">
+        <v>194.52</v>
+      </c>
+      <c r="U26" s="37" t="n">
+        <v>194.52</v>
+      </c>
+      <c r="V26" s="18" t="n">
+        <v>144.01</v>
+      </c>
+      <c r="W26" s="18" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="X26" s="18" t="n">
+        <v>35.06</v>
+      </c>
       <c r="Y26" s="18" t="n">
-        <v>453.37</v>
+        <v>228.13</v>
       </c>
       <c r="Z26" s="37" t="n">
-        <v>453.37</v>
+        <v>228.13</v>
       </c>
       <c r="AA26" s="18" t="n">
-        <v>1074.92</v>
+        <v>221.64</v>
       </c>
       <c r="AB26" s="19" t="n">
-        <v>453.43</v>
+        <v>247.57</v>
       </c>
       <c r="AC26" s="10" t="n"/>
       <c r="AD26" s="10" t="n"/>
@@ -11394,23 +11476,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>확정급여부채</t>
+          <t>당기법인세부채(미지급법인세)</t>
         </is>
       </c>
       <c r="E27" s="18" t="n">
-        <v>87.2</v>
+        <v>0</v>
       </c>
       <c r="F27" s="37" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="G27" s="18" t="n">
-        <v>237.65</v>
-      </c>
-      <c r="H27" s="18" t="n">
-        <v>176.57</v>
-      </c>
-      <c r="I27" s="18" t="n">
-        <v>85.08</v>
+        <v>0</v>
       </c>
       <c r="J27" s="18" t="n">
         <v>0</v>
@@ -11419,46 +11492,45 @@
         <v>0</v>
       </c>
       <c r="L27" s="18" t="n">
-        <v>21.22</v>
-      </c>
-      <c r="M27" s="18" t="n">
-        <v>54.37</v>
-      </c>
-      <c r="N27" s="18" t="n">
-        <v>157.34</v>
-      </c>
-      <c r="O27" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="P27" s="37" t="n">
-        <v>0</v>
-      </c>
+      <c r="P27" s="9" t="n"/>
       <c r="Q27" s="18" t="n">
-        <v>57.1</v>
+        <v>178.14</v>
       </c>
       <c r="R27" s="18" t="n">
-        <v>67.94</v>
+        <v>1097.22</v>
       </c>
       <c r="S27" s="18" t="n">
-        <v>170.52</v>
+        <v>1640.07</v>
       </c>
       <c r="T27" s="18" t="n">
-        <v>168.52</v>
+        <v>3186.94</v>
       </c>
       <c r="U27" s="37" t="n">
-        <v>168.52</v>
+        <v>3186.94</v>
       </c>
       <c r="V27" s="18" t="n">
-        <v>412.87</v>
+        <v>3854.63</v>
       </c>
       <c r="W27" s="18" t="n">
-        <v>417.54</v>
+        <v>2956.4</v>
       </c>
       <c r="X27" s="18" t="n">
-        <v>548.58</v>
-      </c>
-      <c r="Z27" s="9" t="n"/>
-      <c r="AB27" s="5" t="n"/>
+        <v>4268.49</v>
+      </c>
+      <c r="Y27" s="18" t="n">
+        <v>5633.29</v>
+      </c>
+      <c r="Z27" s="37" t="n">
+        <v>5633.29</v>
+      </c>
+      <c r="AA27" s="18" t="n">
+        <v>4113.22</v>
+      </c>
+      <c r="AB27" s="19" t="n">
+        <v>4279.1</v>
+      </c>
       <c r="AC27" s="10" t="n"/>
       <c r="AD27" s="10" t="n"/>
       <c r="AE27" s="11" t="n"/>
@@ -11479,80 +11551,80 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>부채총계</t>
+          <t>비유동부채</t>
         </is>
       </c>
       <c r="E28" s="18" t="n">
-        <v>33313.33</v>
+        <v>1233.46</v>
       </c>
       <c r="F28" s="37" t="n">
-        <v>33313.33</v>
+        <v>1233.46</v>
       </c>
       <c r="G28" s="18" t="n">
-        <v>33986.7</v>
+        <v>1333.26</v>
       </c>
       <c r="H28" s="18" t="n">
-        <v>35511.5</v>
+        <v>1317.18</v>
       </c>
       <c r="I28" s="18" t="n">
-        <v>37284.81</v>
+        <v>1168.27</v>
       </c>
       <c r="J28" s="18" t="n">
-        <v>42643.35</v>
+        <v>1257.11</v>
       </c>
       <c r="K28" s="37" t="n">
-        <v>42643.35</v>
+        <v>1257.11</v>
       </c>
       <c r="L28" s="18" t="n">
-        <v>46178.79</v>
+        <v>1210.79</v>
       </c>
       <c r="M28" s="18" t="n">
-        <v>59112</v>
+        <v>1332.36</v>
       </c>
       <c r="N28" s="18" t="n">
-        <v>57183.26</v>
+        <v>1448.72</v>
       </c>
       <c r="O28" s="18" t="n">
-        <v>72272.46000000001</v>
+        <v>1366.55</v>
       </c>
       <c r="P28" s="37" t="n">
-        <v>72272.46000000001</v>
+        <v>1366.55</v>
       </c>
       <c r="Q28" s="18" t="n">
-        <v>66574.67999999999</v>
+        <v>1406.38</v>
       </c>
       <c r="R28" s="18" t="n">
-        <v>69171.28999999999</v>
+        <v>1312.81</v>
       </c>
       <c r="S28" s="18" t="n">
-        <v>67442.12</v>
+        <v>1400.34</v>
       </c>
       <c r="T28" s="18" t="n">
-        <v>63337.14</v>
+        <v>1539.37</v>
       </c>
       <c r="U28" s="37" t="n">
-        <v>63337.14</v>
+        <v>1539.37</v>
       </c>
       <c r="V28" s="18" t="n">
-        <v>60489.66</v>
+        <v>1772.99</v>
       </c>
       <c r="W28" s="18" t="n">
-        <v>64380.14</v>
+        <v>1688.73</v>
       </c>
       <c r="X28" s="18" t="n">
-        <v>57378.45</v>
+        <v>1818.63</v>
       </c>
       <c r="Y28" s="18" t="n">
-        <v>52783.72</v>
+        <v>1959.13</v>
       </c>
       <c r="Z28" s="37" t="n">
-        <v>52783.72</v>
+        <v>1959.13</v>
       </c>
       <c r="AA28" s="18" t="n">
-        <v>58267.46</v>
+        <v>1806.73</v>
       </c>
       <c r="AB28" s="19" t="n">
-        <v>68474.39999999999</v>
+        <v>1949.45</v>
       </c>
       <c r="AC28" s="10" t="n"/>
       <c r="AD28" s="10" t="n"/>
@@ -11574,80 +11646,49 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>지배주주지분</t>
+          <t>기타비유동금융부채</t>
         </is>
       </c>
       <c r="E29" s="18" t="n">
-        <v>226690.06</v>
+        <v>622.1799999999999</v>
       </c>
       <c r="F29" s="37" t="n">
-        <v>226690.06</v>
+        <v>622.1799999999999</v>
       </c>
       <c r="G29" s="18" t="n">
-        <v>224073.78</v>
+        <v>616.25</v>
       </c>
       <c r="H29" s="18" t="n">
-        <v>223298.74</v>
+        <v>706.27</v>
       </c>
       <c r="I29" s="18" t="n">
-        <v>225329.35</v>
+        <v>694.15</v>
       </c>
       <c r="J29" s="18" t="n">
-        <v>218469.18</v>
+        <v>718.39</v>
       </c>
       <c r="K29" s="37" t="n">
-        <v>218469.18</v>
+        <v>718.39</v>
       </c>
       <c r="L29" s="18" t="n">
-        <v>220091.38</v>
+        <v>703.98</v>
       </c>
       <c r="M29" s="18" t="n">
-        <v>220142.81</v>
-      </c>
-      <c r="N29" s="18" t="n">
-        <v>223102.4</v>
-      </c>
-      <c r="O29" s="18" t="n">
-        <v>225677.81</v>
-      </c>
-      <c r="P29" s="37" t="n">
-        <v>225677.81</v>
-      </c>
-      <c r="Q29" s="18" t="n">
-        <v>229382.89</v>
-      </c>
-      <c r="R29" s="18" t="n">
-        <v>233678.36</v>
-      </c>
-      <c r="S29" s="18" t="n">
-        <v>236222.29</v>
-      </c>
-      <c r="T29" s="18" t="n">
-        <v>245268.75</v>
-      </c>
-      <c r="U29" s="37" t="n">
-        <v>245268.75</v>
-      </c>
-      <c r="V29" s="18" t="n">
-        <v>250103.88</v>
-      </c>
-      <c r="W29" s="18" t="n">
-        <v>254461.61</v>
-      </c>
-      <c r="X29" s="18" t="n">
-        <v>262571.73</v>
-      </c>
+        <v>745.63</v>
+      </c>
+      <c r="P29" s="9" t="n"/>
+      <c r="U29" s="9" t="n"/>
       <c r="Y29" s="18" t="n">
-        <v>269199.84</v>
+        <v>290</v>
       </c>
       <c r="Z29" s="37" t="n">
-        <v>269199.84</v>
+        <v>290</v>
       </c>
       <c r="AA29" s="18" t="n">
-        <v>274614.32</v>
+        <v>964.35</v>
       </c>
       <c r="AB29" s="19" t="n">
-        <v>277841.22</v>
+        <v>360</v>
       </c>
       <c r="AC29" s="10" t="n"/>
       <c r="AD29" s="10" t="n"/>
@@ -11669,80 +11710,80 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>자본금</t>
+          <t>장기금융부채</t>
         </is>
       </c>
       <c r="E30" s="18" t="n">
-        <v>4783.67</v>
+        <v>1146.25</v>
       </c>
       <c r="F30" s="37" t="n">
-        <v>4783.67</v>
+        <v>1146.25</v>
       </c>
       <c r="G30" s="18" t="n">
-        <v>4783.67</v>
+        <v>1095.6</v>
       </c>
       <c r="H30" s="18" t="n">
-        <v>4783.67</v>
+        <v>1140.61</v>
       </c>
       <c r="I30" s="18" t="n">
-        <v>4783.67</v>
+        <v>1083.2</v>
       </c>
       <c r="J30" s="18" t="n">
-        <v>4783.67</v>
+        <v>1077.52</v>
       </c>
       <c r="K30" s="37" t="n">
-        <v>4783.67</v>
+        <v>1077.52</v>
       </c>
       <c r="L30" s="18" t="n">
-        <v>4783.67</v>
+        <v>962.9299999999999</v>
       </c>
       <c r="M30" s="18" t="n">
-        <v>4783.67</v>
+        <v>1004.29</v>
       </c>
       <c r="N30" s="18" t="n">
-        <v>4783.67</v>
+        <v>204.91</v>
       </c>
       <c r="O30" s="18" t="n">
-        <v>4783.67</v>
+        <v>158.13</v>
       </c>
       <c r="P30" s="37" t="n">
-        <v>4783.67</v>
+        <v>158.13</v>
       </c>
       <c r="Q30" s="18" t="n">
-        <v>4783.67</v>
+        <v>111.04</v>
       </c>
       <c r="R30" s="18" t="n">
-        <v>4783.67</v>
+        <v>63.66</v>
       </c>
       <c r="S30" s="18" t="n">
-        <v>4783.67</v>
+        <v>15.97</v>
       </c>
       <c r="T30" s="18" t="n">
-        <v>4783.67</v>
+        <v>9.83</v>
       </c>
       <c r="U30" s="37" t="n">
-        <v>4783.67</v>
+        <v>9.83</v>
       </c>
       <c r="V30" s="18" t="n">
-        <v>4783.67</v>
+        <v>4.33</v>
       </c>
       <c r="W30" s="18" t="n">
-        <v>4783.67</v>
+        <v>1.16</v>
       </c>
       <c r="X30" s="18" t="n">
-        <v>4783.67</v>
+        <v>0</v>
       </c>
       <c r="Y30" s="18" t="n">
-        <v>4783.67</v>
+        <v>453.37</v>
       </c>
       <c r="Z30" s="37" t="n">
-        <v>4783.67</v>
+        <v>453.37</v>
       </c>
       <c r="AA30" s="18" t="n">
-        <v>4783.67</v>
+        <v>1074.92</v>
       </c>
       <c r="AB30" s="19" t="n">
-        <v>4783.67</v>
+        <v>453.43</v>
       </c>
       <c r="AC30" s="10" t="n"/>
       <c r="AD30" s="10" t="n"/>
@@ -11764,81 +11805,71 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>자본잉여금</t>
+          <t>확정급여부채</t>
         </is>
       </c>
       <c r="E31" s="18" t="n">
-        <v>24958.68</v>
+        <v>87.2</v>
       </c>
       <c r="F31" s="37" t="n">
-        <v>24958.68</v>
+        <v>87.2</v>
       </c>
       <c r="G31" s="18" t="n">
-        <v>24974.84</v>
+        <v>237.65</v>
       </c>
       <c r="H31" s="18" t="n">
-        <v>24977.78</v>
+        <v>176.57</v>
       </c>
       <c r="I31" s="18" t="n">
-        <v>24977.78</v>
+        <v>85.08</v>
       </c>
       <c r="J31" s="18" t="n">
-        <v>24978.48</v>
+        <v>0</v>
       </c>
       <c r="K31" s="37" t="n">
-        <v>24978.48</v>
+        <v>0</v>
       </c>
       <c r="L31" s="18" t="n">
-        <v>25026.82</v>
+        <v>21.22</v>
       </c>
       <c r="M31" s="18" t="n">
-        <v>25034.91</v>
+        <v>54.37</v>
       </c>
       <c r="N31" s="18" t="n">
-        <v>25034.91</v>
+        <v>157.34</v>
       </c>
       <c r="O31" s="18" t="n">
-        <v>25035.47</v>
+        <v>0</v>
       </c>
       <c r="P31" s="37" t="n">
-        <v>25035.47</v>
+        <v>0</v>
       </c>
       <c r="Q31" s="18" t="n">
-        <v>25048.84</v>
+        <v>57.1</v>
       </c>
       <c r="R31" s="18" t="n">
-        <v>25053.11</v>
+        <v>67.94</v>
       </c>
       <c r="S31" s="18" t="n">
-        <v>25053.11</v>
+        <v>170.52</v>
       </c>
       <c r="T31" s="18" t="n">
-        <v>25053.11</v>
+        <v>168.52</v>
       </c>
       <c r="U31" s="37" t="n">
-        <v>25053.11</v>
+        <v>168.52</v>
       </c>
       <c r="V31" s="18" t="n">
-        <v>25053.11</v>
+        <v>412.87</v>
       </c>
       <c r="W31" s="18" t="n">
-        <v>25086.07</v>
+        <v>417.54</v>
       </c>
       <c r="X31" s="18" t="n">
-        <v>25086.07</v>
-      </c>
-      <c r="Y31" s="18" t="n">
-        <v>25272.22</v>
-      </c>
-      <c r="Z31" s="37" t="n">
-        <v>25272.22</v>
-      </c>
-      <c r="AA31" s="18" t="n">
-        <v>25272.22</v>
-      </c>
-      <c r="AB31" s="19" t="n">
-        <v>20460.2</v>
-      </c>
+        <v>548.58</v>
+      </c>
+      <c r="Z31" s="9" t="n"/>
+      <c r="AB31" s="5" t="n"/>
       <c r="AC31" s="10" t="n"/>
       <c r="AD31" s="10" t="n"/>
       <c r="AE31" s="11" t="n"/>
@@ -11859,80 +11890,80 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>기타자본</t>
+          <t>비유동리스부채</t>
         </is>
       </c>
       <c r="E32" s="18" t="n">
-        <v>-2586.62</v>
+        <v>524.0700000000001</v>
       </c>
       <c r="F32" s="37" t="n">
-        <v>-2586.62</v>
+        <v>524.0700000000001</v>
       </c>
       <c r="G32" s="18" t="n">
-        <v>-2597.23</v>
+        <v>479.35</v>
       </c>
       <c r="H32" s="18" t="n">
-        <v>-2562.52</v>
+        <v>434.34</v>
       </c>
       <c r="I32" s="18" t="n">
-        <v>-2554.74</v>
+        <v>389.05</v>
       </c>
       <c r="J32" s="18" t="n">
-        <v>-2541.49</v>
+        <v>359.13</v>
       </c>
       <c r="K32" s="37" t="n">
-        <v>-2541.49</v>
+        <v>359.13</v>
       </c>
       <c r="L32" s="18" t="n">
-        <v>-2581.8</v>
+        <v>258.95</v>
       </c>
       <c r="M32" s="18" t="n">
-        <v>-3490.35</v>
+        <v>258.66</v>
       </c>
       <c r="N32" s="18" t="n">
-        <v>-3523.92</v>
+        <v>204.91</v>
       </c>
       <c r="O32" s="18" t="n">
-        <v>-3508.07</v>
+        <v>158.13</v>
       </c>
       <c r="P32" s="37" t="n">
-        <v>-3508.07</v>
+        <v>158.13</v>
       </c>
       <c r="Q32" s="18" t="n">
-        <v>-3509.47</v>
+        <v>111.04</v>
       </c>
       <c r="R32" s="18" t="n">
-        <v>-3471.66</v>
+        <v>63.66</v>
       </c>
       <c r="S32" s="18" t="n">
-        <v>-3455.64</v>
+        <v>15.97</v>
       </c>
       <c r="T32" s="18" t="n">
-        <v>-3436.7</v>
+        <v>9.83</v>
       </c>
       <c r="U32" s="37" t="n">
-        <v>-3436.7</v>
+        <v>9.83</v>
       </c>
       <c r="V32" s="18" t="n">
-        <v>-3419.11</v>
+        <v>4.33</v>
       </c>
       <c r="W32" s="18" t="n">
-        <v>-3374.2</v>
+        <v>1.16</v>
       </c>
       <c r="X32" s="18" t="n">
-        <v>-3334.46</v>
+        <v>0</v>
       </c>
       <c r="Y32" s="18" t="n">
-        <v>-3296.14</v>
+        <v>163.37</v>
       </c>
       <c r="Z32" s="37" t="n">
-        <v>-3296.14</v>
+        <v>163.37</v>
       </c>
       <c r="AA32" s="18" t="n">
-        <v>-3296.14</v>
+        <v>110.57</v>
       </c>
       <c r="AB32" s="19" t="n">
-        <v>-2920.76</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="AC32" s="10" t="n"/>
       <c r="AD32" s="10" t="n"/>
@@ -11954,80 +11985,80 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>기타포괄이익누계액</t>
+          <t>부채총계</t>
         </is>
       </c>
       <c r="E33" s="18" t="n">
-        <v>9330.27</v>
+        <v>33313.33</v>
       </c>
       <c r="F33" s="37" t="n">
-        <v>9330.27</v>
+        <v>33313.33</v>
       </c>
       <c r="G33" s="18" t="n">
-        <v>9330.27</v>
+        <v>33986.7</v>
       </c>
       <c r="H33" s="18" t="n">
-        <v>9330.27</v>
+        <v>35511.5</v>
       </c>
       <c r="I33" s="18" t="n">
-        <v>9330.27</v>
+        <v>37284.81</v>
       </c>
       <c r="J33" s="18" t="n">
-        <v>9330.27</v>
+        <v>42643.35</v>
       </c>
       <c r="K33" s="37" t="n">
-        <v>9330.27</v>
+        <v>42643.35</v>
       </c>
       <c r="L33" s="18" t="n">
-        <v>9330.27</v>
+        <v>46178.79</v>
       </c>
       <c r="M33" s="18" t="n">
-        <v>9330.27</v>
+        <v>59112</v>
       </c>
       <c r="N33" s="18" t="n">
-        <v>9330.27</v>
+        <v>57183.26</v>
       </c>
       <c r="O33" s="18" t="n">
-        <v>9330.27</v>
+        <v>72272.46000000001</v>
       </c>
       <c r="P33" s="37" t="n">
-        <v>9330.27</v>
+        <v>72272.46000000001</v>
       </c>
       <c r="Q33" s="18" t="n">
-        <v>9330.27</v>
+        <v>66574.67999999999</v>
       </c>
       <c r="R33" s="18" t="n">
-        <v>9330.27</v>
+        <v>69171.28999999999</v>
       </c>
       <c r="S33" s="18" t="n">
-        <v>9330.27</v>
+        <v>67442.12</v>
       </c>
       <c r="T33" s="18" t="n">
-        <v>9330.27</v>
+        <v>63337.14</v>
       </c>
       <c r="U33" s="37" t="n">
-        <v>9330.27</v>
+        <v>63337.14</v>
       </c>
       <c r="V33" s="18" t="n">
-        <v>9330.27</v>
+        <v>60489.66</v>
       </c>
       <c r="W33" s="18" t="n">
-        <v>9330.27</v>
+        <v>64380.14</v>
       </c>
       <c r="X33" s="18" t="n">
-        <v>9330.27</v>
+        <v>57378.45</v>
       </c>
       <c r="Y33" s="18" t="n">
-        <v>9330.27</v>
+        <v>52783.72</v>
       </c>
       <c r="Z33" s="37" t="n">
-        <v>9330.27</v>
+        <v>52783.72</v>
       </c>
       <c r="AA33" s="18" t="n">
-        <v>9330.27</v>
+        <v>58267.46</v>
       </c>
       <c r="AB33" s="19" t="n">
-        <v>9330.27</v>
+        <v>68474.39999999999</v>
       </c>
       <c r="AC33" s="10" t="n"/>
       <c r="AD33" s="10" t="n"/>
@@ -12049,80 +12080,80 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>이익잉여금</t>
+          <t>지배주주지분</t>
         </is>
       </c>
       <c r="E34" s="18" t="n">
-        <v>190204.06</v>
+        <v>226690.06</v>
       </c>
       <c r="F34" s="37" t="n">
-        <v>190204.06</v>
+        <v>226690.06</v>
       </c>
       <c r="G34" s="18" t="n">
-        <v>187582.23</v>
+        <v>224073.78</v>
       </c>
       <c r="H34" s="18" t="n">
-        <v>186769.55</v>
+        <v>223298.74</v>
       </c>
       <c r="I34" s="18" t="n">
-        <v>188792.37</v>
+        <v>225329.35</v>
       </c>
       <c r="J34" s="18" t="n">
-        <v>181918.26</v>
+        <v>218469.18</v>
       </c>
       <c r="K34" s="37" t="n">
-        <v>181918.26</v>
+        <v>218469.18</v>
       </c>
       <c r="L34" s="18" t="n">
-        <v>183532.43</v>
+        <v>220091.38</v>
       </c>
       <c r="M34" s="18" t="n">
-        <v>184484.32</v>
+        <v>220142.81</v>
       </c>
       <c r="N34" s="18" t="n">
-        <v>187477.48</v>
+        <v>223102.4</v>
       </c>
       <c r="O34" s="18" t="n">
-        <v>190036.48</v>
+        <v>225677.81</v>
       </c>
       <c r="P34" s="37" t="n">
-        <v>190036.48</v>
+        <v>225677.81</v>
       </c>
       <c r="Q34" s="18" t="n">
-        <v>193729.59</v>
+        <v>229382.89</v>
       </c>
       <c r="R34" s="18" t="n">
-        <v>197982.97</v>
+        <v>233678.36</v>
       </c>
       <c r="S34" s="18" t="n">
-        <v>200510.88</v>
+        <v>236222.29</v>
       </c>
       <c r="T34" s="18" t="n">
-        <v>209538.41</v>
+        <v>245268.75</v>
       </c>
       <c r="U34" s="37" t="n">
-        <v>209538.41</v>
+        <v>245268.75</v>
       </c>
       <c r="V34" s="18" t="n">
-        <v>214355.95</v>
+        <v>250103.88</v>
       </c>
       <c r="W34" s="18" t="n">
-        <v>218635.81</v>
+        <v>254461.61</v>
       </c>
       <c r="X34" s="18" t="n">
-        <v>226706.19</v>
+        <v>262571.73</v>
       </c>
       <c r="Y34" s="18" t="n">
-        <v>233109.82</v>
+        <v>269199.84</v>
       </c>
       <c r="Z34" s="37" t="n">
-        <v>233109.82</v>
+        <v>269199.84</v>
       </c>
       <c r="AA34" s="18" t="n">
-        <v>238524.3</v>
+        <v>274614.32</v>
       </c>
       <c r="AB34" s="19" t="n">
-        <v>246187.85</v>
+        <v>277841.22</v>
       </c>
       <c r="AC34" s="10" t="n"/>
       <c r="AD34" s="10" t="n"/>
@@ -12144,71 +12175,81 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>비지배주주지분</t>
+          <t>자본금</t>
         </is>
       </c>
       <c r="E35" s="18" t="n">
-        <v>0</v>
+        <v>4783.67</v>
       </c>
       <c r="F35" s="37" t="n">
-        <v>0</v>
+        <v>4783.67</v>
       </c>
       <c r="G35" s="18" t="n">
-        <v>0</v>
+        <v>4783.67</v>
       </c>
       <c r="H35" s="18" t="n">
-        <v>0</v>
+        <v>4783.67</v>
       </c>
       <c r="I35" s="18" t="n">
-        <v>0</v>
+        <v>4783.67</v>
       </c>
       <c r="J35" s="18" t="n">
-        <v>0</v>
+        <v>4783.67</v>
       </c>
       <c r="K35" s="37" t="n">
-        <v>0</v>
+        <v>4783.67</v>
       </c>
       <c r="L35" s="18" t="n">
-        <v>0</v>
+        <v>4783.67</v>
       </c>
       <c r="M35" s="18" t="n">
-        <v>0</v>
+        <v>4783.67</v>
       </c>
       <c r="N35" s="18" t="n">
-        <v>0</v>
+        <v>4783.67</v>
       </c>
       <c r="O35" s="18" t="n">
-        <v>0</v>
+        <v>4783.67</v>
       </c>
       <c r="P35" s="37" t="n">
-        <v>0</v>
+        <v>4783.67</v>
       </c>
       <c r="Q35" s="18" t="n">
-        <v>0</v>
+        <v>4783.67</v>
       </c>
       <c r="R35" s="18" t="n">
-        <v>0</v>
+        <v>4783.67</v>
       </c>
       <c r="S35" s="18" t="n">
-        <v>0</v>
+        <v>4783.67</v>
       </c>
       <c r="T35" s="18" t="n">
-        <v>0</v>
+        <v>4783.67</v>
       </c>
       <c r="U35" s="37" t="n">
-        <v>0</v>
+        <v>4783.67</v>
       </c>
       <c r="V35" s="18" t="n">
-        <v>0</v>
+        <v>4783.67</v>
       </c>
       <c r="W35" s="18" t="n">
-        <v>0</v>
+        <v>4783.67</v>
       </c>
       <c r="X35" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" s="9" t="n"/>
-      <c r="AB35" s="5" t="n"/>
+        <v>4783.67</v>
+      </c>
+      <c r="Y35" s="18" t="n">
+        <v>4783.67</v>
+      </c>
+      <c r="Z35" s="37" t="n">
+        <v>4783.67</v>
+      </c>
+      <c r="AA35" s="18" t="n">
+        <v>4783.67</v>
+      </c>
+      <c r="AB35" s="19" t="n">
+        <v>4783.67</v>
+      </c>
       <c r="AC35" s="10" t="n"/>
       <c r="AD35" s="10" t="n"/>
       <c r="AE35" s="11" t="n"/>
@@ -12229,80 +12270,80 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>자본총계</t>
+          <t>자본잉여금</t>
         </is>
       </c>
       <c r="E36" s="18" t="n">
-        <v>226690.06</v>
+        <v>24958.68</v>
       </c>
       <c r="F36" s="37" t="n">
-        <v>226690.06</v>
+        <v>24958.68</v>
       </c>
       <c r="G36" s="18" t="n">
-        <v>224073.78</v>
+        <v>24974.84</v>
       </c>
       <c r="H36" s="18" t="n">
-        <v>223298.74</v>
+        <v>24977.78</v>
       </c>
       <c r="I36" s="18" t="n">
-        <v>225329.35</v>
+        <v>24977.78</v>
       </c>
       <c r="J36" s="18" t="n">
-        <v>218469.18</v>
+        <v>24978.48</v>
       </c>
       <c r="K36" s="37" t="n">
-        <v>218469.18</v>
+        <v>24978.48</v>
       </c>
       <c r="L36" s="18" t="n">
-        <v>220091.38</v>
+        <v>25026.82</v>
       </c>
       <c r="M36" s="18" t="n">
-        <v>220142.81</v>
+        <v>25034.91</v>
       </c>
       <c r="N36" s="18" t="n">
-        <v>223102.4</v>
+        <v>25034.91</v>
       </c>
       <c r="O36" s="18" t="n">
-        <v>225677.81</v>
+        <v>25035.47</v>
       </c>
       <c r="P36" s="37" t="n">
-        <v>225677.81</v>
+        <v>25035.47</v>
       </c>
       <c r="Q36" s="18" t="n">
-        <v>229382.89</v>
+        <v>25048.84</v>
       </c>
       <c r="R36" s="18" t="n">
-        <v>233678.36</v>
+        <v>25053.11</v>
       </c>
       <c r="S36" s="18" t="n">
-        <v>236222.29</v>
+        <v>25053.11</v>
       </c>
       <c r="T36" s="18" t="n">
-        <v>245268.75</v>
+        <v>25053.11</v>
       </c>
       <c r="U36" s="37" t="n">
-        <v>245268.75</v>
+        <v>25053.11</v>
       </c>
       <c r="V36" s="18" t="n">
-        <v>250103.88</v>
+        <v>25053.11</v>
       </c>
       <c r="W36" s="18" t="n">
-        <v>254461.61</v>
+        <v>25086.07</v>
       </c>
       <c r="X36" s="18" t="n">
-        <v>262571.73</v>
+        <v>25086.07</v>
       </c>
       <c r="Y36" s="18" t="n">
-        <v>269199.84</v>
+        <v>25272.22</v>
       </c>
       <c r="Z36" s="37" t="n">
-        <v>269199.84</v>
+        <v>25272.22</v>
       </c>
       <c r="AA36" s="18" t="n">
-        <v>274614.32</v>
+        <v>25272.22</v>
       </c>
       <c r="AB36" s="19" t="n">
-        <v>277841.22</v>
+        <v>20460.2</v>
       </c>
       <c r="AC36" s="10" t="n"/>
       <c r="AD36" s="10" t="n"/>
@@ -12324,80 +12365,80 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>부채와자본총계</t>
+          <t>기타자본</t>
         </is>
       </c>
       <c r="E37" s="18" t="n">
-        <v>260003.39</v>
+        <v>-2586.62</v>
       </c>
       <c r="F37" s="37" t="n">
-        <v>260003.39</v>
+        <v>-2586.62</v>
       </c>
       <c r="G37" s="18" t="n">
-        <v>258060.48</v>
+        <v>-2597.23</v>
       </c>
       <c r="H37" s="18" t="n">
-        <v>258810.24</v>
+        <v>-2562.52</v>
       </c>
       <c r="I37" s="18" t="n">
-        <v>262614.16</v>
+        <v>-2554.74</v>
       </c>
       <c r="J37" s="18" t="n">
-        <v>261112.52</v>
+        <v>-2541.49</v>
       </c>
       <c r="K37" s="37" t="n">
-        <v>261112.52</v>
+        <v>-2541.49</v>
       </c>
       <c r="L37" s="18" t="n">
-        <v>266270.17</v>
+        <v>-2581.8</v>
       </c>
       <c r="M37" s="18" t="n">
-        <v>279254.82</v>
+        <v>-3490.35</v>
       </c>
       <c r="N37" s="18" t="n">
-        <v>280285.66</v>
+        <v>-3523.92</v>
       </c>
       <c r="O37" s="18" t="n">
-        <v>297950.27</v>
+        <v>-3508.07</v>
       </c>
       <c r="P37" s="37" t="n">
-        <v>297950.27</v>
+        <v>-3508.07</v>
       </c>
       <c r="Q37" s="18" t="n">
-        <v>295957.58</v>
+        <v>-3509.47</v>
       </c>
       <c r="R37" s="18" t="n">
-        <v>302849.65</v>
+        <v>-3471.66</v>
       </c>
       <c r="S37" s="18" t="n">
-        <v>303664.4</v>
+        <v>-3455.64</v>
       </c>
       <c r="T37" s="18" t="n">
-        <v>308605.89</v>
+        <v>-3436.7</v>
       </c>
       <c r="U37" s="37" t="n">
-        <v>308605.89</v>
+        <v>-3436.7</v>
       </c>
       <c r="V37" s="18" t="n">
-        <v>310593.54</v>
+        <v>-3419.11</v>
       </c>
       <c r="W37" s="18" t="n">
-        <v>318841.75</v>
+        <v>-3374.2</v>
       </c>
       <c r="X37" s="18" t="n">
-        <v>319950.18</v>
+        <v>-3334.46</v>
       </c>
       <c r="Y37" s="18" t="n">
-        <v>321983.56</v>
+        <v>-3296.14</v>
       </c>
       <c r="Z37" s="37" t="n">
-        <v>321983.56</v>
+        <v>-3296.14</v>
       </c>
       <c r="AA37" s="18" t="n">
-        <v>332881.78</v>
+        <v>-3296.14</v>
       </c>
       <c r="AB37" s="19" t="n">
-        <v>346315.62</v>
+        <v>-2920.76</v>
       </c>
       <c r="AC37" s="10" t="n"/>
       <c r="AD37" s="10" t="n"/>
@@ -12419,80 +12460,80 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>이자발생자산</t>
+          <t>기타포괄이익누계액</t>
         </is>
       </c>
       <c r="E38" s="18" t="n">
-        <v>38439.6</v>
+        <v>9330.27</v>
       </c>
       <c r="F38" s="37" t="n">
-        <v>38439.6</v>
+        <v>9330.27</v>
       </c>
       <c r="G38" s="18" t="n">
-        <v>27317.76</v>
+        <v>9330.27</v>
       </c>
       <c r="H38" s="18" t="n">
-        <v>26668.27</v>
+        <v>9330.27</v>
       </c>
       <c r="I38" s="18" t="n">
-        <v>29176.22</v>
+        <v>9330.27</v>
       </c>
       <c r="J38" s="18" t="n">
-        <v>27883.82</v>
+        <v>9330.27</v>
       </c>
       <c r="K38" s="37" t="n">
-        <v>27883.82</v>
+        <v>9330.27</v>
       </c>
       <c r="L38" s="18" t="n">
-        <v>25275.5</v>
+        <v>9330.27</v>
       </c>
       <c r="M38" s="18" t="n">
-        <v>31968.84</v>
+        <v>9330.27</v>
       </c>
       <c r="N38" s="18" t="n">
-        <v>21958.54</v>
+        <v>9330.27</v>
       </c>
       <c r="O38" s="18" t="n">
-        <v>39294.44</v>
+        <v>9330.27</v>
       </c>
       <c r="P38" s="37" t="n">
-        <v>39294.44</v>
+        <v>9330.27</v>
       </c>
       <c r="Q38" s="18" t="n">
-        <v>30995.1</v>
+        <v>9330.27</v>
       </c>
       <c r="R38" s="18" t="n">
-        <v>34067.27</v>
+        <v>9330.27</v>
       </c>
       <c r="S38" s="18" t="n">
-        <v>35879.5</v>
+        <v>9330.27</v>
       </c>
       <c r="T38" s="18" t="n">
-        <v>34949.76</v>
+        <v>9330.27</v>
       </c>
       <c r="U38" s="37" t="n">
-        <v>34949.76</v>
+        <v>9330.27</v>
       </c>
       <c r="V38" s="18" t="n">
-        <v>38014.46</v>
+        <v>9330.27</v>
       </c>
       <c r="W38" s="18" t="n">
-        <v>35112.52</v>
+        <v>9330.27</v>
       </c>
       <c r="X38" s="18" t="n">
-        <v>38137.1</v>
+        <v>9330.27</v>
       </c>
       <c r="Y38" s="18" t="n">
-        <v>57918.67</v>
+        <v>9330.27</v>
       </c>
       <c r="Z38" s="37" t="n">
-        <v>57918.67</v>
+        <v>9330.27</v>
       </c>
       <c r="AA38" s="18" t="n">
-        <v>52685.95</v>
+        <v>9330.27</v>
       </c>
       <c r="AB38" s="19" t="n">
-        <v>56501.41</v>
+        <v>9330.27</v>
       </c>
       <c r="AC38" s="10" t="n"/>
       <c r="AD38" s="10" t="n"/>
@@ -12514,49 +12555,80 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>기타비유동자산</t>
-        </is>
-      </c>
-      <c r="F39" s="9" t="n"/>
-      <c r="K39" s="9" t="n"/>
+          <t>이익잉여금</t>
+        </is>
+      </c>
+      <c r="E39" s="18" t="n">
+        <v>190204.06</v>
+      </c>
+      <c r="F39" s="37" t="n">
+        <v>190204.06</v>
+      </c>
+      <c r="G39" s="18" t="n">
+        <v>187582.23</v>
+      </c>
+      <c r="H39" s="18" t="n">
+        <v>186769.55</v>
+      </c>
+      <c r="I39" s="18" t="n">
+        <v>188792.37</v>
+      </c>
+      <c r="J39" s="18" t="n">
+        <v>181918.26</v>
+      </c>
+      <c r="K39" s="37" t="n">
+        <v>181918.26</v>
+      </c>
+      <c r="L39" s="18" t="n">
+        <v>183532.43</v>
+      </c>
+      <c r="M39" s="18" t="n">
+        <v>184484.32</v>
+      </c>
       <c r="N39" s="18" t="n">
-        <v>2.37</v>
+        <v>187477.48</v>
       </c>
       <c r="O39" s="18" t="n">
-        <v>2.11</v>
+        <v>190036.48</v>
       </c>
       <c r="P39" s="37" t="n">
-        <v>2.11</v>
+        <v>190036.48</v>
       </c>
       <c r="Q39" s="18" t="n">
-        <v>2.12</v>
+        <v>193729.59</v>
+      </c>
+      <c r="R39" s="18" t="n">
+        <v>197982.97</v>
+      </c>
+      <c r="S39" s="18" t="n">
+        <v>200510.88</v>
       </c>
       <c r="T39" s="18" t="n">
-        <v>1.06</v>
+        <v>209538.41</v>
       </c>
       <c r="U39" s="37" t="n">
-        <v>1.06</v>
+        <v>209538.41</v>
       </c>
       <c r="V39" s="18" t="n">
-        <v>1.06</v>
+        <v>214355.95</v>
       </c>
       <c r="W39" s="18" t="n">
-        <v>1.11</v>
+        <v>218635.81</v>
       </c>
       <c r="X39" s="18" t="n">
-        <v>1.67</v>
+        <v>226706.19</v>
       </c>
       <c r="Y39" s="18" t="n">
-        <v>402.55</v>
+        <v>233109.82</v>
       </c>
       <c r="Z39" s="37" t="n">
-        <v>402.55</v>
+        <v>233109.82</v>
       </c>
       <c r="AA39" s="18" t="n">
-        <v>337.96</v>
+        <v>238524.3</v>
       </c>
       <c r="AB39" s="19" t="n">
-        <v>368.35</v>
+        <v>246187.85</v>
       </c>
       <c r="AC39" s="10" t="n"/>
       <c r="AD39" s="10" t="n"/>
@@ -12578,37 +12650,68 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>기타비유동부채</t>
-        </is>
-      </c>
-      <c r="F40" s="9" t="n"/>
-      <c r="K40" s="9" t="n"/>
+          <t>비지배주주지분</t>
+        </is>
+      </c>
+      <c r="E40" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="N40" s="18" t="n">
-        <v>765.73</v>
+        <v>0</v>
       </c>
       <c r="O40" s="18" t="n">
-        <v>806.37</v>
+        <v>0</v>
       </c>
       <c r="P40" s="37" t="n">
-        <v>806.37</v>
+        <v>0</v>
       </c>
       <c r="Q40" s="18" t="n">
-        <v>804.0599999999999</v>
+        <v>0</v>
+      </c>
+      <c r="R40" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="T40" s="18" t="n">
-        <v>837.96</v>
+        <v>0</v>
       </c>
       <c r="U40" s="37" t="n">
-        <v>837.96</v>
+        <v>0</v>
       </c>
       <c r="V40" s="18" t="n">
-        <v>832.74</v>
+        <v>0</v>
       </c>
       <c r="W40" s="18" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="X40" s="18" t="n">
-        <v>747</v>
+        <v>0</v>
       </c>
       <c r="Z40" s="9" t="n"/>
       <c r="AB40" s="5" t="n"/>
@@ -12632,24 +12735,80 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>단기투자자산(공정가치)</t>
-        </is>
-      </c>
-      <c r="F41" s="9" t="n"/>
-      <c r="K41" s="9" t="n"/>
-      <c r="P41" s="9" t="n"/>
-      <c r="U41" s="9" t="n"/>
+          <t>자본총계</t>
+        </is>
+      </c>
+      <c r="E41" s="18" t="n">
+        <v>226690.06</v>
+      </c>
+      <c r="F41" s="37" t="n">
+        <v>226690.06</v>
+      </c>
+      <c r="G41" s="18" t="n">
+        <v>224073.78</v>
+      </c>
+      <c r="H41" s="18" t="n">
+        <v>223298.74</v>
+      </c>
+      <c r="I41" s="18" t="n">
+        <v>225329.35</v>
+      </c>
+      <c r="J41" s="18" t="n">
+        <v>218469.18</v>
+      </c>
+      <c r="K41" s="37" t="n">
+        <v>218469.18</v>
+      </c>
+      <c r="L41" s="18" t="n">
+        <v>220091.38</v>
+      </c>
+      <c r="M41" s="18" t="n">
+        <v>220142.81</v>
+      </c>
+      <c r="N41" s="18" t="n">
+        <v>223102.4</v>
+      </c>
+      <c r="O41" s="18" t="n">
+        <v>225677.81</v>
+      </c>
+      <c r="P41" s="37" t="n">
+        <v>225677.81</v>
+      </c>
+      <c r="Q41" s="18" t="n">
+        <v>229382.89</v>
+      </c>
+      <c r="R41" s="18" t="n">
+        <v>233678.36</v>
+      </c>
+      <c r="S41" s="18" t="n">
+        <v>236222.29</v>
+      </c>
+      <c r="T41" s="18" t="n">
+        <v>245268.75</v>
+      </c>
+      <c r="U41" s="37" t="n">
+        <v>245268.75</v>
+      </c>
+      <c r="V41" s="18" t="n">
+        <v>250103.88</v>
+      </c>
+      <c r="W41" s="18" t="n">
+        <v>254461.61</v>
+      </c>
+      <c r="X41" s="18" t="n">
+        <v>262571.73</v>
+      </c>
       <c r="Y41" s="18" t="n">
-        <v>34769.73</v>
+        <v>269199.84</v>
       </c>
       <c r="Z41" s="37" t="n">
-        <v>34769.73</v>
+        <v>269199.84</v>
       </c>
       <c r="AA41" s="18" t="n">
-        <v>40501.05</v>
+        <v>274614.32</v>
       </c>
       <c r="AB41" s="19" t="n">
-        <v>30461.19</v>
+        <v>277841.22</v>
       </c>
       <c r="AC41" s="10" t="n"/>
       <c r="AD41" s="10" t="n"/>
@@ -12671,24 +12830,80 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>기타유동자산</t>
-        </is>
-      </c>
-      <c r="F42" s="9" t="n"/>
-      <c r="K42" s="9" t="n"/>
-      <c r="P42" s="9" t="n"/>
-      <c r="U42" s="9" t="n"/>
+          <t>부채와자본총계</t>
+        </is>
+      </c>
+      <c r="E42" s="18" t="n">
+        <v>260003.39</v>
+      </c>
+      <c r="F42" s="37" t="n">
+        <v>260003.39</v>
+      </c>
+      <c r="G42" s="18" t="n">
+        <v>258060.48</v>
+      </c>
+      <c r="H42" s="18" t="n">
+        <v>258810.24</v>
+      </c>
+      <c r="I42" s="18" t="n">
+        <v>262614.16</v>
+      </c>
+      <c r="J42" s="18" t="n">
+        <v>261112.52</v>
+      </c>
+      <c r="K42" s="37" t="n">
+        <v>261112.52</v>
+      </c>
+      <c r="L42" s="18" t="n">
+        <v>266270.17</v>
+      </c>
+      <c r="M42" s="18" t="n">
+        <v>279254.82</v>
+      </c>
+      <c r="N42" s="18" t="n">
+        <v>280285.66</v>
+      </c>
+      <c r="O42" s="18" t="n">
+        <v>297950.27</v>
+      </c>
+      <c r="P42" s="37" t="n">
+        <v>297950.27</v>
+      </c>
+      <c r="Q42" s="18" t="n">
+        <v>295957.58</v>
+      </c>
+      <c r="R42" s="18" t="n">
+        <v>302849.65</v>
+      </c>
+      <c r="S42" s="18" t="n">
+        <v>303664.4</v>
+      </c>
+      <c r="T42" s="18" t="n">
+        <v>308605.89</v>
+      </c>
+      <c r="U42" s="37" t="n">
+        <v>308605.89</v>
+      </c>
+      <c r="V42" s="18" t="n">
+        <v>310593.54</v>
+      </c>
+      <c r="W42" s="18" t="n">
+        <v>318841.75</v>
+      </c>
+      <c r="X42" s="18" t="n">
+        <v>319950.18</v>
+      </c>
       <c r="Y42" s="18" t="n">
-        <v>19076.58</v>
+        <v>321983.56</v>
       </c>
       <c r="Z42" s="37" t="n">
-        <v>19076.58</v>
+        <v>321983.56</v>
       </c>
       <c r="AA42" s="18" t="n">
-        <v>20414.41</v>
+        <v>332881.78</v>
       </c>
       <c r="AB42" s="19" t="n">
-        <v>15424.14</v>
+        <v>346315.62</v>
       </c>
       <c r="AC42" s="10" t="n"/>
       <c r="AD42" s="10" t="n"/>
@@ -12710,24 +12925,80 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>장기매출채권및기타채권</t>
-        </is>
-      </c>
-      <c r="F43" s="9" t="n"/>
-      <c r="K43" s="9" t="n"/>
-      <c r="P43" s="9" t="n"/>
-      <c r="U43" s="9" t="n"/>
+          <t>이자발생자산</t>
+        </is>
+      </c>
+      <c r="E43" s="18" t="n">
+        <v>78325.02</v>
+      </c>
+      <c r="F43" s="37" t="n">
+        <v>78325.02</v>
+      </c>
+      <c r="G43" s="18" t="n">
+        <v>71153.03</v>
+      </c>
+      <c r="H43" s="18" t="n">
+        <v>68486.91</v>
+      </c>
+      <c r="I43" s="18" t="n">
+        <v>70911.66</v>
+      </c>
+      <c r="J43" s="18" t="n">
+        <v>69037.23</v>
+      </c>
+      <c r="K43" s="37" t="n">
+        <v>69037.23</v>
+      </c>
+      <c r="L43" s="18" t="n">
+        <v>67633.46000000001</v>
+      </c>
+      <c r="M43" s="18" t="n">
+        <v>74759.23</v>
+      </c>
+      <c r="N43" s="18" t="n">
+        <v>67209.52</v>
+      </c>
+      <c r="O43" s="18" t="n">
+        <v>85996.46000000001</v>
+      </c>
+      <c r="P43" s="37" t="n">
+        <v>85996.46000000001</v>
+      </c>
+      <c r="Q43" s="18" t="n">
+        <v>78135.75999999999</v>
+      </c>
+      <c r="R43" s="18" t="n">
+        <v>81614.74000000001</v>
+      </c>
+      <c r="S43" s="18" t="n">
+        <v>83551.78</v>
+      </c>
+      <c r="T43" s="18" t="n">
+        <v>76497.92999999999</v>
+      </c>
+      <c r="U43" s="37" t="n">
+        <v>76497.92999999999</v>
+      </c>
+      <c r="V43" s="18" t="n">
+        <v>65630.59</v>
+      </c>
+      <c r="W43" s="18" t="n">
+        <v>47863.86</v>
+      </c>
+      <c r="X43" s="18" t="n">
+        <v>51582.14</v>
+      </c>
       <c r="Y43" s="18" t="n">
-        <v>809.54</v>
+        <v>57918.67</v>
       </c>
       <c r="Z43" s="37" t="n">
-        <v>809.54</v>
+        <v>57918.67</v>
       </c>
       <c r="AA43" s="18" t="n">
-        <v>922.35</v>
+        <v>52685.95</v>
       </c>
       <c r="AB43" s="19" t="n">
-        <v>1030.21</v>
+        <v>56501.41</v>
       </c>
       <c r="AC43" s="10" t="n"/>
       <c r="AD43" s="10" t="n"/>
@@ -12749,24 +13020,49 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>장기금융자산</t>
+          <t>기타비유동자산</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
       <c r="K44" s="9" t="n"/>
-      <c r="P44" s="9" t="n"/>
-      <c r="U44" s="9" t="n"/>
+      <c r="N44" s="18" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O44" s="18" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="P44" s="37" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q44" s="18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T44" s="18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="U44" s="37" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V44" s="18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W44" s="18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X44" s="18" t="n">
+        <v>1.67</v>
+      </c>
       <c r="Y44" s="18" t="n">
-        <v>14471.83</v>
+        <v>402.55</v>
       </c>
       <c r="Z44" s="37" t="n">
-        <v>14471.83</v>
+        <v>402.55</v>
       </c>
       <c r="AA44" s="18" t="n">
-        <v>9497.84</v>
+        <v>337.96</v>
       </c>
       <c r="AB44" s="19" t="n">
-        <v>12248.24</v>
+        <v>368.35</v>
       </c>
       <c r="AC44" s="10" t="n"/>
       <c r="AD44" s="10" t="n"/>
@@ -12788,25 +13084,40 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>투자자산</t>
+          <t>기타비유동부채</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
       <c r="K45" s="9" t="n"/>
-      <c r="P45" s="9" t="n"/>
-      <c r="U45" s="9" t="n"/>
-      <c r="Y45" s="18" t="n">
-        <v>14471.83</v>
-      </c>
-      <c r="Z45" s="37" t="n">
-        <v>14471.83</v>
-      </c>
-      <c r="AA45" s="18" t="n">
-        <v>9497.84</v>
-      </c>
-      <c r="AB45" s="19" t="n">
-        <v>12248.24</v>
-      </c>
+      <c r="N45" s="18" t="n">
+        <v>765.73</v>
+      </c>
+      <c r="O45" s="18" t="n">
+        <v>806.37</v>
+      </c>
+      <c r="P45" s="37" t="n">
+        <v>806.37</v>
+      </c>
+      <c r="Q45" s="18" t="n">
+        <v>804.0599999999999</v>
+      </c>
+      <c r="T45" s="18" t="n">
+        <v>837.96</v>
+      </c>
+      <c r="U45" s="37" t="n">
+        <v>837.96</v>
+      </c>
+      <c r="V45" s="18" t="n">
+        <v>832.74</v>
+      </c>
+      <c r="W45" s="18" t="n">
+        <v>290</v>
+      </c>
+      <c r="X45" s="18" t="n">
+        <v>747</v>
+      </c>
+      <c r="Z45" s="9" t="n"/>
+      <c r="AB45" s="5" t="n"/>
       <c r="AC45" s="10" t="n"/>
       <c r="AD45" s="10" t="n"/>
       <c r="AE45" s="11" t="n"/>
@@ -12827,7 +13138,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>사용권자산</t>
+          <t>기타유동자산</t>
         </is>
       </c>
       <c r="F46" s="9" t="n"/>
@@ -12835,16 +13146,16 @@
       <c r="P46" s="9" t="n"/>
       <c r="U46" s="9" t="n"/>
       <c r="Y46" s="18" t="n">
-        <v>401.66</v>
+        <v>19076.58</v>
       </c>
       <c r="Z46" s="37" t="n">
-        <v>401.66</v>
+        <v>19076.58</v>
       </c>
       <c r="AA46" s="18" t="n">
-        <v>337.07</v>
+        <v>20414.41</v>
       </c>
       <c r="AB46" s="19" t="n">
-        <v>367.46</v>
+        <v>15424.14</v>
       </c>
       <c r="AC46" s="10" t="n"/>
       <c r="AD46" s="10" t="n"/>
@@ -12866,7 +13177,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>기타유동부채</t>
+          <t>사용권자산</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -12874,16 +13185,16 @@
       <c r="P47" s="9" t="n"/>
       <c r="U47" s="9" t="n"/>
       <c r="Y47" s="18" t="n">
-        <v>25910.36</v>
+        <v>401.66</v>
       </c>
       <c r="Z47" s="37" t="n">
-        <v>25910.36</v>
+        <v>401.66</v>
       </c>
       <c r="AA47" s="18" t="n">
-        <v>23230.45</v>
+        <v>337.07</v>
       </c>
       <c r="AB47" s="19" t="n">
-        <v>34347.26</v>
+        <v>367.46</v>
       </c>
       <c r="AC47" s="10" t="n"/>
       <c r="AD47" s="10" t="n"/>
@@ -12905,7 +13216,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>비유동리스부채</t>
+          <t>기타유동부채</t>
         </is>
       </c>
       <c r="F48" s="9" t="n"/>
@@ -12913,16 +13224,16 @@
       <c r="P48" s="9" t="n"/>
       <c r="U48" s="9" t="n"/>
       <c r="Y48" s="18" t="n">
-        <v>163.37</v>
+        <v>25910.36</v>
       </c>
       <c r="Z48" s="37" t="n">
-        <v>163.37</v>
+        <v>25910.36</v>
       </c>
       <c r="AA48" s="18" t="n">
-        <v>110.57</v>
+        <v>23230.45</v>
       </c>
       <c r="AB48" s="19" t="n">
-        <v>93.43000000000001</v>
+        <v>34347.26</v>
       </c>
       <c r="AC48" s="10" t="n"/>
       <c r="AD48" s="10" t="n"/>
@@ -16254,7 +16565,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16857,80 +17168,80 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>기타유동금융자산</t>
+          <t>단기투자자산(공정가치)</t>
         </is>
       </c>
       <c r="E8" s="18" t="n">
-        <v>7924.02</v>
+        <v>4185.91</v>
       </c>
       <c r="F8" s="37" t="n">
-        <v>7924.02</v>
+        <v>4185.91</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>26053.09</v>
+        <v>4275.47</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>26141.43</v>
+        <v>6559.14</v>
       </c>
       <c r="I8" s="18" t="n">
-        <v>26208.01</v>
+        <v>7250.59</v>
       </c>
       <c r="J8" s="18" t="n">
-        <v>27338.3</v>
+        <v>10352.3</v>
       </c>
       <c r="K8" s="37" t="n">
-        <v>27338.3</v>
+        <v>10352.3</v>
       </c>
       <c r="L8" s="18" t="n">
-        <v>27489.55</v>
+        <v>10706.2</v>
       </c>
       <c r="M8" s="18" t="n">
-        <v>27142.21</v>
+        <v>10835</v>
       </c>
       <c r="N8" s="18" t="n">
-        <v>27311.73</v>
+        <v>8371.18</v>
       </c>
       <c r="O8" s="18" t="n">
-        <v>27025.47</v>
+        <v>4097.66</v>
       </c>
       <c r="P8" s="37" t="n">
-        <v>27025.47</v>
+        <v>4097.66</v>
       </c>
       <c r="Q8" s="18" t="n">
-        <v>27246.94</v>
+        <v>4281.83</v>
       </c>
       <c r="R8" s="18" t="n">
-        <v>27459.82</v>
+        <v>4466.09</v>
       </c>
       <c r="S8" s="18" t="n">
-        <v>27670.39</v>
+        <v>4288.21</v>
       </c>
       <c r="T8" s="18" t="n">
-        <v>27890.26</v>
+        <v>12155.52</v>
       </c>
       <c r="U8" s="37" t="n">
-        <v>27890.26</v>
+        <v>12155.52</v>
       </c>
       <c r="V8" s="18" t="n">
-        <v>28128.24</v>
+        <v>24521.68</v>
       </c>
       <c r="W8" s="18" t="n">
-        <v>28592.47</v>
+        <v>38933.25</v>
       </c>
       <c r="X8" s="18" t="n">
-        <v>32626.91</v>
+        <v>34460.12</v>
       </c>
       <c r="Y8" s="18" t="n">
-        <v>32752.46</v>
+        <v>34769.73</v>
       </c>
       <c r="Z8" s="37" t="n">
-        <v>32752.46</v>
+        <v>34769.73</v>
       </c>
       <c r="AA8" s="18" t="n">
-        <v>32878.85</v>
+        <v>40501.05</v>
       </c>
       <c r="AB8" s="19" t="n">
-        <v>32884.83</v>
+        <v>19876.64</v>
       </c>
       <c r="AC8" s="10" t="n"/>
       <c r="AD8" s="10" t="n"/>
@@ -16952,70 +17263,81 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>당기법인세자산(선급법인세)</t>
+          <t>기타유동금융자산</t>
         </is>
       </c>
       <c r="E9" s="18" t="n">
-        <v>423.54</v>
+        <v>7924.02</v>
       </c>
       <c r="F9" s="37" t="n">
-        <v>423.54</v>
+        <v>7924.02</v>
       </c>
       <c r="G9" s="18" t="n">
-        <v>423.54</v>
+        <v>26053.09</v>
       </c>
       <c r="H9" s="18" t="n">
-        <v>105.24</v>
+        <v>26141.43</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>163.09</v>
+        <v>26208.01</v>
       </c>
       <c r="J9" s="18" t="n">
-        <v>240.55</v>
+        <v>27338.3</v>
       </c>
       <c r="K9" s="37" t="n">
-        <v>240.55</v>
+        <v>27338.3</v>
       </c>
       <c r="L9" s="18" t="n">
-        <v>397.28</v>
+        <v>27489.55</v>
       </c>
       <c r="M9" s="18" t="n">
-        <v>273.19</v>
+        <v>27142.21</v>
       </c>
       <c r="N9" s="18" t="n">
-        <v>351.91</v>
+        <v>27311.73</v>
       </c>
       <c r="O9" s="18" t="n">
-        <v>2.45</v>
+        <v>27025.47</v>
       </c>
       <c r="P9" s="37" t="n">
-        <v>2.45</v>
+        <v>27025.47</v>
       </c>
       <c r="Q9" s="18" t="n">
-        <v>2.45</v>
+        <v>27246.94</v>
       </c>
       <c r="R9" s="18" t="n">
-        <v>0</v>
+        <v>27459.82</v>
       </c>
       <c r="S9" s="18" t="n">
-        <v>0</v>
+        <v>27670.39</v>
       </c>
       <c r="T9" s="18" t="n">
-        <v>0</v>
+        <v>27890.26</v>
       </c>
       <c r="U9" s="37" t="n">
-        <v>0</v>
+        <v>27890.26</v>
+      </c>
+      <c r="V9" s="18" t="n">
+        <v>28128.24</v>
+      </c>
+      <c r="W9" s="18" t="n">
+        <v>28592.47</v>
+      </c>
+      <c r="X9" s="18" t="n">
+        <v>32626.91</v>
       </c>
       <c r="Y9" s="18" t="n">
-        <v>0</v>
+        <v>32752.46</v>
       </c>
       <c r="Z9" s="37" t="n">
-        <v>0</v>
+        <v>32752.46</v>
       </c>
       <c r="AA9" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="5" t="n"/>
+        <v>32878.85</v>
+      </c>
+      <c r="AB9" s="19" t="n">
+        <v>32884.83</v>
+      </c>
       <c r="AC9" s="10" t="n"/>
       <c r="AD9" s="10" t="n"/>
       <c r="AE9" s="11" t="n"/>
@@ -17036,81 +17358,70 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>재고자산</t>
+          <t>당기법인세자산(선급법인세)</t>
         </is>
       </c>
       <c r="E10" s="18" t="n">
-        <v>26699.72</v>
+        <v>423.54</v>
       </c>
       <c r="F10" s="37" t="n">
-        <v>26699.72</v>
+        <v>423.54</v>
       </c>
       <c r="G10" s="18" t="n">
-        <v>24665.28</v>
+        <v>423.54</v>
       </c>
       <c r="H10" s="18" t="n">
-        <v>25399.1</v>
+        <v>105.24</v>
       </c>
       <c r="I10" s="18" t="n">
-        <v>28173.54</v>
+        <v>163.09</v>
       </c>
       <c r="J10" s="18" t="n">
-        <v>23035.99</v>
+        <v>240.55</v>
       </c>
       <c r="K10" s="37" t="n">
-        <v>23035.99</v>
+        <v>240.55</v>
       </c>
       <c r="L10" s="18" t="n">
-        <v>26098.23</v>
+        <v>397.28</v>
       </c>
       <c r="M10" s="18" t="n">
-        <v>31202.1</v>
+        <v>273.19</v>
       </c>
       <c r="N10" s="18" t="n">
-        <v>35096.88</v>
+        <v>351.91</v>
       </c>
       <c r="O10" s="18" t="n">
-        <v>35944.53</v>
+        <v>2.45</v>
       </c>
       <c r="P10" s="37" t="n">
-        <v>35944.53</v>
+        <v>2.45</v>
       </c>
       <c r="Q10" s="18" t="n">
-        <v>41530.27</v>
+        <v>2.45</v>
       </c>
       <c r="R10" s="18" t="n">
-        <v>39486.88</v>
+        <v>0</v>
       </c>
       <c r="S10" s="18" t="n">
-        <v>39695.24</v>
+        <v>0</v>
       </c>
       <c r="T10" s="18" t="n">
-        <v>35108.31</v>
+        <v>0</v>
       </c>
       <c r="U10" s="37" t="n">
-        <v>35108.31</v>
-      </c>
-      <c r="V10" s="18" t="n">
-        <v>37816.22</v>
-      </c>
-      <c r="W10" s="18" t="n">
-        <v>39994.42</v>
-      </c>
-      <c r="X10" s="18" t="n">
-        <v>36993.11</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="18" t="n">
-        <v>32674.91</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="37" t="n">
-        <v>32674.91</v>
+        <v>0</v>
       </c>
       <c r="AA10" s="18" t="n">
-        <v>45381.18</v>
-      </c>
-      <c r="AB10" s="19" t="n">
-        <v>40269.66</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB10" s="5" t="n"/>
       <c r="AC10" s="10" t="n"/>
       <c r="AD10" s="10" t="n"/>
       <c r="AE10" s="11" t="n"/>
@@ -17131,28 +17442,81 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>매각예정비유동자산및처분자산</t>
+          <t>재고자산</t>
         </is>
       </c>
       <c r="E11" s="18" t="n">
-        <v>0</v>
+        <v>26699.72</v>
       </c>
       <c r="F11" s="37" t="n">
-        <v>0</v>
+        <v>26699.72</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>24665.28</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>25399.1</v>
+      </c>
+      <c r="I11" s="18" t="n">
+        <v>28173.54</v>
       </c>
       <c r="J11" s="18" t="n">
-        <v>0</v>
+        <v>23035.99</v>
       </c>
       <c r="K11" s="37" t="n">
-        <v>0</v>
+        <v>23035.99</v>
       </c>
       <c r="L11" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="9" t="n"/>
-      <c r="U11" s="9" t="n"/>
-      <c r="Z11" s="9" t="n"/>
-      <c r="AB11" s="5" t="n"/>
+        <v>26098.23</v>
+      </c>
+      <c r="M11" s="18" t="n">
+        <v>31202.1</v>
+      </c>
+      <c r="N11" s="18" t="n">
+        <v>35096.88</v>
+      </c>
+      <c r="O11" s="18" t="n">
+        <v>35944.53</v>
+      </c>
+      <c r="P11" s="37" t="n">
+        <v>35944.53</v>
+      </c>
+      <c r="Q11" s="18" t="n">
+        <v>41530.27</v>
+      </c>
+      <c r="R11" s="18" t="n">
+        <v>39486.88</v>
+      </c>
+      <c r="S11" s="18" t="n">
+        <v>39695.24</v>
+      </c>
+      <c r="T11" s="18" t="n">
+        <v>35108.31</v>
+      </c>
+      <c r="U11" s="37" t="n">
+        <v>35108.31</v>
+      </c>
+      <c r="V11" s="18" t="n">
+        <v>37816.22</v>
+      </c>
+      <c r="W11" s="18" t="n">
+        <v>39994.42</v>
+      </c>
+      <c r="X11" s="18" t="n">
+        <v>36993.11</v>
+      </c>
+      <c r="Y11" s="18" t="n">
+        <v>32674.91</v>
+      </c>
+      <c r="Z11" s="37" t="n">
+        <v>32674.91</v>
+      </c>
+      <c r="AA11" s="18" t="n">
+        <v>45381.18</v>
+      </c>
+      <c r="AB11" s="19" t="n">
+        <v>40269.66</v>
+      </c>
       <c r="AC11" s="10" t="n"/>
       <c r="AD11" s="10" t="n"/>
       <c r="AE11" s="11" t="n"/>
@@ -17173,81 +17537,28 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>비유동자산</t>
+          <t>매각예정비유동자산및처분자산</t>
         </is>
       </c>
       <c r="E12" s="18" t="n">
-        <v>144259.07</v>
+        <v>0</v>
       </c>
       <c r="F12" s="37" t="n">
-        <v>144259.07</v>
-      </c>
-      <c r="G12" s="18" t="n">
-        <v>134398.19</v>
-      </c>
-      <c r="H12" s="18" t="n">
-        <v>134025.69</v>
-      </c>
-      <c r="I12" s="18" t="n">
-        <v>133693.72</v>
+        <v>0</v>
       </c>
       <c r="J12" s="18" t="n">
-        <v>132870.06</v>
+        <v>0</v>
       </c>
       <c r="K12" s="37" t="n">
-        <v>132870.06</v>
+        <v>0</v>
       </c>
       <c r="L12" s="18" t="n">
-        <v>133144.53</v>
-      </c>
-      <c r="M12" s="18" t="n">
-        <v>137123.73</v>
-      </c>
-      <c r="N12" s="18" t="n">
-        <v>140917.65</v>
-      </c>
-      <c r="O12" s="18" t="n">
-        <v>144350.37</v>
-      </c>
-      <c r="P12" s="37" t="n">
-        <v>144350.37</v>
-      </c>
-      <c r="Q12" s="18" t="n">
-        <v>143607.76</v>
-      </c>
-      <c r="R12" s="18" t="n">
-        <v>146306.52</v>
-      </c>
-      <c r="S12" s="18" t="n">
-        <v>144885.84</v>
-      </c>
-      <c r="T12" s="18" t="n">
-        <v>139692.58</v>
-      </c>
-      <c r="U12" s="37" t="n">
-        <v>139692.58</v>
-      </c>
-      <c r="V12" s="18" t="n">
-        <v>126029.11</v>
-      </c>
-      <c r="W12" s="18" t="n">
-        <v>114345.29</v>
-      </c>
-      <c r="X12" s="18" t="n">
-        <v>114593.24</v>
-      </c>
-      <c r="Y12" s="18" t="n">
-        <v>113487.44</v>
-      </c>
-      <c r="Z12" s="37" t="n">
-        <v>113487.44</v>
-      </c>
-      <c r="AA12" s="18" t="n">
-        <v>107459.24</v>
-      </c>
-      <c r="AB12" s="19" t="n">
-        <v>148609.85</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P12" s="9" t="n"/>
+      <c r="U12" s="9" t="n"/>
+      <c r="Z12" s="9" t="n"/>
+      <c r="AB12" s="5" t="n"/>
       <c r="AC12" s="10" t="n"/>
       <c r="AD12" s="10" t="n"/>
       <c r="AE12" s="11" t="n"/>
@@ -17268,80 +17579,80 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>종속기업및관계기업투자</t>
+          <t>비유동자산</t>
         </is>
       </c>
       <c r="E13" s="18" t="n">
-        <v>8000</v>
+        <v>144259.07</v>
       </c>
       <c r="F13" s="37" t="n">
-        <v>8000</v>
+        <v>144259.07</v>
       </c>
       <c r="G13" s="18" t="n">
-        <v>8000</v>
+        <v>134398.19</v>
       </c>
       <c r="H13" s="18" t="n">
-        <v>8000</v>
+        <v>134025.69</v>
       </c>
       <c r="I13" s="18" t="n">
-        <v>8000</v>
+        <v>133693.72</v>
       </c>
       <c r="J13" s="18" t="n">
-        <v>8000</v>
+        <v>132870.06</v>
       </c>
       <c r="K13" s="37" t="n">
-        <v>8000</v>
+        <v>132870.06</v>
       </c>
       <c r="L13" s="18" t="n">
-        <v>8000</v>
+        <v>133144.53</v>
       </c>
       <c r="M13" s="18" t="n">
-        <v>8000</v>
+        <v>137123.73</v>
       </c>
       <c r="N13" s="18" t="n">
-        <v>8000</v>
+        <v>140917.65</v>
       </c>
       <c r="O13" s="18" t="n">
-        <v>8000</v>
+        <v>144350.37</v>
       </c>
       <c r="P13" s="37" t="n">
-        <v>8000</v>
+        <v>144350.37</v>
       </c>
       <c r="Q13" s="18" t="n">
-        <v>8000</v>
+        <v>143607.76</v>
       </c>
       <c r="R13" s="18" t="n">
-        <v>8000</v>
+        <v>146306.52</v>
       </c>
       <c r="S13" s="18" t="n">
-        <v>8000</v>
+        <v>144885.84</v>
       </c>
       <c r="T13" s="18" t="n">
-        <v>8000</v>
+        <v>139692.58</v>
       </c>
       <c r="U13" s="37" t="n">
-        <v>8000</v>
+        <v>139692.58</v>
       </c>
       <c r="V13" s="18" t="n">
-        <v>8000</v>
+        <v>126029.11</v>
       </c>
       <c r="W13" s="18" t="n">
-        <v>8000</v>
+        <v>114345.29</v>
       </c>
       <c r="X13" s="18" t="n">
-        <v>8000</v>
+        <v>114593.24</v>
       </c>
       <c r="Y13" s="18" t="n">
-        <v>8000</v>
+        <v>113487.44</v>
       </c>
       <c r="Z13" s="37" t="n">
-        <v>8000</v>
+        <v>113487.44</v>
       </c>
       <c r="AA13" s="18" t="n">
-        <v>8000</v>
+        <v>107459.24</v>
       </c>
       <c r="AB13" s="19" t="n">
-        <v>39955.08</v>
+        <v>148609.85</v>
       </c>
       <c r="AC13" s="10" t="n"/>
       <c r="AD13" s="10" t="n"/>
@@ -17363,80 +17674,80 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>투자자산</t>
+          <t>장기매출채권및기타채권</t>
         </is>
       </c>
       <c r="E14" s="18" t="n">
-        <v>8000</v>
+        <v>813.6900000000001</v>
       </c>
       <c r="F14" s="37" t="n">
-        <v>8000</v>
+        <v>813.6900000000001</v>
       </c>
       <c r="G14" s="18" t="n">
-        <v>8000</v>
+        <v>924.67</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>8000</v>
+        <v>1230.12</v>
       </c>
       <c r="I14" s="18" t="n">
-        <v>8000</v>
+        <v>1484.21</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>8000</v>
+        <v>81.14</v>
       </c>
       <c r="K14" s="37" t="n">
-        <v>8000</v>
+        <v>81.14</v>
       </c>
       <c r="L14" s="18" t="n">
-        <v>8000</v>
+        <v>37.83</v>
       </c>
       <c r="M14" s="18" t="n">
-        <v>8000</v>
+        <v>104.49</v>
       </c>
       <c r="N14" s="18" t="n">
-        <v>8000</v>
+        <v>177.2</v>
       </c>
       <c r="O14" s="18" t="n">
-        <v>8000</v>
+        <v>726.05</v>
       </c>
       <c r="P14" s="37" t="n">
-        <v>8000</v>
+        <v>726.05</v>
       </c>
       <c r="Q14" s="18" t="n">
-        <v>8000</v>
+        <v>1009.24</v>
       </c>
       <c r="R14" s="18" t="n">
-        <v>8000</v>
+        <v>1930.09</v>
       </c>
       <c r="S14" s="18" t="n">
-        <v>8000</v>
+        <v>611.4299999999999</v>
       </c>
       <c r="T14" s="18" t="n">
-        <v>8000</v>
+        <v>1662.41</v>
       </c>
       <c r="U14" s="37" t="n">
-        <v>8000</v>
+        <v>1662.41</v>
       </c>
       <c r="V14" s="18" t="n">
-        <v>8000</v>
+        <v>606.5700000000001</v>
       </c>
       <c r="W14" s="18" t="n">
-        <v>8000</v>
+        <v>1060.04</v>
       </c>
       <c r="X14" s="18" t="n">
-        <v>8000</v>
+        <v>1083.31</v>
       </c>
       <c r="Y14" s="18" t="n">
-        <v>21921.85</v>
+        <v>809.54</v>
       </c>
       <c r="Z14" s="37" t="n">
-        <v>21921.85</v>
+        <v>809.54</v>
       </c>
       <c r="AA14" s="18" t="n">
-        <v>16949.14</v>
+        <v>922.35</v>
       </c>
       <c r="AB14" s="19" t="n">
-        <v>49436.48</v>
+        <v>1030.21</v>
       </c>
       <c r="AC14" s="10" t="n"/>
       <c r="AD14" s="10" t="n"/>
@@ -17458,80 +17769,80 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>유형자산</t>
+          <t>장기금융자산</t>
         </is>
       </c>
       <c r="E15" s="18" t="n">
-        <v>70528</v>
+        <v>39580.42</v>
       </c>
       <c r="F15" s="37" t="n">
-        <v>70528</v>
+        <v>39580.42</v>
       </c>
       <c r="G15" s="18" t="n">
-        <v>74046.16</v>
+        <v>43530.27</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>75007.48</v>
+        <v>41513.64</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>75040.81</v>
+        <v>41430.44</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>74727.63</v>
+        <v>40848.41</v>
       </c>
       <c r="K15" s="37" t="n">
-        <v>74727.63</v>
+        <v>40848.41</v>
       </c>
       <c r="L15" s="18" t="n">
-        <v>74299.91</v>
+        <v>42052.96</v>
       </c>
       <c r="M15" s="18" t="n">
-        <v>77956.75999999999</v>
+        <v>42485.39</v>
       </c>
       <c r="N15" s="18" t="n">
-        <v>79991.78999999999</v>
+        <v>44945.98</v>
       </c>
       <c r="O15" s="18" t="n">
-        <v>81179.59</v>
+        <v>46172.47</v>
       </c>
       <c r="P15" s="37" t="n">
-        <v>81179.59</v>
+        <v>46172.47</v>
       </c>
       <c r="Q15" s="18" t="n">
-        <v>80387.2</v>
+        <v>46611.11</v>
       </c>
       <c r="R15" s="18" t="n">
-        <v>81383.59</v>
+        <v>47017.92</v>
       </c>
       <c r="S15" s="18" t="n">
-        <v>80801.12</v>
+        <v>47142.73</v>
       </c>
       <c r="T15" s="18" t="n">
-        <v>77890</v>
+        <v>41014.85</v>
       </c>
       <c r="U15" s="37" t="n">
-        <v>77890</v>
+        <v>41014.85</v>
       </c>
       <c r="V15" s="18" t="n">
-        <v>78572.48</v>
+        <v>27082.82</v>
       </c>
       <c r="W15" s="18" t="n">
-        <v>70839.60000000001</v>
+        <v>12218.02</v>
       </c>
       <c r="X15" s="18" t="n">
-        <v>70452.2</v>
+        <v>12911.72</v>
       </c>
       <c r="Y15" s="18" t="n">
-        <v>67447.06</v>
+        <v>13921.85</v>
       </c>
       <c r="Z15" s="37" t="n">
-        <v>67447.06</v>
+        <v>13921.85</v>
       </c>
       <c r="AA15" s="18" t="n">
-        <v>67153.91</v>
+        <v>8949.139999999999</v>
       </c>
       <c r="AB15" s="19" t="n">
-        <v>74798.10000000001</v>
+        <v>9481.4</v>
       </c>
       <c r="AC15" s="10" t="n"/>
       <c r="AD15" s="10" t="n"/>
@@ -17553,80 +17864,80 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>투자부동산</t>
+          <t>투자자산</t>
         </is>
       </c>
       <c r="E16" s="18" t="n">
-        <v>1876.49</v>
+        <v>47580.42</v>
       </c>
       <c r="F16" s="37" t="n">
-        <v>1876.49</v>
+        <v>47580.42</v>
       </c>
       <c r="G16" s="18" t="n">
-        <v>1863.36</v>
+        <v>51530.27</v>
       </c>
       <c r="H16" s="18" t="n">
-        <v>1850.22</v>
+        <v>49513.64</v>
       </c>
       <c r="I16" s="18" t="n">
-        <v>1837.08</v>
+        <v>49430.44</v>
       </c>
       <c r="J16" s="18" t="n">
-        <v>1906.88</v>
+        <v>48848.41</v>
       </c>
       <c r="K16" s="37" t="n">
-        <v>1906.88</v>
+        <v>48848.41</v>
       </c>
       <c r="L16" s="18" t="n">
-        <v>1897.7</v>
+        <v>50052.96</v>
       </c>
       <c r="M16" s="18" t="n">
-        <v>1888.53</v>
+        <v>50485.39</v>
       </c>
       <c r="N16" s="18" t="n">
-        <v>1879.36</v>
+        <v>52945.98</v>
       </c>
       <c r="O16" s="18" t="n">
-        <v>1870.19</v>
+        <v>54172.47</v>
       </c>
       <c r="P16" s="37" t="n">
-        <v>1870.19</v>
+        <v>54172.47</v>
       </c>
       <c r="Q16" s="18" t="n">
-        <v>1861.01</v>
+        <v>54611.11</v>
       </c>
       <c r="R16" s="18" t="n">
-        <v>1851.84</v>
+        <v>55017.92</v>
       </c>
       <c r="S16" s="18" t="n">
-        <v>1842.67</v>
+        <v>55142.73</v>
       </c>
       <c r="T16" s="18" t="n">
-        <v>5487.18</v>
+        <v>49014.85</v>
       </c>
       <c r="U16" s="37" t="n">
-        <v>5487.18</v>
+        <v>49014.85</v>
       </c>
       <c r="V16" s="18" t="n">
-        <v>5470.99</v>
+        <v>35082.82</v>
       </c>
       <c r="W16" s="18" t="n">
-        <v>15642.89</v>
+        <v>20218.02</v>
       </c>
       <c r="X16" s="18" t="n">
-        <v>15623.2</v>
+        <v>20911.72</v>
       </c>
       <c r="Y16" s="18" t="n">
-        <v>18244.34</v>
+        <v>21921.85</v>
       </c>
       <c r="Z16" s="37" t="n">
-        <v>18244.34</v>
+        <v>21921.85</v>
       </c>
       <c r="AA16" s="18" t="n">
-        <v>18210.59</v>
+        <v>16949.14</v>
       </c>
       <c r="AB16" s="19" t="n">
-        <v>18190.73</v>
+        <v>49436.48</v>
       </c>
       <c r="AC16" s="10" t="n"/>
       <c r="AD16" s="10" t="n"/>
@@ -17648,80 +17959,80 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>무형자산</t>
+          <t>종속기업및관계기업투자</t>
         </is>
       </c>
       <c r="E17" s="18" t="n">
-        <v>1410.97</v>
+        <v>8000</v>
       </c>
       <c r="F17" s="37" t="n">
-        <v>1410.97</v>
+        <v>8000</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>1354.67</v>
+        <v>8000</v>
       </c>
       <c r="H17" s="18" t="n">
-        <v>1293.55</v>
+        <v>8000</v>
       </c>
       <c r="I17" s="18" t="n">
-        <v>1263.99</v>
+        <v>8000</v>
       </c>
       <c r="J17" s="18" t="n">
-        <v>1212.83</v>
+        <v>8000</v>
       </c>
       <c r="K17" s="37" t="n">
-        <v>1212.83</v>
+        <v>8000</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>1150.79</v>
+        <v>8000</v>
       </c>
       <c r="M17" s="18" t="n">
-        <v>1101.94</v>
+        <v>8000</v>
       </c>
       <c r="N17" s="18" t="n">
-        <v>1040.07</v>
+        <v>8000</v>
       </c>
       <c r="O17" s="18" t="n">
-        <v>993.78</v>
+        <v>8000</v>
       </c>
       <c r="P17" s="37" t="n">
-        <v>993.78</v>
+        <v>8000</v>
       </c>
       <c r="Q17" s="18" t="n">
-        <v>981.1900000000001</v>
+        <v>8000</v>
       </c>
       <c r="R17" s="18" t="n">
-        <v>961.1</v>
+        <v>8000</v>
       </c>
       <c r="S17" s="18" t="n">
-        <v>952.46</v>
+        <v>8000</v>
       </c>
       <c r="T17" s="18" t="n">
-        <v>943.05</v>
+        <v>8000</v>
       </c>
       <c r="U17" s="37" t="n">
-        <v>943.05</v>
+        <v>8000</v>
       </c>
       <c r="V17" s="18" t="n">
-        <v>947.13</v>
+        <v>8000</v>
       </c>
       <c r="W17" s="18" t="n">
-        <v>1250.01</v>
+        <v>8000</v>
       </c>
       <c r="X17" s="18" t="n">
-        <v>1241.37</v>
+        <v>8000</v>
       </c>
       <c r="Y17" s="18" t="n">
-        <v>1244.76</v>
+        <v>8000</v>
       </c>
       <c r="Z17" s="37" t="n">
-        <v>1244.76</v>
+        <v>8000</v>
       </c>
       <c r="AA17" s="18" t="n">
-        <v>1251.67</v>
+        <v>8000</v>
       </c>
       <c r="AB17" s="19" t="n">
-        <v>1270.71</v>
+        <v>39955.08</v>
       </c>
       <c r="AC17" s="10" t="n"/>
       <c r="AD17" s="10" t="n"/>
@@ -17743,80 +18054,80 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>이연법인세자산</t>
+          <t>유형자산</t>
         </is>
       </c>
       <c r="E18" s="18" t="n">
-        <v>802.05</v>
+        <v>70528</v>
       </c>
       <c r="F18" s="37" t="n">
-        <v>802.05</v>
+        <v>70528</v>
       </c>
       <c r="G18" s="18" t="n">
-        <v>1284.25</v>
+        <v>74046.16</v>
       </c>
       <c r="H18" s="18" t="n">
-        <v>1731.67</v>
+        <v>75007.48</v>
       </c>
       <c r="I18" s="18" t="n">
-        <v>1233.96</v>
+        <v>75040.81</v>
       </c>
       <c r="J18" s="18" t="n">
-        <v>3762.71</v>
+        <v>74727.63</v>
       </c>
       <c r="K18" s="37" t="n">
-        <v>3762.71</v>
+        <v>74727.63</v>
       </c>
       <c r="L18" s="18" t="n">
-        <v>3392.41</v>
+        <v>74299.91</v>
       </c>
       <c r="M18" s="18" t="n">
-        <v>3217.04</v>
+        <v>77956.75999999999</v>
       </c>
       <c r="N18" s="18" t="n">
-        <v>2544.4</v>
+        <v>79991.78999999999</v>
       </c>
       <c r="O18" s="18" t="n">
-        <v>2882.6</v>
+        <v>81179.59</v>
       </c>
       <c r="P18" s="37" t="n">
-        <v>2882.6</v>
+        <v>81179.59</v>
       </c>
       <c r="Q18" s="18" t="n">
-        <v>2316.57</v>
+        <v>80387.2</v>
       </c>
       <c r="R18" s="18" t="n">
-        <v>2461.18</v>
+        <v>81383.59</v>
       </c>
       <c r="S18" s="18" t="n">
-        <v>2689.66</v>
+        <v>80801.12</v>
       </c>
       <c r="T18" s="18" t="n">
-        <v>1967.58</v>
+        <v>77890</v>
       </c>
       <c r="U18" s="37" t="n">
-        <v>1967.58</v>
+        <v>77890</v>
       </c>
       <c r="V18" s="18" t="n">
-        <v>2803.15</v>
+        <v>78572.48</v>
       </c>
       <c r="W18" s="18" t="n">
-        <v>2987.19</v>
+        <v>70839.60000000001</v>
       </c>
       <c r="X18" s="18" t="n">
-        <v>2908.61</v>
+        <v>70452.2</v>
       </c>
       <c r="Y18" s="18" t="n">
-        <v>3418.23</v>
+        <v>67447.06</v>
       </c>
       <c r="Z18" s="37" t="n">
-        <v>3418.23</v>
+        <v>67447.06</v>
       </c>
       <c r="AA18" s="18" t="n">
-        <v>2634.51</v>
+        <v>67153.91</v>
       </c>
       <c r="AB18" s="19" t="n">
-        <v>3522.74</v>
+        <v>74798.10000000001</v>
       </c>
       <c r="AC18" s="10" t="n"/>
       <c r="AD18" s="10" t="n"/>
@@ -17838,80 +18149,80 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>자산총계</t>
+          <t>투자부동산</t>
         </is>
       </c>
       <c r="E19" s="18" t="n">
-        <v>241431.73</v>
+        <v>1876.49</v>
       </c>
       <c r="F19" s="37" t="n">
-        <v>241431.73</v>
+        <v>1876.49</v>
       </c>
       <c r="G19" s="18" t="n">
-        <v>236928.74</v>
+        <v>1863.36</v>
       </c>
       <c r="H19" s="18" t="n">
-        <v>238045.93</v>
+        <v>1850.22</v>
       </c>
       <c r="I19" s="18" t="n">
-        <v>242021.41</v>
+        <v>1837.08</v>
       </c>
       <c r="J19" s="18" t="n">
-        <v>239085.99</v>
+        <v>1906.88</v>
       </c>
       <c r="K19" s="37" t="n">
-        <v>239085.99</v>
+        <v>1906.88</v>
       </c>
       <c r="L19" s="18" t="n">
-        <v>245766.22</v>
+        <v>1897.7</v>
       </c>
       <c r="M19" s="18" t="n">
-        <v>259016.44</v>
+        <v>1888.53</v>
       </c>
       <c r="N19" s="18" t="n">
-        <v>261330.87</v>
+        <v>1879.36</v>
       </c>
       <c r="O19" s="18" t="n">
-        <v>275699.82</v>
+        <v>1870.19</v>
       </c>
       <c r="P19" s="37" t="n">
-        <v>275699.82</v>
+        <v>1870.19</v>
       </c>
       <c r="Q19" s="18" t="n">
-        <v>276591.11</v>
+        <v>1861.01</v>
       </c>
       <c r="R19" s="18" t="n">
-        <v>283216.57</v>
+        <v>1851.84</v>
       </c>
       <c r="S19" s="18" t="n">
-        <v>280780.74</v>
+        <v>1842.67</v>
       </c>
       <c r="T19" s="18" t="n">
-        <v>289770.81</v>
+        <v>5487.18</v>
       </c>
       <c r="U19" s="37" t="n">
-        <v>289770.81</v>
+        <v>5487.18</v>
       </c>
       <c r="V19" s="18" t="n">
-        <v>291838.36</v>
+        <v>5470.99</v>
       </c>
       <c r="W19" s="18" t="n">
-        <v>297235.91</v>
+        <v>15642.89</v>
       </c>
       <c r="X19" s="18" t="n">
-        <v>299316.59</v>
+        <v>15623.2</v>
       </c>
       <c r="Y19" s="18" t="n">
-        <v>300149.59</v>
+        <v>18244.34</v>
       </c>
       <c r="Z19" s="37" t="n">
-        <v>300149.59</v>
+        <v>18244.34</v>
       </c>
       <c r="AA19" s="18" t="n">
-        <v>312984.1</v>
+        <v>18210.59</v>
       </c>
       <c r="AB19" s="19" t="n">
-        <v>330570.96</v>
+        <v>18190.73</v>
       </c>
       <c r="AC19" s="10" t="n"/>
       <c r="AD19" s="10" t="n"/>
@@ -17933,80 +18244,80 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>유동부채</t>
+          <t>무형자산</t>
         </is>
       </c>
       <c r="E20" s="18" t="n">
-        <v>23726.09</v>
+        <v>1410.97</v>
       </c>
       <c r="F20" s="37" t="n">
-        <v>23726.09</v>
+        <v>1410.97</v>
       </c>
       <c r="G20" s="18" t="n">
-        <v>21903.97</v>
+        <v>1354.67</v>
       </c>
       <c r="H20" s="18" t="n">
-        <v>24245.92</v>
+        <v>1293.55</v>
       </c>
       <c r="I20" s="18" t="n">
-        <v>26466.13</v>
+        <v>1263.99</v>
       </c>
       <c r="J20" s="18" t="n">
-        <v>30018</v>
+        <v>1212.83</v>
       </c>
       <c r="K20" s="37" t="n">
-        <v>30018</v>
+        <v>1212.83</v>
       </c>
       <c r="L20" s="18" t="n">
-        <v>35307.28</v>
+        <v>1150.79</v>
       </c>
       <c r="M20" s="18" t="n">
-        <v>48152.46</v>
+        <v>1101.94</v>
       </c>
       <c r="N20" s="18" t="n">
-        <v>47989.91</v>
+        <v>1040.07</v>
       </c>
       <c r="O20" s="18" t="n">
-        <v>59956.38</v>
+        <v>993.78</v>
       </c>
       <c r="P20" s="37" t="n">
-        <v>59956.38</v>
+        <v>993.78</v>
       </c>
       <c r="Q20" s="18" t="n">
-        <v>57239.05</v>
+        <v>981.1900000000001</v>
       </c>
       <c r="R20" s="18" t="n">
-        <v>59647.1</v>
+        <v>961.1</v>
       </c>
       <c r="S20" s="18" t="n">
-        <v>55010.77</v>
+        <v>952.46</v>
       </c>
       <c r="T20" s="18" t="n">
-        <v>54592.39</v>
+        <v>943.05</v>
       </c>
       <c r="U20" s="37" t="n">
-        <v>54592.39</v>
+        <v>943.05</v>
       </c>
       <c r="V20" s="18" t="n">
-        <v>52506.68</v>
+        <v>947.13</v>
       </c>
       <c r="W20" s="18" t="n">
-        <v>53217.08</v>
+        <v>1250.01</v>
       </c>
       <c r="X20" s="18" t="n">
-        <v>47531.54</v>
+        <v>1241.37</v>
       </c>
       <c r="Y20" s="18" t="n">
-        <v>41767.89</v>
+        <v>1244.76</v>
       </c>
       <c r="Z20" s="37" t="n">
-        <v>41767.89</v>
+        <v>1244.76</v>
       </c>
       <c r="AA20" s="18" t="n">
-        <v>49737.36</v>
+        <v>1251.67</v>
       </c>
       <c r="AB20" s="19" t="n">
-        <v>59055.91</v>
+        <v>1270.71</v>
       </c>
       <c r="AC20" s="10" t="n"/>
       <c r="AD20" s="10" t="n"/>
@@ -18028,80 +18339,80 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>매입채무및기타채무</t>
+          <t>이연법인세자산</t>
         </is>
       </c>
       <c r="E21" s="18" t="n">
-        <v>12528.12</v>
+        <v>802.05</v>
       </c>
       <c r="F21" s="37" t="n">
-        <v>12528.12</v>
+        <v>802.05</v>
       </c>
       <c r="G21" s="18" t="n">
-        <v>12527.52</v>
+        <v>1284.25</v>
       </c>
       <c r="H21" s="18" t="n">
-        <v>11542.38</v>
+        <v>1731.67</v>
       </c>
       <c r="I21" s="18" t="n">
-        <v>12005.87</v>
+        <v>1233.96</v>
       </c>
       <c r="J21" s="18" t="n">
-        <v>10024.45</v>
+        <v>3762.71</v>
       </c>
       <c r="K21" s="37" t="n">
-        <v>10024.45</v>
+        <v>3762.71</v>
       </c>
       <c r="L21" s="18" t="n">
-        <v>12301.5</v>
+        <v>3392.41</v>
       </c>
       <c r="M21" s="18" t="n">
-        <v>13375.88</v>
+        <v>3217.04</v>
       </c>
       <c r="N21" s="18" t="n">
-        <v>13126.53</v>
+        <v>2544.4</v>
       </c>
       <c r="O21" s="18" t="n">
-        <v>16048.64</v>
+        <v>2882.6</v>
       </c>
       <c r="P21" s="37" t="n">
-        <v>16048.64</v>
+        <v>2882.6</v>
       </c>
       <c r="Q21" s="18" t="n">
-        <v>14694.96</v>
+        <v>2316.57</v>
       </c>
       <c r="R21" s="18" t="n">
-        <v>15453.44</v>
+        <v>2461.18</v>
       </c>
       <c r="S21" s="18" t="n">
-        <v>14105.37</v>
+        <v>2689.66</v>
       </c>
       <c r="T21" s="18" t="n">
-        <v>17868.25</v>
+        <v>1967.58</v>
       </c>
       <c r="U21" s="37" t="n">
-        <v>17868.25</v>
+        <v>1967.58</v>
       </c>
       <c r="V21" s="18" t="n">
-        <v>18520.94</v>
+        <v>2803.15</v>
       </c>
       <c r="W21" s="18" t="n">
-        <v>22080.58</v>
+        <v>2987.19</v>
       </c>
       <c r="X21" s="18" t="n">
-        <v>18905.12</v>
+        <v>2908.61</v>
       </c>
       <c r="Y21" s="18" t="n">
-        <v>16596.13</v>
+        <v>3418.23</v>
       </c>
       <c r="Z21" s="37" t="n">
-        <v>16596.13</v>
+        <v>3418.23</v>
       </c>
       <c r="AA21" s="18" t="n">
-        <v>26542.28</v>
+        <v>2634.51</v>
       </c>
       <c r="AB21" s="19" t="n">
-        <v>23857.82</v>
+        <v>3522.74</v>
       </c>
       <c r="AC21" s="10" t="n"/>
       <c r="AD21" s="10" t="n"/>
@@ -18123,80 +18434,80 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>유동리스부채</t>
+          <t>자산총계</t>
         </is>
       </c>
       <c r="E22" s="18" t="n">
-        <v>197.24</v>
+        <v>241431.73</v>
       </c>
       <c r="F22" s="37" t="n">
-        <v>197.24</v>
+        <v>241431.73</v>
       </c>
       <c r="G22" s="18" t="n">
-        <v>193.24</v>
+        <v>236928.74</v>
       </c>
       <c r="H22" s="18" t="n">
-        <v>189.25</v>
+        <v>238045.93</v>
       </c>
       <c r="I22" s="18" t="n">
-        <v>185.25</v>
+        <v>242021.41</v>
       </c>
       <c r="J22" s="18" t="n">
-        <v>180.62</v>
+        <v>239085.99</v>
       </c>
       <c r="K22" s="37" t="n">
-        <v>180.62</v>
+        <v>239085.99</v>
       </c>
       <c r="L22" s="18" t="n">
-        <v>181.78</v>
+        <v>245766.22</v>
       </c>
       <c r="M22" s="18" t="n">
-        <v>182.96</v>
+        <v>259016.44</v>
       </c>
       <c r="N22" s="18" t="n">
-        <v>184.14</v>
+        <v>261330.87</v>
       </c>
       <c r="O22" s="18" t="n">
-        <v>185.33</v>
+        <v>275699.82</v>
       </c>
       <c r="P22" s="37" t="n">
-        <v>185.33</v>
+        <v>275699.82</v>
       </c>
       <c r="Q22" s="18" t="n">
-        <v>186.52</v>
+        <v>276591.11</v>
       </c>
       <c r="R22" s="18" t="n">
-        <v>187.73</v>
+        <v>283216.57</v>
       </c>
       <c r="S22" s="18" t="n">
-        <v>188.94</v>
+        <v>280780.74</v>
       </c>
       <c r="T22" s="18" t="n">
-        <v>194.52</v>
+        <v>289770.81</v>
       </c>
       <c r="U22" s="37" t="n">
-        <v>194.52</v>
+        <v>289770.81</v>
       </c>
       <c r="V22" s="18" t="n">
-        <v>144.01</v>
+        <v>291838.36</v>
       </c>
       <c r="W22" s="18" t="n">
-        <v>90.75</v>
+        <v>297235.91</v>
       </c>
       <c r="X22" s="18" t="n">
-        <v>35.06</v>
+        <v>299316.59</v>
       </c>
       <c r="Y22" s="18" t="n">
-        <v>228.13</v>
+        <v>300149.59</v>
       </c>
       <c r="Z22" s="37" t="n">
-        <v>228.13</v>
+        <v>300149.59</v>
       </c>
       <c r="AA22" s="18" t="n">
-        <v>221.64</v>
+        <v>312984.1</v>
       </c>
       <c r="AB22" s="19" t="n">
-        <v>241.13</v>
+        <v>330570.96</v>
       </c>
       <c r="AC22" s="10" t="n"/>
       <c r="AD22" s="10" t="n"/>
@@ -18218,80 +18529,80 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>리스부채</t>
+          <t>유동부채</t>
         </is>
       </c>
       <c r="E23" s="18" t="n">
-        <v>197.24</v>
+        <v>23726.09</v>
       </c>
       <c r="F23" s="37" t="n">
-        <v>197.24</v>
+        <v>23726.09</v>
       </c>
       <c r="G23" s="18" t="n">
-        <v>193.24</v>
+        <v>21903.97</v>
       </c>
       <c r="H23" s="18" t="n">
-        <v>189.25</v>
+        <v>24245.92</v>
       </c>
       <c r="I23" s="18" t="n">
-        <v>185.25</v>
+        <v>26466.13</v>
       </c>
       <c r="J23" s="18" t="n">
-        <v>180.62</v>
+        <v>30018</v>
       </c>
       <c r="K23" s="37" t="n">
-        <v>180.62</v>
+        <v>30018</v>
       </c>
       <c r="L23" s="18" t="n">
-        <v>181.78</v>
+        <v>35307.28</v>
       </c>
       <c r="M23" s="18" t="n">
-        <v>182.96</v>
+        <v>48152.46</v>
       </c>
       <c r="N23" s="18" t="n">
-        <v>184.14</v>
+        <v>47989.91</v>
       </c>
       <c r="O23" s="18" t="n">
-        <v>185.33</v>
+        <v>59956.38</v>
       </c>
       <c r="P23" s="37" t="n">
-        <v>185.33</v>
+        <v>59956.38</v>
       </c>
       <c r="Q23" s="18" t="n">
-        <v>186.52</v>
+        <v>57239.05</v>
       </c>
       <c r="R23" s="18" t="n">
-        <v>187.73</v>
+        <v>59647.1</v>
       </c>
       <c r="S23" s="18" t="n">
-        <v>188.94</v>
+        <v>55010.77</v>
       </c>
       <c r="T23" s="18" t="n">
-        <v>194.52</v>
+        <v>54592.39</v>
       </c>
       <c r="U23" s="37" t="n">
-        <v>194.52</v>
+        <v>54592.39</v>
       </c>
       <c r="V23" s="18" t="n">
-        <v>144.01</v>
+        <v>52506.68</v>
       </c>
       <c r="W23" s="18" t="n">
-        <v>90.75</v>
+        <v>53217.08</v>
       </c>
       <c r="X23" s="18" t="n">
-        <v>35.06</v>
+        <v>47531.54</v>
       </c>
       <c r="Y23" s="18" t="n">
-        <v>391.5</v>
+        <v>41767.89</v>
       </c>
       <c r="Z23" s="37" t="n">
-        <v>391.5</v>
+        <v>41767.89</v>
       </c>
       <c r="AA23" s="18" t="n">
-        <v>332.21</v>
+        <v>49737.36</v>
       </c>
       <c r="AB23" s="19" t="n">
-        <v>334.56</v>
+        <v>59055.91</v>
       </c>
       <c r="AC23" s="10" t="n"/>
       <c r="AD23" s="10" t="n"/>
@@ -18313,80 +18624,80 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>단기금융부채</t>
+          <t>매입채무및기타채무</t>
         </is>
       </c>
       <c r="E24" s="18" t="n">
-        <v>197.24</v>
+        <v>12528.12</v>
       </c>
       <c r="F24" s="37" t="n">
-        <v>197.24</v>
+        <v>12528.12</v>
       </c>
       <c r="G24" s="18" t="n">
-        <v>193.24</v>
+        <v>12527.52</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>189.25</v>
+        <v>11542.38</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>185.25</v>
+        <v>12005.87</v>
       </c>
       <c r="J24" s="18" t="n">
-        <v>180.62</v>
+        <v>10024.45</v>
       </c>
       <c r="K24" s="37" t="n">
-        <v>180.62</v>
+        <v>10024.45</v>
       </c>
       <c r="L24" s="18" t="n">
-        <v>181.78</v>
+        <v>12301.5</v>
       </c>
       <c r="M24" s="18" t="n">
-        <v>182.96</v>
+        <v>13375.88</v>
       </c>
       <c r="N24" s="18" t="n">
-        <v>184.14</v>
+        <v>13126.53</v>
       </c>
       <c r="O24" s="18" t="n">
-        <v>185.33</v>
+        <v>16048.64</v>
       </c>
       <c r="P24" s="37" t="n">
-        <v>185.33</v>
+        <v>16048.64</v>
       </c>
       <c r="Q24" s="18" t="n">
-        <v>186.52</v>
+        <v>14694.96</v>
       </c>
       <c r="R24" s="18" t="n">
-        <v>187.73</v>
+        <v>15453.44</v>
       </c>
       <c r="S24" s="18" t="n">
-        <v>188.94</v>
+        <v>14105.37</v>
       </c>
       <c r="T24" s="18" t="n">
-        <v>194.52</v>
+        <v>17868.25</v>
       </c>
       <c r="U24" s="37" t="n">
-        <v>194.52</v>
+        <v>17868.25</v>
       </c>
       <c r="V24" s="18" t="n">
-        <v>144.01</v>
+        <v>18520.94</v>
       </c>
       <c r="W24" s="18" t="n">
-        <v>90.75</v>
+        <v>22080.58</v>
       </c>
       <c r="X24" s="18" t="n">
-        <v>35.06</v>
+        <v>18905.12</v>
       </c>
       <c r="Y24" s="18" t="n">
-        <v>228.13</v>
+        <v>16596.13</v>
       </c>
       <c r="Z24" s="37" t="n">
-        <v>228.13</v>
+        <v>16596.13</v>
       </c>
       <c r="AA24" s="18" t="n">
-        <v>221.64</v>
+        <v>26542.28</v>
       </c>
       <c r="AB24" s="19" t="n">
-        <v>241.13</v>
+        <v>23857.82</v>
       </c>
       <c r="AC24" s="10" t="n"/>
       <c r="AD24" s="10" t="n"/>
@@ -18408,60 +18719,80 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>당기법인세부채(미지급법인세)</t>
+          <t>유동리스부채</t>
         </is>
       </c>
       <c r="E25" s="18" t="n">
-        <v>0</v>
+        <v>197.24</v>
       </c>
       <c r="F25" s="37" t="n">
-        <v>0</v>
+        <v>197.24</v>
+      </c>
+      <c r="G25" s="18" t="n">
+        <v>193.24</v>
+      </c>
+      <c r="H25" s="18" t="n">
+        <v>189.25</v>
+      </c>
+      <c r="I25" s="18" t="n">
+        <v>185.25</v>
       </c>
       <c r="J25" s="18" t="n">
-        <v>0</v>
+        <v>180.62</v>
       </c>
       <c r="K25" s="37" t="n">
-        <v>0</v>
+        <v>180.62</v>
       </c>
       <c r="L25" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" s="9" t="n"/>
+        <v>181.78</v>
+      </c>
+      <c r="M25" s="18" t="n">
+        <v>182.96</v>
+      </c>
+      <c r="N25" s="18" t="n">
+        <v>184.14</v>
+      </c>
+      <c r="O25" s="18" t="n">
+        <v>185.33</v>
+      </c>
+      <c r="P25" s="37" t="n">
+        <v>185.33</v>
+      </c>
       <c r="Q25" s="18" t="n">
-        <v>178.14</v>
+        <v>186.52</v>
       </c>
       <c r="R25" s="18" t="n">
-        <v>1109.07</v>
+        <v>187.73</v>
       </c>
       <c r="S25" s="18" t="n">
-        <v>1640.07</v>
+        <v>188.94</v>
       </c>
       <c r="T25" s="18" t="n">
-        <v>3186.94</v>
+        <v>194.52</v>
       </c>
       <c r="U25" s="37" t="n">
-        <v>3186.94</v>
+        <v>194.52</v>
       </c>
       <c r="V25" s="18" t="n">
-        <v>3841.17</v>
+        <v>144.01</v>
       </c>
       <c r="W25" s="18" t="n">
-        <v>2948.23</v>
+        <v>90.75</v>
       </c>
       <c r="X25" s="18" t="n">
-        <v>4204.01</v>
+        <v>35.06</v>
       </c>
       <c r="Y25" s="18" t="n">
-        <v>5509.96</v>
+        <v>228.13</v>
       </c>
       <c r="Z25" s="37" t="n">
-        <v>5509.96</v>
+        <v>228.13</v>
       </c>
       <c r="AA25" s="18" t="n">
-        <v>4009.33</v>
+        <v>221.64</v>
       </c>
       <c r="AB25" s="19" t="n">
-        <v>3723.49</v>
+        <v>241.13</v>
       </c>
       <c r="AC25" s="10" t="n"/>
       <c r="AD25" s="10" t="n"/>
@@ -18483,80 +18814,80 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>비유동부채</t>
+          <t>리스부채</t>
         </is>
       </c>
       <c r="E26" s="18" t="n">
-        <v>834.0700000000001</v>
+        <v>721.3099999999999</v>
       </c>
       <c r="F26" s="37" t="n">
-        <v>834.0700000000001</v>
+        <v>721.3099999999999</v>
       </c>
       <c r="G26" s="18" t="n">
-        <v>789.35</v>
+        <v>672.59</v>
       </c>
       <c r="H26" s="18" t="n">
-        <v>822.34</v>
+        <v>623.59</v>
       </c>
       <c r="I26" s="18" t="n">
-        <v>777.05</v>
+        <v>574.3</v>
       </c>
       <c r="J26" s="18" t="n">
-        <v>911.04</v>
+        <v>524.0700000000001</v>
       </c>
       <c r="K26" s="37" t="n">
-        <v>911.04</v>
+        <v>524.0700000000001</v>
       </c>
       <c r="L26" s="18" t="n">
-        <v>912.21</v>
+        <v>479.35</v>
       </c>
       <c r="M26" s="18" t="n">
-        <v>913.0700000000001</v>
+        <v>434.35</v>
       </c>
       <c r="N26" s="18" t="n">
-        <v>913.64</v>
+        <v>389.05</v>
       </c>
       <c r="O26" s="18" t="n">
-        <v>928.1799999999999</v>
+        <v>343.46</v>
       </c>
       <c r="P26" s="37" t="n">
-        <v>928.1799999999999</v>
+        <v>343.46</v>
       </c>
       <c r="Q26" s="18" t="n">
-        <v>913.22</v>
+        <v>297.56</v>
       </c>
       <c r="R26" s="18" t="n">
-        <v>897.95</v>
+        <v>251.39</v>
       </c>
       <c r="S26" s="18" t="n">
-        <v>882.38</v>
+        <v>204.91</v>
       </c>
       <c r="T26" s="18" t="n">
-        <v>900.88</v>
+        <v>204.35</v>
       </c>
       <c r="U26" s="37" t="n">
-        <v>900.88</v>
+        <v>204.35</v>
       </c>
       <c r="V26" s="18" t="n">
-        <v>895.38</v>
+        <v>148.34</v>
       </c>
       <c r="W26" s="18" t="n">
-        <v>814.22</v>
+        <v>91.91</v>
       </c>
       <c r="X26" s="18" t="n">
-        <v>813.05</v>
+        <v>35.06</v>
       </c>
       <c r="Y26" s="18" t="n">
-        <v>1012.33</v>
+        <v>391.5</v>
       </c>
       <c r="Z26" s="37" t="n">
-        <v>1012.33</v>
+        <v>391.5</v>
       </c>
       <c r="AA26" s="18" t="n">
-        <v>939.53</v>
+        <v>332.21</v>
       </c>
       <c r="AB26" s="19" t="n">
-        <v>997.59</v>
+        <v>334.56</v>
       </c>
       <c r="AC26" s="10" t="n"/>
       <c r="AD26" s="10" t="n"/>
@@ -18578,49 +18909,80 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>기타비유동금융부채</t>
+          <t>단기금융부채</t>
         </is>
       </c>
       <c r="E27" s="18" t="n">
-        <v>310</v>
+        <v>197.24</v>
       </c>
       <c r="F27" s="37" t="n">
-        <v>310</v>
+        <v>197.24</v>
       </c>
       <c r="G27" s="18" t="n">
-        <v>310</v>
+        <v>193.24</v>
       </c>
       <c r="H27" s="18" t="n">
-        <v>388</v>
+        <v>189.25</v>
       </c>
       <c r="I27" s="18" t="n">
-        <v>388</v>
+        <v>185.25</v>
       </c>
       <c r="J27" s="18" t="n">
-        <v>388</v>
+        <v>180.62</v>
       </c>
       <c r="K27" s="37" t="n">
-        <v>388</v>
+        <v>180.62</v>
       </c>
       <c r="L27" s="18" t="n">
-        <v>388</v>
+        <v>181.78</v>
       </c>
       <c r="M27" s="18" t="n">
-        <v>388</v>
-      </c>
-      <c r="P27" s="9" t="n"/>
-      <c r="U27" s="9" t="n"/>
+        <v>182.96</v>
+      </c>
+      <c r="N27" s="18" t="n">
+        <v>184.14</v>
+      </c>
+      <c r="O27" s="18" t="n">
+        <v>185.33</v>
+      </c>
+      <c r="P27" s="37" t="n">
+        <v>185.33</v>
+      </c>
+      <c r="Q27" s="18" t="n">
+        <v>186.52</v>
+      </c>
+      <c r="R27" s="18" t="n">
+        <v>187.73</v>
+      </c>
+      <c r="S27" s="18" t="n">
+        <v>188.94</v>
+      </c>
+      <c r="T27" s="18" t="n">
+        <v>194.52</v>
+      </c>
+      <c r="U27" s="37" t="n">
+        <v>194.52</v>
+      </c>
+      <c r="V27" s="18" t="n">
+        <v>144.01</v>
+      </c>
+      <c r="W27" s="18" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="X27" s="18" t="n">
+        <v>35.06</v>
+      </c>
       <c r="Y27" s="18" t="n">
-        <v>290</v>
+        <v>228.13</v>
       </c>
       <c r="Z27" s="37" t="n">
-        <v>290</v>
+        <v>228.13</v>
       </c>
       <c r="AA27" s="18" t="n">
-        <v>270</v>
+        <v>221.64</v>
       </c>
       <c r="AB27" s="19" t="n">
-        <v>360</v>
+        <v>241.13</v>
       </c>
       <c r="AC27" s="10" t="n"/>
       <c r="AD27" s="10" t="n"/>
@@ -18642,49 +19004,60 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>장기금융부채</t>
+          <t>당기법인세부채(미지급법인세)</t>
         </is>
       </c>
       <c r="E28" s="18" t="n">
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="F28" s="37" t="n">
-        <v>310</v>
-      </c>
-      <c r="G28" s="18" t="n">
-        <v>310</v>
-      </c>
-      <c r="H28" s="18" t="n">
-        <v>388</v>
-      </c>
-      <c r="I28" s="18" t="n">
-        <v>388</v>
+        <v>0</v>
       </c>
       <c r="J28" s="18" t="n">
-        <v>388</v>
+        <v>0</v>
       </c>
       <c r="K28" s="37" t="n">
-        <v>388</v>
+        <v>0</v>
       </c>
       <c r="L28" s="18" t="n">
-        <v>388</v>
-      </c>
-      <c r="M28" s="18" t="n">
-        <v>388</v>
+        <v>0</v>
       </c>
       <c r="P28" s="9" t="n"/>
-      <c r="U28" s="9" t="n"/>
+      <c r="Q28" s="18" t="n">
+        <v>178.14</v>
+      </c>
+      <c r="R28" s="18" t="n">
+        <v>1109.07</v>
+      </c>
+      <c r="S28" s="18" t="n">
+        <v>1640.07</v>
+      </c>
+      <c r="T28" s="18" t="n">
+        <v>3186.94</v>
+      </c>
+      <c r="U28" s="37" t="n">
+        <v>3186.94</v>
+      </c>
+      <c r="V28" s="18" t="n">
+        <v>3841.17</v>
+      </c>
+      <c r="W28" s="18" t="n">
+        <v>2948.23</v>
+      </c>
+      <c r="X28" s="18" t="n">
+        <v>4204.01</v>
+      </c>
       <c r="Y28" s="18" t="n">
-        <v>453.37</v>
+        <v>5509.96</v>
       </c>
       <c r="Z28" s="37" t="n">
-        <v>453.37</v>
+        <v>5509.96</v>
       </c>
       <c r="AA28" s="18" t="n">
-        <v>380.57</v>
+        <v>4009.33</v>
       </c>
       <c r="AB28" s="19" t="n">
-        <v>453.43</v>
+        <v>3723.49</v>
       </c>
       <c r="AC28" s="10" t="n"/>
       <c r="AD28" s="10" t="n"/>
@@ -18706,80 +19079,80 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>부채총계</t>
+          <t>비유동부채</t>
         </is>
       </c>
       <c r="E29" s="18" t="n">
-        <v>24560.17</v>
+        <v>834.0700000000001</v>
       </c>
       <c r="F29" s="37" t="n">
-        <v>24560.17</v>
+        <v>834.0700000000001</v>
       </c>
       <c r="G29" s="18" t="n">
-        <v>22693.32</v>
+        <v>789.35</v>
       </c>
       <c r="H29" s="18" t="n">
-        <v>25068.26</v>
+        <v>822.34</v>
       </c>
       <c r="I29" s="18" t="n">
-        <v>27243.18</v>
+        <v>777.05</v>
       </c>
       <c r="J29" s="18" t="n">
-        <v>30929.05</v>
+        <v>911.04</v>
       </c>
       <c r="K29" s="37" t="n">
-        <v>30929.05</v>
+        <v>911.04</v>
       </c>
       <c r="L29" s="18" t="n">
-        <v>36219.49</v>
+        <v>912.21</v>
       </c>
       <c r="M29" s="18" t="n">
-        <v>49065.53</v>
+        <v>913.0700000000001</v>
       </c>
       <c r="N29" s="18" t="n">
-        <v>48903.56</v>
+        <v>913.64</v>
       </c>
       <c r="O29" s="18" t="n">
-        <v>60884.57</v>
+        <v>928.1799999999999</v>
       </c>
       <c r="P29" s="37" t="n">
-        <v>60884.57</v>
+        <v>928.1799999999999</v>
       </c>
       <c r="Q29" s="18" t="n">
-        <v>58152.27</v>
+        <v>913.22</v>
       </c>
       <c r="R29" s="18" t="n">
-        <v>60545.06</v>
+        <v>897.95</v>
       </c>
       <c r="S29" s="18" t="n">
-        <v>55893.15</v>
+        <v>882.38</v>
       </c>
       <c r="T29" s="18" t="n">
-        <v>55493.28</v>
+        <v>900.88</v>
       </c>
       <c r="U29" s="37" t="n">
-        <v>55493.28</v>
+        <v>900.88</v>
       </c>
       <c r="V29" s="18" t="n">
-        <v>53402.06</v>
+        <v>895.38</v>
       </c>
       <c r="W29" s="18" t="n">
-        <v>54031.3</v>
+        <v>814.22</v>
       </c>
       <c r="X29" s="18" t="n">
-        <v>48344.6</v>
+        <v>813.05</v>
       </c>
       <c r="Y29" s="18" t="n">
-        <v>42780.22</v>
+        <v>1012.33</v>
       </c>
       <c r="Z29" s="37" t="n">
-        <v>42780.22</v>
+        <v>1012.33</v>
       </c>
       <c r="AA29" s="18" t="n">
-        <v>50676.89</v>
+        <v>939.53</v>
       </c>
       <c r="AB29" s="19" t="n">
-        <v>60053.51</v>
+        <v>997.59</v>
       </c>
       <c r="AC29" s="10" t="n"/>
       <c r="AD29" s="10" t="n"/>
@@ -18801,80 +19174,49 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>자본금</t>
+          <t>기타비유동금융부채</t>
         </is>
       </c>
       <c r="E30" s="18" t="n">
-        <v>4783.67</v>
+        <v>310</v>
       </c>
       <c r="F30" s="37" t="n">
-        <v>4783.67</v>
+        <v>310</v>
       </c>
       <c r="G30" s="18" t="n">
-        <v>4783.67</v>
+        <v>310</v>
       </c>
       <c r="H30" s="18" t="n">
-        <v>4783.67</v>
+        <v>388</v>
       </c>
       <c r="I30" s="18" t="n">
-        <v>4783.67</v>
+        <v>388</v>
       </c>
       <c r="J30" s="18" t="n">
-        <v>4783.67</v>
+        <v>388</v>
       </c>
       <c r="K30" s="37" t="n">
-        <v>4783.67</v>
+        <v>388</v>
       </c>
       <c r="L30" s="18" t="n">
-        <v>4783.67</v>
+        <v>388</v>
       </c>
       <c r="M30" s="18" t="n">
-        <v>4783.67</v>
-      </c>
-      <c r="N30" s="18" t="n">
-        <v>4783.67</v>
-      </c>
-      <c r="O30" s="18" t="n">
-        <v>4783.67</v>
-      </c>
-      <c r="P30" s="37" t="n">
-        <v>4783.67</v>
-      </c>
-      <c r="Q30" s="18" t="n">
-        <v>4783.67</v>
-      </c>
-      <c r="R30" s="18" t="n">
-        <v>4783.67</v>
-      </c>
-      <c r="S30" s="18" t="n">
-        <v>4783.67</v>
-      </c>
-      <c r="T30" s="18" t="n">
-        <v>4783.67</v>
-      </c>
-      <c r="U30" s="37" t="n">
-        <v>4783.67</v>
-      </c>
-      <c r="V30" s="18" t="n">
-        <v>4783.67</v>
-      </c>
-      <c r="W30" s="18" t="n">
-        <v>4783.67</v>
-      </c>
-      <c r="X30" s="18" t="n">
-        <v>4783.67</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="P30" s="9" t="n"/>
+      <c r="U30" s="9" t="n"/>
       <c r="Y30" s="18" t="n">
-        <v>4783.67</v>
+        <v>290</v>
       </c>
       <c r="Z30" s="37" t="n">
-        <v>4783.67</v>
+        <v>290</v>
       </c>
       <c r="AA30" s="18" t="n">
-        <v>4783.67</v>
+        <v>270</v>
       </c>
       <c r="AB30" s="19" t="n">
-        <v>4783.67</v>
+        <v>360</v>
       </c>
       <c r="AC30" s="10" t="n"/>
       <c r="AD30" s="10" t="n"/>
@@ -18896,80 +19238,80 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>자본잉여금</t>
+          <t>장기금융부채</t>
         </is>
       </c>
       <c r="E31" s="18" t="n">
-        <v>24958.68</v>
+        <v>834.0700000000001</v>
       </c>
       <c r="F31" s="37" t="n">
-        <v>24958.68</v>
+        <v>834.0700000000001</v>
       </c>
       <c r="G31" s="18" t="n">
-        <v>24974.84</v>
+        <v>789.35</v>
       </c>
       <c r="H31" s="18" t="n">
-        <v>24977.78</v>
+        <v>822.34</v>
       </c>
       <c r="I31" s="18" t="n">
-        <v>24977.78</v>
+        <v>777.05</v>
       </c>
       <c r="J31" s="18" t="n">
-        <v>24978.48</v>
+        <v>731.45</v>
       </c>
       <c r="K31" s="37" t="n">
-        <v>24978.48</v>
+        <v>731.45</v>
       </c>
       <c r="L31" s="18" t="n">
-        <v>25026.82</v>
+        <v>685.5700000000001</v>
       </c>
       <c r="M31" s="18" t="n">
-        <v>25034.91</v>
+        <v>639.39</v>
       </c>
       <c r="N31" s="18" t="n">
-        <v>25034.91</v>
+        <v>204.91</v>
       </c>
       <c r="O31" s="18" t="n">
-        <v>25035.47</v>
+        <v>158.13</v>
       </c>
       <c r="P31" s="37" t="n">
-        <v>25035.47</v>
+        <v>158.13</v>
       </c>
       <c r="Q31" s="18" t="n">
-        <v>25048.84</v>
+        <v>111.04</v>
       </c>
       <c r="R31" s="18" t="n">
-        <v>25053.11</v>
+        <v>63.66</v>
       </c>
       <c r="S31" s="18" t="n">
-        <v>25053.11</v>
+        <v>15.97</v>
       </c>
       <c r="T31" s="18" t="n">
-        <v>25053.11</v>
+        <v>9.83</v>
       </c>
       <c r="U31" s="37" t="n">
-        <v>25053.11</v>
+        <v>9.83</v>
       </c>
       <c r="V31" s="18" t="n">
-        <v>25053.11</v>
+        <v>4.33</v>
       </c>
       <c r="W31" s="18" t="n">
-        <v>25086.07</v>
+        <v>1.16</v>
       </c>
       <c r="X31" s="18" t="n">
-        <v>25086.07</v>
+        <v>0</v>
       </c>
       <c r="Y31" s="18" t="n">
-        <v>25272.22</v>
+        <v>453.37</v>
       </c>
       <c r="Z31" s="37" t="n">
-        <v>25272.22</v>
+        <v>453.37</v>
       </c>
       <c r="AA31" s="18" t="n">
-        <v>25272.22</v>
+        <v>380.57</v>
       </c>
       <c r="AB31" s="19" t="n">
-        <v>25536.36</v>
+        <v>453.43</v>
       </c>
       <c r="AC31" s="10" t="n"/>
       <c r="AD31" s="10" t="n"/>
@@ -18991,80 +19333,80 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>기타자본</t>
+          <t>비유동리스부채</t>
         </is>
       </c>
       <c r="E32" s="18" t="n">
-        <v>-2586.62</v>
+        <v>524.0700000000001</v>
       </c>
       <c r="F32" s="37" t="n">
-        <v>-2586.62</v>
+        <v>524.0700000000001</v>
       </c>
       <c r="G32" s="18" t="n">
-        <v>-2597.23</v>
+        <v>479.35</v>
       </c>
       <c r="H32" s="18" t="n">
-        <v>-2562.52</v>
+        <v>434.34</v>
       </c>
       <c r="I32" s="18" t="n">
-        <v>-2554.74</v>
+        <v>389.05</v>
       </c>
       <c r="J32" s="18" t="n">
-        <v>-2541.49</v>
+        <v>343.45</v>
       </c>
       <c r="K32" s="37" t="n">
-        <v>-2541.49</v>
+        <v>343.45</v>
       </c>
       <c r="L32" s="18" t="n">
-        <v>-2581.8</v>
+        <v>297.57</v>
       </c>
       <c r="M32" s="18" t="n">
-        <v>-3490.35</v>
+        <v>251.39</v>
       </c>
       <c r="N32" s="18" t="n">
-        <v>-3523.92</v>
+        <v>204.91</v>
       </c>
       <c r="O32" s="18" t="n">
-        <v>-3508.07</v>
+        <v>158.13</v>
       </c>
       <c r="P32" s="37" t="n">
-        <v>-3508.07</v>
+        <v>158.13</v>
       </c>
       <c r="Q32" s="18" t="n">
-        <v>-3509.47</v>
+        <v>111.04</v>
       </c>
       <c r="R32" s="18" t="n">
-        <v>-3471.66</v>
+        <v>63.66</v>
       </c>
       <c r="S32" s="18" t="n">
-        <v>-3455.64</v>
+        <v>15.97</v>
       </c>
       <c r="T32" s="18" t="n">
-        <v>-3436.7</v>
+        <v>9.83</v>
       </c>
       <c r="U32" s="37" t="n">
-        <v>-3436.7</v>
+        <v>9.83</v>
       </c>
       <c r="V32" s="18" t="n">
-        <v>-3419.11</v>
+        <v>4.33</v>
       </c>
       <c r="W32" s="18" t="n">
-        <v>-3374.2</v>
+        <v>1.16</v>
       </c>
       <c r="X32" s="18" t="n">
-        <v>-3334.46</v>
+        <v>0</v>
       </c>
       <c r="Y32" s="18" t="n">
-        <v>-3296.14</v>
+        <v>163.37</v>
       </c>
       <c r="Z32" s="37" t="n">
-        <v>-3296.14</v>
+        <v>163.37</v>
       </c>
       <c r="AA32" s="18" t="n">
-        <v>-3296.14</v>
+        <v>110.57</v>
       </c>
       <c r="AB32" s="19" t="n">
-        <v>-2920.76</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="AC32" s="10" t="n"/>
       <c r="AD32" s="10" t="n"/>
@@ -19086,80 +19428,80 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>기타포괄이익누계액</t>
+          <t>부채총계</t>
         </is>
       </c>
       <c r="E33" s="18" t="n">
-        <v>9330.27</v>
+        <v>24560.17</v>
       </c>
       <c r="F33" s="37" t="n">
-        <v>9330.27</v>
+        <v>24560.17</v>
       </c>
       <c r="G33" s="18" t="n">
-        <v>9330.27</v>
+        <v>22693.32</v>
       </c>
       <c r="H33" s="18" t="n">
-        <v>9330.27</v>
+        <v>25068.26</v>
       </c>
       <c r="I33" s="18" t="n">
-        <v>9330.27</v>
+        <v>27243.18</v>
       </c>
       <c r="J33" s="18" t="n">
-        <v>9330.27</v>
+        <v>30929.05</v>
       </c>
       <c r="K33" s="37" t="n">
-        <v>9330.27</v>
+        <v>30929.05</v>
       </c>
       <c r="L33" s="18" t="n">
-        <v>9330.27</v>
+        <v>36219.49</v>
       </c>
       <c r="M33" s="18" t="n">
-        <v>9330.27</v>
+        <v>49065.53</v>
       </c>
       <c r="N33" s="18" t="n">
-        <v>9330.27</v>
+        <v>48903.56</v>
       </c>
       <c r="O33" s="18" t="n">
-        <v>9330.27</v>
+        <v>60884.57</v>
       </c>
       <c r="P33" s="37" t="n">
-        <v>9330.27</v>
+        <v>60884.57</v>
       </c>
       <c r="Q33" s="18" t="n">
-        <v>9330.27</v>
+        <v>58152.27</v>
       </c>
       <c r="R33" s="18" t="n">
-        <v>9330.27</v>
+        <v>60545.06</v>
       </c>
       <c r="S33" s="18" t="n">
-        <v>9330.27</v>
+        <v>55893.15</v>
       </c>
       <c r="T33" s="18" t="n">
-        <v>9330.27</v>
+        <v>55493.28</v>
       </c>
       <c r="U33" s="37" t="n">
-        <v>9330.27</v>
+        <v>55493.28</v>
       </c>
       <c r="V33" s="18" t="n">
-        <v>9330.27</v>
+        <v>53402.06</v>
       </c>
       <c r="W33" s="18" t="n">
-        <v>9330.27</v>
+        <v>54031.3</v>
       </c>
       <c r="X33" s="18" t="n">
-        <v>9330.27</v>
+        <v>48344.6</v>
       </c>
       <c r="Y33" s="18" t="n">
-        <v>9330.27</v>
+        <v>42780.22</v>
       </c>
       <c r="Z33" s="37" t="n">
-        <v>9330.27</v>
+        <v>42780.22</v>
       </c>
       <c r="AA33" s="18" t="n">
-        <v>9330.27</v>
+        <v>50676.89</v>
       </c>
       <c r="AB33" s="19" t="n">
-        <v>9330.27</v>
+        <v>60053.51</v>
       </c>
       <c r="AC33" s="10" t="n"/>
       <c r="AD33" s="10" t="n"/>
@@ -19181,80 +19523,80 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>이익잉여금</t>
+          <t>자본금</t>
         </is>
       </c>
       <c r="E34" s="18" t="n">
-        <v>180385.56</v>
+        <v>4783.67</v>
       </c>
       <c r="F34" s="37" t="n">
-        <v>180385.56</v>
+        <v>4783.67</v>
       </c>
       <c r="G34" s="18" t="n">
-        <v>177743.87</v>
+        <v>4783.67</v>
       </c>
       <c r="H34" s="18" t="n">
-        <v>176448.47</v>
+        <v>4783.67</v>
       </c>
       <c r="I34" s="18" t="n">
-        <v>178241.25</v>
+        <v>4783.67</v>
       </c>
       <c r="J34" s="18" t="n">
-        <v>171606.02</v>
+        <v>4783.67</v>
       </c>
       <c r="K34" s="37" t="n">
-        <v>171606.02</v>
+        <v>4783.67</v>
       </c>
       <c r="L34" s="18" t="n">
-        <v>172987.78</v>
+        <v>4783.67</v>
       </c>
       <c r="M34" s="18" t="n">
-        <v>174292.42</v>
+        <v>4783.67</v>
       </c>
       <c r="N34" s="18" t="n">
-        <v>176802.39</v>
+        <v>4783.67</v>
       </c>
       <c r="O34" s="18" t="n">
-        <v>179173.92</v>
+        <v>4783.67</v>
       </c>
       <c r="P34" s="37" t="n">
-        <v>179173.92</v>
+        <v>4783.67</v>
       </c>
       <c r="Q34" s="18" t="n">
-        <v>182785.54</v>
+        <v>4783.67</v>
       </c>
       <c r="R34" s="18" t="n">
-        <v>186976.13</v>
+        <v>4783.67</v>
       </c>
       <c r="S34" s="18" t="n">
-        <v>189176.18</v>
+        <v>4783.67</v>
       </c>
       <c r="T34" s="18" t="n">
-        <v>198547.19</v>
+        <v>4783.67</v>
       </c>
       <c r="U34" s="37" t="n">
-        <v>198547.19</v>
+        <v>4783.67</v>
       </c>
       <c r="V34" s="18" t="n">
-        <v>202688.36</v>
+        <v>4783.67</v>
       </c>
       <c r="W34" s="18" t="n">
-        <v>207378.81</v>
+        <v>4783.67</v>
       </c>
       <c r="X34" s="18" t="n">
-        <v>215106.46</v>
+        <v>4783.67</v>
       </c>
       <c r="Y34" s="18" t="n">
-        <v>221279.35</v>
+        <v>4783.67</v>
       </c>
       <c r="Z34" s="37" t="n">
-        <v>221279.35</v>
+        <v>4783.67</v>
       </c>
       <c r="AA34" s="18" t="n">
-        <v>226217.19</v>
+        <v>4783.67</v>
       </c>
       <c r="AB34" s="19" t="n">
-        <v>233787.92</v>
+        <v>4783.67</v>
       </c>
       <c r="AC34" s="10" t="n"/>
       <c r="AD34" s="10" t="n"/>
@@ -19276,80 +19618,80 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>자본총계</t>
+          <t>자본잉여금</t>
         </is>
       </c>
       <c r="E35" s="18" t="n">
-        <v>216871.56</v>
+        <v>24958.68</v>
       </c>
       <c r="F35" s="37" t="n">
-        <v>216871.56</v>
+        <v>24958.68</v>
       </c>
       <c r="G35" s="18" t="n">
-        <v>214235.41</v>
+        <v>24974.84</v>
       </c>
       <c r="H35" s="18" t="n">
-        <v>212977.67</v>
+        <v>24977.78</v>
       </c>
       <c r="I35" s="18" t="n">
-        <v>214778.23</v>
+        <v>24977.78</v>
       </c>
       <c r="J35" s="18" t="n">
-        <v>208156.94</v>
+        <v>24978.48</v>
       </c>
       <c r="K35" s="37" t="n">
-        <v>208156.94</v>
+        <v>24978.48</v>
       </c>
       <c r="L35" s="18" t="n">
-        <v>209546.73</v>
+        <v>25026.82</v>
       </c>
       <c r="M35" s="18" t="n">
-        <v>209950.91</v>
+        <v>25034.91</v>
       </c>
       <c r="N35" s="18" t="n">
-        <v>212427.32</v>
+        <v>25034.91</v>
       </c>
       <c r="O35" s="18" t="n">
-        <v>214815.25</v>
+        <v>25035.47</v>
       </c>
       <c r="P35" s="37" t="n">
-        <v>214815.25</v>
+        <v>25035.47</v>
       </c>
       <c r="Q35" s="18" t="n">
-        <v>218438.84</v>
+        <v>25048.84</v>
       </c>
       <c r="R35" s="18" t="n">
-        <v>222671.51</v>
+        <v>25053.11</v>
       </c>
       <c r="S35" s="18" t="n">
-        <v>224887.59</v>
+        <v>25053.11</v>
       </c>
       <c r="T35" s="18" t="n">
-        <v>234277.53</v>
+        <v>25053.11</v>
       </c>
       <c r="U35" s="37" t="n">
-        <v>234277.53</v>
+        <v>25053.11</v>
       </c>
       <c r="V35" s="18" t="n">
-        <v>238436.3</v>
+        <v>25053.11</v>
       </c>
       <c r="W35" s="18" t="n">
-        <v>243204.61</v>
+        <v>25086.07</v>
       </c>
       <c r="X35" s="18" t="n">
-        <v>250972</v>
+        <v>25086.07</v>
       </c>
       <c r="Y35" s="18" t="n">
-        <v>257369.37</v>
+        <v>25272.22</v>
       </c>
       <c r="Z35" s="37" t="n">
-        <v>257369.37</v>
+        <v>25272.22</v>
       </c>
       <c r="AA35" s="18" t="n">
-        <v>262307.21</v>
+        <v>25272.22</v>
       </c>
       <c r="AB35" s="19" t="n">
-        <v>270517.45</v>
+        <v>25536.36</v>
       </c>
       <c r="AC35" s="10" t="n"/>
       <c r="AD35" s="10" t="n"/>
@@ -19371,80 +19713,80 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>부채와자본총계</t>
+          <t>기타자본</t>
         </is>
       </c>
       <c r="E36" s="18" t="n">
-        <v>241431.73</v>
+        <v>-2586.62</v>
       </c>
       <c r="F36" s="37" t="n">
-        <v>241431.73</v>
+        <v>-2586.62</v>
       </c>
       <c r="G36" s="18" t="n">
-        <v>236928.74</v>
+        <v>-2597.23</v>
       </c>
       <c r="H36" s="18" t="n">
-        <v>238045.93</v>
+        <v>-2562.52</v>
       </c>
       <c r="I36" s="18" t="n">
-        <v>242021.41</v>
+        <v>-2554.74</v>
       </c>
       <c r="J36" s="18" t="n">
-        <v>239085.99</v>
+        <v>-2541.49</v>
       </c>
       <c r="K36" s="37" t="n">
-        <v>239085.99</v>
+        <v>-2541.49</v>
       </c>
       <c r="L36" s="18" t="n">
-        <v>245766.22</v>
+        <v>-2581.8</v>
       </c>
       <c r="M36" s="18" t="n">
-        <v>259016.44</v>
+        <v>-3490.35</v>
       </c>
       <c r="N36" s="18" t="n">
-        <v>261330.87</v>
+        <v>-3523.92</v>
       </c>
       <c r="O36" s="18" t="n">
-        <v>275699.82</v>
+        <v>-3508.07</v>
       </c>
       <c r="P36" s="37" t="n">
-        <v>275699.82</v>
+        <v>-3508.07</v>
       </c>
       <c r="Q36" s="18" t="n">
-        <v>276591.11</v>
+        <v>-3509.47</v>
       </c>
       <c r="R36" s="18" t="n">
-        <v>283216.57</v>
+        <v>-3471.66</v>
       </c>
       <c r="S36" s="18" t="n">
-        <v>280780.74</v>
+        <v>-3455.64</v>
       </c>
       <c r="T36" s="18" t="n">
-        <v>289770.81</v>
+        <v>-3436.7</v>
       </c>
       <c r="U36" s="37" t="n">
-        <v>289770.81</v>
+        <v>-3436.7</v>
       </c>
       <c r="V36" s="18" t="n">
-        <v>291838.36</v>
+        <v>-3419.11</v>
       </c>
       <c r="W36" s="18" t="n">
-        <v>297235.91</v>
+        <v>-3374.2</v>
       </c>
       <c r="X36" s="18" t="n">
-        <v>299316.59</v>
+        <v>-3334.46</v>
       </c>
       <c r="Y36" s="18" t="n">
-        <v>300149.59</v>
+        <v>-3296.14</v>
       </c>
       <c r="Z36" s="37" t="n">
-        <v>300149.59</v>
+        <v>-3296.14</v>
       </c>
       <c r="AA36" s="18" t="n">
-        <v>312984.1</v>
+        <v>-3296.14</v>
       </c>
       <c r="AB36" s="19" t="n">
-        <v>330570.96</v>
+        <v>-2920.76</v>
       </c>
       <c r="AC36" s="10" t="n"/>
       <c r="AD36" s="10" t="n"/>
@@ -19466,80 +19808,80 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>지배주주지분</t>
+          <t>기타포괄이익누계액</t>
         </is>
       </c>
       <c r="E37" s="18" t="n">
-        <v>216871.56</v>
+        <v>9330.27</v>
       </c>
       <c r="F37" s="37" t="n">
-        <v>216871.56</v>
+        <v>9330.27</v>
       </c>
       <c r="G37" s="18" t="n">
-        <v>214235.41</v>
+        <v>9330.27</v>
       </c>
       <c r="H37" s="18" t="n">
-        <v>212977.67</v>
+        <v>9330.27</v>
       </c>
       <c r="I37" s="18" t="n">
-        <v>214778.23</v>
+        <v>9330.27</v>
       </c>
       <c r="J37" s="18" t="n">
-        <v>208156.94</v>
+        <v>9330.27</v>
       </c>
       <c r="K37" s="37" t="n">
-        <v>208156.94</v>
+        <v>9330.27</v>
       </c>
       <c r="L37" s="18" t="n">
-        <v>209546.73</v>
+        <v>9330.27</v>
       </c>
       <c r="M37" s="18" t="n">
-        <v>209950.91</v>
+        <v>9330.27</v>
       </c>
       <c r="N37" s="18" t="n">
-        <v>212427.32</v>
+        <v>9330.27</v>
       </c>
       <c r="O37" s="18" t="n">
-        <v>214815.25</v>
+        <v>9330.27</v>
       </c>
       <c r="P37" s="37" t="n">
-        <v>214815.25</v>
+        <v>9330.27</v>
       </c>
       <c r="Q37" s="18" t="n">
-        <v>218438.84</v>
+        <v>9330.27</v>
       </c>
       <c r="R37" s="18" t="n">
-        <v>222671.51</v>
+        <v>9330.27</v>
       </c>
       <c r="S37" s="18" t="n">
-        <v>224887.59</v>
+        <v>9330.27</v>
       </c>
       <c r="T37" s="18" t="n">
-        <v>234277.53</v>
+        <v>9330.27</v>
       </c>
       <c r="U37" s="37" t="n">
-        <v>234277.53</v>
+        <v>9330.27</v>
       </c>
       <c r="V37" s="18" t="n">
-        <v>238436.3</v>
+        <v>9330.27</v>
       </c>
       <c r="W37" s="18" t="n">
-        <v>243204.61</v>
+        <v>9330.27</v>
       </c>
       <c r="X37" s="18" t="n">
-        <v>250972</v>
+        <v>9330.27</v>
       </c>
       <c r="Y37" s="18" t="n">
-        <v>257369.37</v>
+        <v>9330.27</v>
       </c>
       <c r="Z37" s="37" t="n">
-        <v>257369.37</v>
+        <v>9330.27</v>
       </c>
       <c r="AA37" s="18" t="n">
-        <v>262307.21</v>
+        <v>9330.27</v>
       </c>
       <c r="AB37" s="19" t="n">
-        <v>270517.45</v>
+        <v>9330.27</v>
       </c>
       <c r="AC37" s="10" t="n"/>
       <c r="AD37" s="10" t="n"/>
@@ -19561,80 +19903,80 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>이자발생자산</t>
+          <t>이익잉여금</t>
         </is>
       </c>
       <c r="E38" s="18" t="n">
-        <v>36607.43</v>
+        <v>180385.56</v>
       </c>
       <c r="F38" s="37" t="n">
-        <v>36607.43</v>
+        <v>180385.56</v>
       </c>
       <c r="G38" s="18" t="n">
-        <v>22415.6</v>
+        <v>177743.87</v>
       </c>
       <c r="H38" s="18" t="n">
-        <v>22021.35</v>
+        <v>176448.47</v>
       </c>
       <c r="I38" s="18" t="n">
-        <v>25178.13</v>
+        <v>178241.25</v>
       </c>
       <c r="J38" s="18" t="n">
-        <v>21659.58</v>
+        <v>171606.02</v>
       </c>
       <c r="K38" s="37" t="n">
-        <v>21659.58</v>
+        <v>171606.02</v>
       </c>
       <c r="L38" s="18" t="n">
-        <v>20035.41</v>
+        <v>172987.78</v>
       </c>
       <c r="M38" s="18" t="n">
-        <v>25451.96</v>
+        <v>174292.42</v>
       </c>
       <c r="N38" s="18" t="n">
-        <v>17921.71</v>
+        <v>176802.39</v>
       </c>
       <c r="O38" s="18" t="n">
-        <v>29984.55</v>
+        <v>179173.92</v>
       </c>
       <c r="P38" s="37" t="n">
-        <v>29984.55</v>
+        <v>179173.92</v>
       </c>
       <c r="Q38" s="18" t="n">
-        <v>24578.62</v>
+        <v>182785.54</v>
       </c>
       <c r="R38" s="18" t="n">
-        <v>29218.42</v>
+        <v>186976.13</v>
       </c>
       <c r="S38" s="18" t="n">
-        <v>29322.15</v>
+        <v>189176.18</v>
       </c>
       <c r="T38" s="18" t="n">
-        <v>30793.59</v>
+        <v>198547.19</v>
       </c>
       <c r="U38" s="37" t="n">
-        <v>30793.59</v>
+        <v>198547.19</v>
       </c>
       <c r="V38" s="18" t="n">
-        <v>32180.7</v>
+        <v>202688.36</v>
       </c>
       <c r="W38" s="18" t="n">
-        <v>27156.16</v>
+        <v>207378.81</v>
       </c>
       <c r="X38" s="18" t="n">
-        <v>34691.89</v>
+        <v>215106.46</v>
       </c>
       <c r="Y38" s="18" t="n">
-        <v>53209.79</v>
+        <v>221279.35</v>
       </c>
       <c r="Z38" s="37" t="n">
-        <v>53209.79</v>
+        <v>221279.35</v>
       </c>
       <c r="AA38" s="18" t="n">
-        <v>48668.38</v>
+        <v>226217.19</v>
       </c>
       <c r="AB38" s="19" t="n">
-        <v>42721.37</v>
+        <v>233787.92</v>
       </c>
       <c r="AC38" s="10" t="n"/>
       <c r="AD38" s="10" t="n"/>
@@ -19656,46 +19998,81 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>기타비유동부채</t>
-        </is>
-      </c>
-      <c r="F39" s="9" t="n"/>
-      <c r="K39" s="9" t="n"/>
+          <t>자본총계</t>
+        </is>
+      </c>
+      <c r="E39" s="18" t="n">
+        <v>216871.56</v>
+      </c>
+      <c r="F39" s="37" t="n">
+        <v>216871.56</v>
+      </c>
+      <c r="G39" s="18" t="n">
+        <v>214235.41</v>
+      </c>
+      <c r="H39" s="18" t="n">
+        <v>212977.67</v>
+      </c>
+      <c r="I39" s="18" t="n">
+        <v>214778.23</v>
+      </c>
+      <c r="J39" s="18" t="n">
+        <v>208156.94</v>
+      </c>
+      <c r="K39" s="37" t="n">
+        <v>208156.94</v>
+      </c>
+      <c r="L39" s="18" t="n">
+        <v>209546.73</v>
+      </c>
+      <c r="M39" s="18" t="n">
+        <v>209950.91</v>
+      </c>
       <c r="N39" s="18" t="n">
-        <v>388</v>
+        <v>212427.32</v>
       </c>
       <c r="O39" s="18" t="n">
-        <v>368</v>
+        <v>214815.25</v>
       </c>
       <c r="P39" s="37" t="n">
-        <v>368</v>
+        <v>214815.25</v>
       </c>
       <c r="Q39" s="18" t="n">
-        <v>368</v>
+        <v>218438.84</v>
       </c>
       <c r="R39" s="18" t="n">
-        <v>368</v>
+        <v>222671.51</v>
       </c>
       <c r="S39" s="18" t="n">
-        <v>368</v>
+        <v>224887.59</v>
       </c>
       <c r="T39" s="18" t="n">
-        <v>368</v>
+        <v>234277.53</v>
       </c>
       <c r="U39" s="37" t="n">
-        <v>368</v>
+        <v>234277.53</v>
       </c>
       <c r="V39" s="18" t="n">
-        <v>368</v>
+        <v>238436.3</v>
       </c>
       <c r="W39" s="18" t="n">
-        <v>290</v>
+        <v>243204.61</v>
       </c>
       <c r="X39" s="18" t="n">
-        <v>290</v>
-      </c>
-      <c r="Z39" s="9" t="n"/>
-      <c r="AB39" s="5" t="n"/>
+        <v>250972</v>
+      </c>
+      <c r="Y39" s="18" t="n">
+        <v>257369.37</v>
+      </c>
+      <c r="Z39" s="37" t="n">
+        <v>257369.37</v>
+      </c>
+      <c r="AA39" s="18" t="n">
+        <v>262307.21</v>
+      </c>
+      <c r="AB39" s="19" t="n">
+        <v>270517.45</v>
+      </c>
       <c r="AC39" s="10" t="n"/>
       <c r="AD39" s="10" t="n"/>
       <c r="AE39" s="11" t="n"/>
@@ -19716,24 +20093,80 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>단기투자자산(공정가치)</t>
-        </is>
-      </c>
-      <c r="F40" s="9" t="n"/>
-      <c r="K40" s="9" t="n"/>
-      <c r="P40" s="9" t="n"/>
-      <c r="U40" s="9" t="n"/>
+          <t>부채와자본총계</t>
+        </is>
+      </c>
+      <c r="E40" s="18" t="n">
+        <v>241431.73</v>
+      </c>
+      <c r="F40" s="37" t="n">
+        <v>241431.73</v>
+      </c>
+      <c r="G40" s="18" t="n">
+        <v>236928.74</v>
+      </c>
+      <c r="H40" s="18" t="n">
+        <v>238045.93</v>
+      </c>
+      <c r="I40" s="18" t="n">
+        <v>242021.41</v>
+      </c>
+      <c r="J40" s="18" t="n">
+        <v>239085.99</v>
+      </c>
+      <c r="K40" s="37" t="n">
+        <v>239085.99</v>
+      </c>
+      <c r="L40" s="18" t="n">
+        <v>245766.22</v>
+      </c>
+      <c r="M40" s="18" t="n">
+        <v>259016.44</v>
+      </c>
+      <c r="N40" s="18" t="n">
+        <v>261330.87</v>
+      </c>
+      <c r="O40" s="18" t="n">
+        <v>275699.82</v>
+      </c>
+      <c r="P40" s="37" t="n">
+        <v>275699.82</v>
+      </c>
+      <c r="Q40" s="18" t="n">
+        <v>276591.11</v>
+      </c>
+      <c r="R40" s="18" t="n">
+        <v>283216.57</v>
+      </c>
+      <c r="S40" s="18" t="n">
+        <v>280780.74</v>
+      </c>
+      <c r="T40" s="18" t="n">
+        <v>289770.81</v>
+      </c>
+      <c r="U40" s="37" t="n">
+        <v>289770.81</v>
+      </c>
+      <c r="V40" s="18" t="n">
+        <v>291838.36</v>
+      </c>
+      <c r="W40" s="18" t="n">
+        <v>297235.91</v>
+      </c>
+      <c r="X40" s="18" t="n">
+        <v>299316.59</v>
+      </c>
       <c r="Y40" s="18" t="n">
-        <v>34769.73</v>
+        <v>300149.59</v>
       </c>
       <c r="Z40" s="37" t="n">
-        <v>34769.73</v>
+        <v>300149.59</v>
       </c>
       <c r="AA40" s="18" t="n">
-        <v>40501.05</v>
+        <v>312984.1</v>
       </c>
       <c r="AB40" s="19" t="n">
-        <v>19876.64</v>
+        <v>330570.96</v>
       </c>
       <c r="AC40" s="10" t="n"/>
       <c r="AD40" s="10" t="n"/>
@@ -19755,24 +20188,80 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>기타유동자산</t>
-        </is>
-      </c>
-      <c r="F41" s="9" t="n"/>
-      <c r="K41" s="9" t="n"/>
-      <c r="P41" s="9" t="n"/>
-      <c r="U41" s="9" t="n"/>
+          <t>지배주주지분</t>
+        </is>
+      </c>
+      <c r="E41" s="18" t="n">
+        <v>216871.56</v>
+      </c>
+      <c r="F41" s="37" t="n">
+        <v>216871.56</v>
+      </c>
+      <c r="G41" s="18" t="n">
+        <v>214235.41</v>
+      </c>
+      <c r="H41" s="18" t="n">
+        <v>212977.67</v>
+      </c>
+      <c r="I41" s="18" t="n">
+        <v>214778.23</v>
+      </c>
+      <c r="J41" s="18" t="n">
+        <v>208156.94</v>
+      </c>
+      <c r="K41" s="37" t="n">
+        <v>208156.94</v>
+      </c>
+      <c r="L41" s="18" t="n">
+        <v>209546.73</v>
+      </c>
+      <c r="M41" s="18" t="n">
+        <v>209950.91</v>
+      </c>
+      <c r="N41" s="18" t="n">
+        <v>212427.32</v>
+      </c>
+      <c r="O41" s="18" t="n">
+        <v>214815.25</v>
+      </c>
+      <c r="P41" s="37" t="n">
+        <v>214815.25</v>
+      </c>
+      <c r="Q41" s="18" t="n">
+        <v>218438.84</v>
+      </c>
+      <c r="R41" s="18" t="n">
+        <v>222671.51</v>
+      </c>
+      <c r="S41" s="18" t="n">
+        <v>224887.59</v>
+      </c>
+      <c r="T41" s="18" t="n">
+        <v>234277.53</v>
+      </c>
+      <c r="U41" s="37" t="n">
+        <v>234277.53</v>
+      </c>
+      <c r="V41" s="18" t="n">
+        <v>238436.3</v>
+      </c>
+      <c r="W41" s="18" t="n">
+        <v>243204.61</v>
+      </c>
+      <c r="X41" s="18" t="n">
+        <v>250972</v>
+      </c>
       <c r="Y41" s="18" t="n">
-        <v>14318.03</v>
+        <v>257369.37</v>
       </c>
       <c r="Z41" s="37" t="n">
-        <v>14318.03</v>
+        <v>257369.37</v>
       </c>
       <c r="AA41" s="18" t="n">
-        <v>16075.42</v>
+        <v>262307.21</v>
       </c>
       <c r="AB41" s="19" t="n">
-        <v>12112.62</v>
+        <v>270517.45</v>
       </c>
       <c r="AC41" s="10" t="n"/>
       <c r="AD41" s="10" t="n"/>
@@ -19794,24 +20283,80 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>장기매출채권및기타채권</t>
-        </is>
-      </c>
-      <c r="F42" s="9" t="n"/>
-      <c r="K42" s="9" t="n"/>
-      <c r="P42" s="9" t="n"/>
-      <c r="U42" s="9" t="n"/>
+          <t>이자발생자산</t>
+        </is>
+      </c>
+      <c r="E42" s="18" t="n">
+        <v>76187.85000000001</v>
+      </c>
+      <c r="F42" s="37" t="n">
+        <v>76187.85000000001</v>
+      </c>
+      <c r="G42" s="18" t="n">
+        <v>65945.87</v>
+      </c>
+      <c r="H42" s="18" t="n">
+        <v>63534.99</v>
+      </c>
+      <c r="I42" s="18" t="n">
+        <v>66608.57000000001</v>
+      </c>
+      <c r="J42" s="18" t="n">
+        <v>62507.99</v>
+      </c>
+      <c r="K42" s="37" t="n">
+        <v>62507.99</v>
+      </c>
+      <c r="L42" s="18" t="n">
+        <v>62088.37</v>
+      </c>
+      <c r="M42" s="18" t="n">
+        <v>67937.35000000001</v>
+      </c>
+      <c r="N42" s="18" t="n">
+        <v>62867.69</v>
+      </c>
+      <c r="O42" s="18" t="n">
+        <v>76157.02</v>
+      </c>
+      <c r="P42" s="37" t="n">
+        <v>76157.02</v>
+      </c>
+      <c r="Q42" s="18" t="n">
+        <v>71189.73</v>
+      </c>
+      <c r="R42" s="18" t="n">
+        <v>76236.34</v>
+      </c>
+      <c r="S42" s="18" t="n">
+        <v>76464.88</v>
+      </c>
+      <c r="T42" s="18" t="n">
+        <v>71808.44</v>
+      </c>
+      <c r="U42" s="37" t="n">
+        <v>71808.44</v>
+      </c>
+      <c r="V42" s="18" t="n">
+        <v>59263.52</v>
+      </c>
+      <c r="W42" s="18" t="n">
+        <v>39374.18</v>
+      </c>
+      <c r="X42" s="18" t="n">
+        <v>47603.61</v>
+      </c>
       <c r="Y42" s="18" t="n">
-        <v>809.54</v>
+        <v>53209.79</v>
       </c>
       <c r="Z42" s="37" t="n">
-        <v>809.54</v>
+        <v>53209.79</v>
       </c>
       <c r="AA42" s="18" t="n">
-        <v>922.35</v>
+        <v>48668.38</v>
       </c>
       <c r="AB42" s="19" t="n">
-        <v>1030.21</v>
+        <v>42721.37</v>
       </c>
       <c r="AC42" s="10" t="n"/>
       <c r="AD42" s="10" t="n"/>
@@ -19833,25 +20378,46 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>장기금융자산</t>
+          <t>기타비유동부채</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
       <c r="K43" s="9" t="n"/>
-      <c r="P43" s="9" t="n"/>
-      <c r="U43" s="9" t="n"/>
-      <c r="Y43" s="18" t="n">
-        <v>13921.85</v>
-      </c>
-      <c r="Z43" s="37" t="n">
-        <v>13921.85</v>
-      </c>
-      <c r="AA43" s="18" t="n">
-        <v>8949.139999999999</v>
-      </c>
-      <c r="AB43" s="19" t="n">
-        <v>9481.4</v>
-      </c>
+      <c r="N43" s="18" t="n">
+        <v>388</v>
+      </c>
+      <c r="O43" s="18" t="n">
+        <v>368</v>
+      </c>
+      <c r="P43" s="37" t="n">
+        <v>368</v>
+      </c>
+      <c r="Q43" s="18" t="n">
+        <v>368</v>
+      </c>
+      <c r="R43" s="18" t="n">
+        <v>368</v>
+      </c>
+      <c r="S43" s="18" t="n">
+        <v>368</v>
+      </c>
+      <c r="T43" s="18" t="n">
+        <v>368</v>
+      </c>
+      <c r="U43" s="37" t="n">
+        <v>368</v>
+      </c>
+      <c r="V43" s="18" t="n">
+        <v>368</v>
+      </c>
+      <c r="W43" s="18" t="n">
+        <v>290</v>
+      </c>
+      <c r="X43" s="18" t="n">
+        <v>290</v>
+      </c>
+      <c r="Z43" s="9" t="n"/>
+      <c r="AB43" s="5" t="n"/>
       <c r="AC43" s="10" t="n"/>
       <c r="AD43" s="10" t="n"/>
       <c r="AE43" s="11" t="n"/>
@@ -19872,7 +20438,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>사용권자산</t>
+          <t>기타유동자산</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -19880,16 +20446,16 @@
       <c r="P44" s="9" t="n"/>
       <c r="U44" s="9" t="n"/>
       <c r="Y44" s="18" t="n">
-        <v>401.66</v>
+        <v>14318.03</v>
       </c>
       <c r="Z44" s="37" t="n">
-        <v>401.66</v>
+        <v>14318.03</v>
       </c>
       <c r="AA44" s="18" t="n">
-        <v>337.07</v>
+        <v>16075.42</v>
       </c>
       <c r="AB44" s="19" t="n">
-        <v>360.87</v>
+        <v>12112.62</v>
       </c>
       <c r="AC44" s="10" t="n"/>
       <c r="AD44" s="10" t="n"/>
@@ -19911,7 +20477,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>기타비유동자산</t>
+          <t>사용권자산</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -19950,7 +20516,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>기타유동부채</t>
+          <t>기타비유동자산</t>
         </is>
       </c>
       <c r="F46" s="9" t="n"/>
@@ -19958,16 +20524,16 @@
       <c r="P46" s="9" t="n"/>
       <c r="U46" s="9" t="n"/>
       <c r="Y46" s="18" t="n">
-        <v>19433.67</v>
+        <v>401.66</v>
       </c>
       <c r="Z46" s="37" t="n">
-        <v>19433.67</v>
+        <v>401.66</v>
       </c>
       <c r="AA46" s="18" t="n">
-        <v>18964.12</v>
+        <v>337.07</v>
       </c>
       <c r="AB46" s="19" t="n">
-        <v>31233.47</v>
+        <v>360.87</v>
       </c>
       <c r="AC46" s="10" t="n"/>
       <c r="AD46" s="10" t="n"/>
@@ -19989,7 +20555,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>비유동리스부채</t>
+          <t>기타유동부채</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -19997,16 +20563,16 @@
       <c r="P47" s="9" t="n"/>
       <c r="U47" s="9" t="n"/>
       <c r="Y47" s="18" t="n">
-        <v>163.37</v>
+        <v>19433.67</v>
       </c>
       <c r="Z47" s="37" t="n">
-        <v>163.37</v>
+        <v>19433.67</v>
       </c>
       <c r="AA47" s="18" t="n">
-        <v>110.57</v>
+        <v>18964.12</v>
       </c>
       <c r="AB47" s="19" t="n">
-        <v>93.43000000000001</v>
+        <v>31233.47</v>
       </c>
       <c r="AC47" s="10" t="n"/>
       <c r="AD47" s="10" t="n"/>
@@ -35878,7 +36444,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3132.9</v>
+        <v>2956.3</v>
       </c>
     </row>
     <row r="30">
@@ -35898,7 +36464,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.68</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="32">
@@ -35918,7 +36484,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1048</v>
+        <v>0.0989</v>
       </c>
     </row>
     <row r="34">
@@ -35928,7 +36494,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="35">
@@ -35938,7 +36504,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>34700</v>
+        <v>32900</v>
       </c>
     </row>
     <row r="36">

--- a/argus/kship/models/108380_model.xlsx
+++ b/argus/kship/models/108380_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4700,35 +4700,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4819,35 +4819,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4938,35 +4938,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5057,35 +5057,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5176,35 +5176,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5295,35 +5295,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5414,35 +5414,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5533,35 +5533,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5668,7 +5668,7 @@
         <v>18520</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>17780</v>
+        <v>17750</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5941,7 +5941,7 @@
         <v>17674.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>18418</v>
+        <v>18412</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8257,11 +8257,11 @@
         </is>
       </c>
       <c r="D39" s="34" t="n">
-        <v>17780</v>
+        <v>17750</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 18,790원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 18,080원)</t>
         </is>
       </c>
       <c r="F39" s="9" t="n"/>
@@ -8571,7 +8571,7 @@
         </is>
       </c>
       <c r="D47" s="36" t="n">
-        <v>0.06922589795370447</v>
+        <v>0.06922589795370446</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.01</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/108380_model.xlsx
+++ b/argus/kship/models/108380_model.xlsx
@@ -3829,7 +3829,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4700,35 +4700,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4819,35 +4819,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4938,35 +4938,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5057,35 +5057,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5176,35 +5176,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5295,35 +5295,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5414,35 +5414,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5533,35 +5533,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9123,7 +9123,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16565,7 +16565,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/108380_model.xlsx
+++ b/argus/kship/models/108380_model.xlsx
@@ -3829,7 +3829,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9123,7 +9123,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16565,7 +16565,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/108380_model.xlsx
+++ b/argus/kship/models/108380_model.xlsx
@@ -3829,7 +3829,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5668,7 @@
         <v>18520</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>17750</v>
+        <v>16760</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5850,7 +5850,7 @@
         <v>14000</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>17630</v>
+        <v>16670</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5941,7 +5941,7 @@
         <v>17674.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>18412</v>
+        <v>18136.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8257,7 +8257,7 @@
         </is>
       </c>
       <c r="D39" s="34" t="n">
-        <v>17750</v>
+        <v>16760</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
       </c>
       <c r="D40" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16565,7 +16565,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29707,7 +29707,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34456,7 +34456,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36464,7 +36464,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="32">
@@ -36474,7 +36474,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/108380_model.xlsx
+++ b/argus/kship/models/108380_model.xlsx
@@ -3829,7 +3829,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4700,35 +4700,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4819,35 +4819,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4938,35 +4938,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5057,35 +5057,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5176,35 +5176,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5295,35 +5295,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5414,35 +5414,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5533,35 +5533,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5668,7 +5668,7 @@
         <v>18520</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>16760</v>
+        <v>16860</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5850,7 +5850,7 @@
         <v>14000</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>16670</v>
+        <v>16190</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5941,7 +5941,7 @@
         <v>17674.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>18136.7</v>
+        <v>17945.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8257,11 +8257,11 @@
         </is>
       </c>
       <c r="D39" s="34" t="n">
-        <v>16760</v>
+        <v>16860</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 18,080원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 17,680원)</t>
         </is>
       </c>
       <c r="F39" s="9" t="n"/>
@@ -8297,7 +8297,7 @@
       </c>
       <c r="D40" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16565,7 +16565,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29707,7 +29707,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34456,7 +34456,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36464,7 +36464,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.67</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/108380_model.xlsx
+++ b/argus/kship/models/108380_model.xlsx
@@ -3829,7 +3829,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4700,35 +4700,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4819,35 +4819,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4938,35 +4938,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5057,35 +5057,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5176,35 +5176,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5295,35 +5295,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5414,35 +5414,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5533,35 +5533,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5668,7 +5668,7 @@
         <v>18520</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>16860</v>
+        <v>17140</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5941,7 +5941,7 @@
         <v>17674.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>17945.7</v>
+        <v>17830</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8257,11 +8257,11 @@
         </is>
       </c>
       <c r="D39" s="34" t="n">
-        <v>16860</v>
+        <v>17140</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 17,680원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 16,670원)</t>
         </is>
       </c>
       <c r="F39" s="9" t="n"/>
@@ -8297,7 +8297,7 @@
       </c>
       <c r="D40" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16565,7 +16565,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29707,7 +29707,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34456,7 +34456,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36464,7 +36464,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="32">
@@ -36474,7 +36474,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/108380_model.xlsx
+++ b/argus/kship/models/108380_model.xlsx
@@ -3829,7 +3829,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4700,35 +4700,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4819,35 +4819,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4938,35 +4938,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5057,35 +5057,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5176,35 +5176,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5295,35 +5295,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5414,35 +5414,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5533,35 +5533,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5668,7 +5668,7 @@
         <v>18520</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>17140</v>
+        <v>16700</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5850,7 +5850,7 @@
         <v>14000</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>16190</v>
+        <v>15600</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5941,7 +5941,7 @@
         <v>17674.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>17830</v>
+        <v>17408.2</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8257,11 +8257,11 @@
         </is>
       </c>
       <c r="D39" s="34" t="n">
-        <v>17140</v>
+        <v>16700</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 16,670원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 16,150원)</t>
         </is>
       </c>
       <c r="F39" s="9" t="n"/>
@@ -8297,7 +8297,7 @@
       </c>
       <c r="D40" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16565,7 +16565,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29707,7 +29707,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34456,7 +34456,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36464,7 +36464,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.8</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="32">
@@ -36474,7 +36474,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/108380_model.xlsx
+++ b/argus/kship/models/108380_model.xlsx
@@ -3829,7 +3829,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4700,35 +4700,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4819,35 +4819,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4938,35 +4938,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5057,35 +5057,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5176,35 +5176,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5295,35 +5295,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5414,35 +5414,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5533,35 +5533,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5668,7 +5668,7 @@
         <v>18520</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>16700</v>
+        <v>14720</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5850,7 +5850,7 @@
         <v>14000</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>15600</v>
+        <v>14690</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5941,7 +5941,7 @@
         <v>17674.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>17408.2</v>
+        <v>16833.1</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8257,11 +8257,11 @@
         </is>
       </c>
       <c r="D39" s="34" t="n">
-        <v>16700</v>
+        <v>14720</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 16,150원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 15,550원)</t>
         </is>
       </c>
       <c r="F39" s="9" t="n"/>
@@ -8297,7 +8297,7 @@
       </c>
       <c r="D40" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16565,7 +16565,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29707,7 +29707,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34456,7 +34456,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36464,7 +36464,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.65</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="32">
@@ -36474,7 +36474,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="33">
